--- a/docs/modelo-cadastro-gestores.xlsx
+++ b/docs/modelo-cadastro-gestores.xlsx
@@ -7,9 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pessoas" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gestor por empresa" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Como preencher" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gestor por empresa" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Base de gestores" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pessoas" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Como preencher" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,6 +442,9101 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Nome do gestor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Cargo</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>E-mail do gestor</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Gestor de contrato,Gerente,Supervisor,Coordenador"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E3001"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Nome do gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>E-mail do gestor</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Gerência de área (GA)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Gerência geral (GG)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Centro de custo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="E2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="E4" s="2" t="n"/>
+    </row>
+    <row r="5">
+      <c r="E5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="E6" s="2" t="n"/>
+    </row>
+    <row r="7">
+      <c r="E7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="E8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="E9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="E10" s="2" t="n"/>
+    </row>
+    <row r="11">
+      <c r="E11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="E12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="E13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="E14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="E15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="E16" s="2" t="n"/>
+    </row>
+    <row r="17">
+      <c r="E17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="E18" s="2" t="n"/>
+    </row>
+    <row r="19">
+      <c r="E19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="E20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="E21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="E22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="E23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="E24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="E25" s="2" t="n"/>
+    </row>
+    <row r="26">
+      <c r="E26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="E27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="E28" s="2" t="n"/>
+    </row>
+    <row r="29">
+      <c r="E29" s="2" t="n"/>
+    </row>
+    <row r="30">
+      <c r="E30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="E31" s="2" t="n"/>
+    </row>
+    <row r="32">
+      <c r="E32" s="2" t="n"/>
+    </row>
+    <row r="33">
+      <c r="E33" s="2" t="n"/>
+    </row>
+    <row r="34">
+      <c r="E34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="E35" s="2" t="n"/>
+    </row>
+    <row r="36">
+      <c r="E36" s="2" t="n"/>
+    </row>
+    <row r="37">
+      <c r="E37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="E38" s="2" t="n"/>
+    </row>
+    <row r="39">
+      <c r="E39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="E40" s="2" t="n"/>
+    </row>
+    <row r="41">
+      <c r="E41" s="2" t="n"/>
+    </row>
+    <row r="42">
+      <c r="E42" s="2" t="n"/>
+    </row>
+    <row r="43">
+      <c r="E43" s="2" t="n"/>
+    </row>
+    <row r="44">
+      <c r="E44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="E45" s="2" t="n"/>
+    </row>
+    <row r="46">
+      <c r="E46" s="2" t="n"/>
+    </row>
+    <row r="47">
+      <c r="E47" s="2" t="n"/>
+    </row>
+    <row r="48">
+      <c r="E48" s="2" t="n"/>
+    </row>
+    <row r="49">
+      <c r="E49" s="2" t="n"/>
+    </row>
+    <row r="50">
+      <c r="E50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="E51" s="2" t="n"/>
+    </row>
+    <row r="52">
+      <c r="E52" s="2" t="n"/>
+    </row>
+    <row r="53">
+      <c r="E53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="E54" s="2" t="n"/>
+    </row>
+    <row r="55">
+      <c r="E55" s="2" t="n"/>
+    </row>
+    <row r="56">
+      <c r="E56" s="2" t="n"/>
+    </row>
+    <row r="57">
+      <c r="E57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="E58" s="2" t="n"/>
+    </row>
+    <row r="59">
+      <c r="E59" s="2" t="n"/>
+    </row>
+    <row r="60">
+      <c r="E60" s="2" t="n"/>
+    </row>
+    <row r="61">
+      <c r="E61" s="2" t="n"/>
+    </row>
+    <row r="62">
+      <c r="E62" s="2" t="n"/>
+    </row>
+    <row r="63">
+      <c r="E63" s="2" t="n"/>
+    </row>
+    <row r="64">
+      <c r="E64" s="2" t="n"/>
+    </row>
+    <row r="65">
+      <c r="E65" s="2" t="n"/>
+    </row>
+    <row r="66">
+      <c r="E66" s="2" t="n"/>
+    </row>
+    <row r="67">
+      <c r="E67" s="2" t="n"/>
+    </row>
+    <row r="68">
+      <c r="E68" s="2" t="n"/>
+    </row>
+    <row r="69">
+      <c r="E69" s="2" t="n"/>
+    </row>
+    <row r="70">
+      <c r="E70" s="2" t="n"/>
+    </row>
+    <row r="71">
+      <c r="E71" s="2" t="n"/>
+    </row>
+    <row r="72">
+      <c r="E72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="E73" s="2" t="n"/>
+    </row>
+    <row r="74">
+      <c r="E74" s="2" t="n"/>
+    </row>
+    <row r="75">
+      <c r="E75" s="2" t="n"/>
+    </row>
+    <row r="76">
+      <c r="E76" s="2" t="n"/>
+    </row>
+    <row r="77">
+      <c r="E77" s="2" t="n"/>
+    </row>
+    <row r="78">
+      <c r="E78" s="2" t="n"/>
+    </row>
+    <row r="79">
+      <c r="E79" s="2" t="n"/>
+    </row>
+    <row r="80">
+      <c r="E80" s="2" t="n"/>
+    </row>
+    <row r="81">
+      <c r="E81" s="2" t="n"/>
+    </row>
+    <row r="82">
+      <c r="E82" s="2" t="n"/>
+    </row>
+    <row r="83">
+      <c r="E83" s="2" t="n"/>
+    </row>
+    <row r="84">
+      <c r="E84" s="2" t="n"/>
+    </row>
+    <row r="85">
+      <c r="E85" s="2" t="n"/>
+    </row>
+    <row r="86">
+      <c r="E86" s="2" t="n"/>
+    </row>
+    <row r="87">
+      <c r="E87" s="2" t="n"/>
+    </row>
+    <row r="88">
+      <c r="E88" s="2" t="n"/>
+    </row>
+    <row r="89">
+      <c r="E89" s="2" t="n"/>
+    </row>
+    <row r="90">
+      <c r="E90" s="2" t="n"/>
+    </row>
+    <row r="91">
+      <c r="E91" s="2" t="n"/>
+    </row>
+    <row r="92">
+      <c r="E92" s="2" t="n"/>
+    </row>
+    <row r="93">
+      <c r="E93" s="2" t="n"/>
+    </row>
+    <row r="94">
+      <c r="E94" s="2" t="n"/>
+    </row>
+    <row r="95">
+      <c r="E95" s="2" t="n"/>
+    </row>
+    <row r="96">
+      <c r="E96" s="2" t="n"/>
+    </row>
+    <row r="97">
+      <c r="E97" s="2" t="n"/>
+    </row>
+    <row r="98">
+      <c r="E98" s="2" t="n"/>
+    </row>
+    <row r="99">
+      <c r="E99" s="2" t="n"/>
+    </row>
+    <row r="100">
+      <c r="E100" s="2" t="n"/>
+    </row>
+    <row r="101">
+      <c r="E101" s="2" t="n"/>
+    </row>
+    <row r="102">
+      <c r="E102" s="2" t="n"/>
+    </row>
+    <row r="103">
+      <c r="E103" s="2" t="n"/>
+    </row>
+    <row r="104">
+      <c r="E104" s="2" t="n"/>
+    </row>
+    <row r="105">
+      <c r="E105" s="2" t="n"/>
+    </row>
+    <row r="106">
+      <c r="E106" s="2" t="n"/>
+    </row>
+    <row r="107">
+      <c r="E107" s="2" t="n"/>
+    </row>
+    <row r="108">
+      <c r="E108" s="2" t="n"/>
+    </row>
+    <row r="109">
+      <c r="E109" s="2" t="n"/>
+    </row>
+    <row r="110">
+      <c r="E110" s="2" t="n"/>
+    </row>
+    <row r="111">
+      <c r="E111" s="2" t="n"/>
+    </row>
+    <row r="112">
+      <c r="E112" s="2" t="n"/>
+    </row>
+    <row r="113">
+      <c r="E113" s="2" t="n"/>
+    </row>
+    <row r="114">
+      <c r="E114" s="2" t="n"/>
+    </row>
+    <row r="115">
+      <c r="E115" s="2" t="n"/>
+    </row>
+    <row r="116">
+      <c r="E116" s="2" t="n"/>
+    </row>
+    <row r="117">
+      <c r="E117" s="2" t="n"/>
+    </row>
+    <row r="118">
+      <c r="E118" s="2" t="n"/>
+    </row>
+    <row r="119">
+      <c r="E119" s="2" t="n"/>
+    </row>
+    <row r="120">
+      <c r="E120" s="2" t="n"/>
+    </row>
+    <row r="121">
+      <c r="E121" s="2" t="n"/>
+    </row>
+    <row r="122">
+      <c r="E122" s="2" t="n"/>
+    </row>
+    <row r="123">
+      <c r="E123" s="2" t="n"/>
+    </row>
+    <row r="124">
+      <c r="E124" s="2" t="n"/>
+    </row>
+    <row r="125">
+      <c r="E125" s="2" t="n"/>
+    </row>
+    <row r="126">
+      <c r="E126" s="2" t="n"/>
+    </row>
+    <row r="127">
+      <c r="E127" s="2" t="n"/>
+    </row>
+    <row r="128">
+      <c r="E128" s="2" t="n"/>
+    </row>
+    <row r="129">
+      <c r="E129" s="2" t="n"/>
+    </row>
+    <row r="130">
+      <c r="E130" s="2" t="n"/>
+    </row>
+    <row r="131">
+      <c r="E131" s="2" t="n"/>
+    </row>
+    <row r="132">
+      <c r="E132" s="2" t="n"/>
+    </row>
+    <row r="133">
+      <c r="E133" s="2" t="n"/>
+    </row>
+    <row r="134">
+      <c r="E134" s="2" t="n"/>
+    </row>
+    <row r="135">
+      <c r="E135" s="2" t="n"/>
+    </row>
+    <row r="136">
+      <c r="E136" s="2" t="n"/>
+    </row>
+    <row r="137">
+      <c r="E137" s="2" t="n"/>
+    </row>
+    <row r="138">
+      <c r="E138" s="2" t="n"/>
+    </row>
+    <row r="139">
+      <c r="E139" s="2" t="n"/>
+    </row>
+    <row r="140">
+      <c r="E140" s="2" t="n"/>
+    </row>
+    <row r="141">
+      <c r="E141" s="2" t="n"/>
+    </row>
+    <row r="142">
+      <c r="E142" s="2" t="n"/>
+    </row>
+    <row r="143">
+      <c r="E143" s="2" t="n"/>
+    </row>
+    <row r="144">
+      <c r="E144" s="2" t="n"/>
+    </row>
+    <row r="145">
+      <c r="E145" s="2" t="n"/>
+    </row>
+    <row r="146">
+      <c r="E146" s="2" t="n"/>
+    </row>
+    <row r="147">
+      <c r="E147" s="2" t="n"/>
+    </row>
+    <row r="148">
+      <c r="E148" s="2" t="n"/>
+    </row>
+    <row r="149">
+      <c r="E149" s="2" t="n"/>
+    </row>
+    <row r="150">
+      <c r="E150" s="2" t="n"/>
+    </row>
+    <row r="151">
+      <c r="E151" s="2" t="n"/>
+    </row>
+    <row r="152">
+      <c r="E152" s="2" t="n"/>
+    </row>
+    <row r="153">
+      <c r="E153" s="2" t="n"/>
+    </row>
+    <row r="154">
+      <c r="E154" s="2" t="n"/>
+    </row>
+    <row r="155">
+      <c r="E155" s="2" t="n"/>
+    </row>
+    <row r="156">
+      <c r="E156" s="2" t="n"/>
+    </row>
+    <row r="157">
+      <c r="E157" s="2" t="n"/>
+    </row>
+    <row r="158">
+      <c r="E158" s="2" t="n"/>
+    </row>
+    <row r="159">
+      <c r="E159" s="2" t="n"/>
+    </row>
+    <row r="160">
+      <c r="E160" s="2" t="n"/>
+    </row>
+    <row r="161">
+      <c r="E161" s="2" t="n"/>
+    </row>
+    <row r="162">
+      <c r="E162" s="2" t="n"/>
+    </row>
+    <row r="163">
+      <c r="E163" s="2" t="n"/>
+    </row>
+    <row r="164">
+      <c r="E164" s="2" t="n"/>
+    </row>
+    <row r="165">
+      <c r="E165" s="2" t="n"/>
+    </row>
+    <row r="166">
+      <c r="E166" s="2" t="n"/>
+    </row>
+    <row r="167">
+      <c r="E167" s="2" t="n"/>
+    </row>
+    <row r="168">
+      <c r="E168" s="2" t="n"/>
+    </row>
+    <row r="169">
+      <c r="E169" s="2" t="n"/>
+    </row>
+    <row r="170">
+      <c r="E170" s="2" t="n"/>
+    </row>
+    <row r="171">
+      <c r="E171" s="2" t="n"/>
+    </row>
+    <row r="172">
+      <c r="E172" s="2" t="n"/>
+    </row>
+    <row r="173">
+      <c r="E173" s="2" t="n"/>
+    </row>
+    <row r="174">
+      <c r="E174" s="2" t="n"/>
+    </row>
+    <row r="175">
+      <c r="E175" s="2" t="n"/>
+    </row>
+    <row r="176">
+      <c r="E176" s="2" t="n"/>
+    </row>
+    <row r="177">
+      <c r="E177" s="2" t="n"/>
+    </row>
+    <row r="178">
+      <c r="E178" s="2" t="n"/>
+    </row>
+    <row r="179">
+      <c r="E179" s="2" t="n"/>
+    </row>
+    <row r="180">
+      <c r="E180" s="2" t="n"/>
+    </row>
+    <row r="181">
+      <c r="E181" s="2" t="n"/>
+    </row>
+    <row r="182">
+      <c r="E182" s="2" t="n"/>
+    </row>
+    <row r="183">
+      <c r="E183" s="2" t="n"/>
+    </row>
+    <row r="184">
+      <c r="E184" s="2" t="n"/>
+    </row>
+    <row r="185">
+      <c r="E185" s="2" t="n"/>
+    </row>
+    <row r="186">
+      <c r="E186" s="2" t="n"/>
+    </row>
+    <row r="187">
+      <c r="E187" s="2" t="n"/>
+    </row>
+    <row r="188">
+      <c r="E188" s="2" t="n"/>
+    </row>
+    <row r="189">
+      <c r="E189" s="2" t="n"/>
+    </row>
+    <row r="190">
+      <c r="E190" s="2" t="n"/>
+    </row>
+    <row r="191">
+      <c r="E191" s="2" t="n"/>
+    </row>
+    <row r="192">
+      <c r="E192" s="2" t="n"/>
+    </row>
+    <row r="193">
+      <c r="E193" s="2" t="n"/>
+    </row>
+    <row r="194">
+      <c r="E194" s="2" t="n"/>
+    </row>
+    <row r="195">
+      <c r="E195" s="2" t="n"/>
+    </row>
+    <row r="196">
+      <c r="E196" s="2" t="n"/>
+    </row>
+    <row r="197">
+      <c r="E197" s="2" t="n"/>
+    </row>
+    <row r="198">
+      <c r="E198" s="2" t="n"/>
+    </row>
+    <row r="199">
+      <c r="E199" s="2" t="n"/>
+    </row>
+    <row r="200">
+      <c r="E200" s="2" t="n"/>
+    </row>
+    <row r="201">
+      <c r="E201" s="2" t="n"/>
+    </row>
+    <row r="202">
+      <c r="E202" s="2" t="n"/>
+    </row>
+    <row r="203">
+      <c r="E203" s="2" t="n"/>
+    </row>
+    <row r="204">
+      <c r="E204" s="2" t="n"/>
+    </row>
+    <row r="205">
+      <c r="E205" s="2" t="n"/>
+    </row>
+    <row r="206">
+      <c r="E206" s="2" t="n"/>
+    </row>
+    <row r="207">
+      <c r="E207" s="2" t="n"/>
+    </row>
+    <row r="208">
+      <c r="E208" s="2" t="n"/>
+    </row>
+    <row r="209">
+      <c r="E209" s="2" t="n"/>
+    </row>
+    <row r="210">
+      <c r="E210" s="2" t="n"/>
+    </row>
+    <row r="211">
+      <c r="E211" s="2" t="n"/>
+    </row>
+    <row r="212">
+      <c r="E212" s="2" t="n"/>
+    </row>
+    <row r="213">
+      <c r="E213" s="2" t="n"/>
+    </row>
+    <row r="214">
+      <c r="E214" s="2" t="n"/>
+    </row>
+    <row r="215">
+      <c r="E215" s="2" t="n"/>
+    </row>
+    <row r="216">
+      <c r="E216" s="2" t="n"/>
+    </row>
+    <row r="217">
+      <c r="E217" s="2" t="n"/>
+    </row>
+    <row r="218">
+      <c r="E218" s="2" t="n"/>
+    </row>
+    <row r="219">
+      <c r="E219" s="2" t="n"/>
+    </row>
+    <row r="220">
+      <c r="E220" s="2" t="n"/>
+    </row>
+    <row r="221">
+      <c r="E221" s="2" t="n"/>
+    </row>
+    <row r="222">
+      <c r="E222" s="2" t="n"/>
+    </row>
+    <row r="223">
+      <c r="E223" s="2" t="n"/>
+    </row>
+    <row r="224">
+      <c r="E224" s="2" t="n"/>
+    </row>
+    <row r="225">
+      <c r="E225" s="2" t="n"/>
+    </row>
+    <row r="226">
+      <c r="E226" s="2" t="n"/>
+    </row>
+    <row r="227">
+      <c r="E227" s="2" t="n"/>
+    </row>
+    <row r="228">
+      <c r="E228" s="2" t="n"/>
+    </row>
+    <row r="229">
+      <c r="E229" s="2" t="n"/>
+    </row>
+    <row r="230">
+      <c r="E230" s="2" t="n"/>
+    </row>
+    <row r="231">
+      <c r="E231" s="2" t="n"/>
+    </row>
+    <row r="232">
+      <c r="E232" s="2" t="n"/>
+    </row>
+    <row r="233">
+      <c r="E233" s="2" t="n"/>
+    </row>
+    <row r="234">
+      <c r="E234" s="2" t="n"/>
+    </row>
+    <row r="235">
+      <c r="E235" s="2" t="n"/>
+    </row>
+    <row r="236">
+      <c r="E236" s="2" t="n"/>
+    </row>
+    <row r="237">
+      <c r="E237" s="2" t="n"/>
+    </row>
+    <row r="238">
+      <c r="E238" s="2" t="n"/>
+    </row>
+    <row r="239">
+      <c r="E239" s="2" t="n"/>
+    </row>
+    <row r="240">
+      <c r="E240" s="2" t="n"/>
+    </row>
+    <row r="241">
+      <c r="E241" s="2" t="n"/>
+    </row>
+    <row r="242">
+      <c r="E242" s="2" t="n"/>
+    </row>
+    <row r="243">
+      <c r="E243" s="2" t="n"/>
+    </row>
+    <row r="244">
+      <c r="E244" s="2" t="n"/>
+    </row>
+    <row r="245">
+      <c r="E245" s="2" t="n"/>
+    </row>
+    <row r="246">
+      <c r="E246" s="2" t="n"/>
+    </row>
+    <row r="247">
+      <c r="E247" s="2" t="n"/>
+    </row>
+    <row r="248">
+      <c r="E248" s="2" t="n"/>
+    </row>
+    <row r="249">
+      <c r="E249" s="2" t="n"/>
+    </row>
+    <row r="250">
+      <c r="E250" s="2" t="n"/>
+    </row>
+    <row r="251">
+      <c r="E251" s="2" t="n"/>
+    </row>
+    <row r="252">
+      <c r="E252" s="2" t="n"/>
+    </row>
+    <row r="253">
+      <c r="E253" s="2" t="n"/>
+    </row>
+    <row r="254">
+      <c r="E254" s="2" t="n"/>
+    </row>
+    <row r="255">
+      <c r="E255" s="2" t="n"/>
+    </row>
+    <row r="256">
+      <c r="E256" s="2" t="n"/>
+    </row>
+    <row r="257">
+      <c r="E257" s="2" t="n"/>
+    </row>
+    <row r="258">
+      <c r="E258" s="2" t="n"/>
+    </row>
+    <row r="259">
+      <c r="E259" s="2" t="n"/>
+    </row>
+    <row r="260">
+      <c r="E260" s="2" t="n"/>
+    </row>
+    <row r="261">
+      <c r="E261" s="2" t="n"/>
+    </row>
+    <row r="262">
+      <c r="E262" s="2" t="n"/>
+    </row>
+    <row r="263">
+      <c r="E263" s="2" t="n"/>
+    </row>
+    <row r="264">
+      <c r="E264" s="2" t="n"/>
+    </row>
+    <row r="265">
+      <c r="E265" s="2" t="n"/>
+    </row>
+    <row r="266">
+      <c r="E266" s="2" t="n"/>
+    </row>
+    <row r="267">
+      <c r="E267" s="2" t="n"/>
+    </row>
+    <row r="268">
+      <c r="E268" s="2" t="n"/>
+    </row>
+    <row r="269">
+      <c r="E269" s="2" t="n"/>
+    </row>
+    <row r="270">
+      <c r="E270" s="2" t="n"/>
+    </row>
+    <row r="271">
+      <c r="E271" s="2" t="n"/>
+    </row>
+    <row r="272">
+      <c r="E272" s="2" t="n"/>
+    </row>
+    <row r="273">
+      <c r="E273" s="2" t="n"/>
+    </row>
+    <row r="274">
+      <c r="E274" s="2" t="n"/>
+    </row>
+    <row r="275">
+      <c r="E275" s="2" t="n"/>
+    </row>
+    <row r="276">
+      <c r="E276" s="2" t="n"/>
+    </row>
+    <row r="277">
+      <c r="E277" s="2" t="n"/>
+    </row>
+    <row r="278">
+      <c r="E278" s="2" t="n"/>
+    </row>
+    <row r="279">
+      <c r="E279" s="2" t="n"/>
+    </row>
+    <row r="280">
+      <c r="E280" s="2" t="n"/>
+    </row>
+    <row r="281">
+      <c r="E281" s="2" t="n"/>
+    </row>
+    <row r="282">
+      <c r="E282" s="2" t="n"/>
+    </row>
+    <row r="283">
+      <c r="E283" s="2" t="n"/>
+    </row>
+    <row r="284">
+      <c r="E284" s="2" t="n"/>
+    </row>
+    <row r="285">
+      <c r="E285" s="2" t="n"/>
+    </row>
+    <row r="286">
+      <c r="E286" s="2" t="n"/>
+    </row>
+    <row r="287">
+      <c r="E287" s="2" t="n"/>
+    </row>
+    <row r="288">
+      <c r="E288" s="2" t="n"/>
+    </row>
+    <row r="289">
+      <c r="E289" s="2" t="n"/>
+    </row>
+    <row r="290">
+      <c r="E290" s="2" t="n"/>
+    </row>
+    <row r="291">
+      <c r="E291" s="2" t="n"/>
+    </row>
+    <row r="292">
+      <c r="E292" s="2" t="n"/>
+    </row>
+    <row r="293">
+      <c r="E293" s="2" t="n"/>
+    </row>
+    <row r="294">
+      <c r="E294" s="2" t="n"/>
+    </row>
+    <row r="295">
+      <c r="E295" s="2" t="n"/>
+    </row>
+    <row r="296">
+      <c r="E296" s="2" t="n"/>
+    </row>
+    <row r="297">
+      <c r="E297" s="2" t="n"/>
+    </row>
+    <row r="298">
+      <c r="E298" s="2" t="n"/>
+    </row>
+    <row r="299">
+      <c r="E299" s="2" t="n"/>
+    </row>
+    <row r="300">
+      <c r="E300" s="2" t="n"/>
+    </row>
+    <row r="301">
+      <c r="E301" s="2" t="n"/>
+    </row>
+    <row r="302">
+      <c r="E302" s="2" t="n"/>
+    </row>
+    <row r="303">
+      <c r="E303" s="2" t="n"/>
+    </row>
+    <row r="304">
+      <c r="E304" s="2" t="n"/>
+    </row>
+    <row r="305">
+      <c r="E305" s="2" t="n"/>
+    </row>
+    <row r="306">
+      <c r="E306" s="2" t="n"/>
+    </row>
+    <row r="307">
+      <c r="E307" s="2" t="n"/>
+    </row>
+    <row r="308">
+      <c r="E308" s="2" t="n"/>
+    </row>
+    <row r="309">
+      <c r="E309" s="2" t="n"/>
+    </row>
+    <row r="310">
+      <c r="E310" s="2" t="n"/>
+    </row>
+    <row r="311">
+      <c r="E311" s="2" t="n"/>
+    </row>
+    <row r="312">
+      <c r="E312" s="2" t="n"/>
+    </row>
+    <row r="313">
+      <c r="E313" s="2" t="n"/>
+    </row>
+    <row r="314">
+      <c r="E314" s="2" t="n"/>
+    </row>
+    <row r="315">
+      <c r="E315" s="2" t="n"/>
+    </row>
+    <row r="316">
+      <c r="E316" s="2" t="n"/>
+    </row>
+    <row r="317">
+      <c r="E317" s="2" t="n"/>
+    </row>
+    <row r="318">
+      <c r="E318" s="2" t="n"/>
+    </row>
+    <row r="319">
+      <c r="E319" s="2" t="n"/>
+    </row>
+    <row r="320">
+      <c r="E320" s="2" t="n"/>
+    </row>
+    <row r="321">
+      <c r="E321" s="2" t="n"/>
+    </row>
+    <row r="322">
+      <c r="E322" s="2" t="n"/>
+    </row>
+    <row r="323">
+      <c r="E323" s="2" t="n"/>
+    </row>
+    <row r="324">
+      <c r="E324" s="2" t="n"/>
+    </row>
+    <row r="325">
+      <c r="E325" s="2" t="n"/>
+    </row>
+    <row r="326">
+      <c r="E326" s="2" t="n"/>
+    </row>
+    <row r="327">
+      <c r="E327" s="2" t="n"/>
+    </row>
+    <row r="328">
+      <c r="E328" s="2" t="n"/>
+    </row>
+    <row r="329">
+      <c r="E329" s="2" t="n"/>
+    </row>
+    <row r="330">
+      <c r="E330" s="2" t="n"/>
+    </row>
+    <row r="331">
+      <c r="E331" s="2" t="n"/>
+    </row>
+    <row r="332">
+      <c r="E332" s="2" t="n"/>
+    </row>
+    <row r="333">
+      <c r="E333" s="2" t="n"/>
+    </row>
+    <row r="334">
+      <c r="E334" s="2" t="n"/>
+    </row>
+    <row r="335">
+      <c r="E335" s="2" t="n"/>
+    </row>
+    <row r="336">
+      <c r="E336" s="2" t="n"/>
+    </row>
+    <row r="337">
+      <c r="E337" s="2" t="n"/>
+    </row>
+    <row r="338">
+      <c r="E338" s="2" t="n"/>
+    </row>
+    <row r="339">
+      <c r="E339" s="2" t="n"/>
+    </row>
+    <row r="340">
+      <c r="E340" s="2" t="n"/>
+    </row>
+    <row r="341">
+      <c r="E341" s="2" t="n"/>
+    </row>
+    <row r="342">
+      <c r="E342" s="2" t="n"/>
+    </row>
+    <row r="343">
+      <c r="E343" s="2" t="n"/>
+    </row>
+    <row r="344">
+      <c r="E344" s="2" t="n"/>
+    </row>
+    <row r="345">
+      <c r="E345" s="2" t="n"/>
+    </row>
+    <row r="346">
+      <c r="E346" s="2" t="n"/>
+    </row>
+    <row r="347">
+      <c r="E347" s="2" t="n"/>
+    </row>
+    <row r="348">
+      <c r="E348" s="2" t="n"/>
+    </row>
+    <row r="349">
+      <c r="E349" s="2" t="n"/>
+    </row>
+    <row r="350">
+      <c r="E350" s="2" t="n"/>
+    </row>
+    <row r="351">
+      <c r="E351" s="2" t="n"/>
+    </row>
+    <row r="352">
+      <c r="E352" s="2" t="n"/>
+    </row>
+    <row r="353">
+      <c r="E353" s="2" t="n"/>
+    </row>
+    <row r="354">
+      <c r="E354" s="2" t="n"/>
+    </row>
+    <row r="355">
+      <c r="E355" s="2" t="n"/>
+    </row>
+    <row r="356">
+      <c r="E356" s="2" t="n"/>
+    </row>
+    <row r="357">
+      <c r="E357" s="2" t="n"/>
+    </row>
+    <row r="358">
+      <c r="E358" s="2" t="n"/>
+    </row>
+    <row r="359">
+      <c r="E359" s="2" t="n"/>
+    </row>
+    <row r="360">
+      <c r="E360" s="2" t="n"/>
+    </row>
+    <row r="361">
+      <c r="E361" s="2" t="n"/>
+    </row>
+    <row r="362">
+      <c r="E362" s="2" t="n"/>
+    </row>
+    <row r="363">
+      <c r="E363" s="2" t="n"/>
+    </row>
+    <row r="364">
+      <c r="E364" s="2" t="n"/>
+    </row>
+    <row r="365">
+      <c r="E365" s="2" t="n"/>
+    </row>
+    <row r="366">
+      <c r="E366" s="2" t="n"/>
+    </row>
+    <row r="367">
+      <c r="E367" s="2" t="n"/>
+    </row>
+    <row r="368">
+      <c r="E368" s="2" t="n"/>
+    </row>
+    <row r="369">
+      <c r="E369" s="2" t="n"/>
+    </row>
+    <row r="370">
+      <c r="E370" s="2" t="n"/>
+    </row>
+    <row r="371">
+      <c r="E371" s="2" t="n"/>
+    </row>
+    <row r="372">
+      <c r="E372" s="2" t="n"/>
+    </row>
+    <row r="373">
+      <c r="E373" s="2" t="n"/>
+    </row>
+    <row r="374">
+      <c r="E374" s="2" t="n"/>
+    </row>
+    <row r="375">
+      <c r="E375" s="2" t="n"/>
+    </row>
+    <row r="376">
+      <c r="E376" s="2" t="n"/>
+    </row>
+    <row r="377">
+      <c r="E377" s="2" t="n"/>
+    </row>
+    <row r="378">
+      <c r="E378" s="2" t="n"/>
+    </row>
+    <row r="379">
+      <c r="E379" s="2" t="n"/>
+    </row>
+    <row r="380">
+      <c r="E380" s="2" t="n"/>
+    </row>
+    <row r="381">
+      <c r="E381" s="2" t="n"/>
+    </row>
+    <row r="382">
+      <c r="E382" s="2" t="n"/>
+    </row>
+    <row r="383">
+      <c r="E383" s="2" t="n"/>
+    </row>
+    <row r="384">
+      <c r="E384" s="2" t="n"/>
+    </row>
+    <row r="385">
+      <c r="E385" s="2" t="n"/>
+    </row>
+    <row r="386">
+      <c r="E386" s="2" t="n"/>
+    </row>
+    <row r="387">
+      <c r="E387" s="2" t="n"/>
+    </row>
+    <row r="388">
+      <c r="E388" s="2" t="n"/>
+    </row>
+    <row r="389">
+      <c r="E389" s="2" t="n"/>
+    </row>
+    <row r="390">
+      <c r="E390" s="2" t="n"/>
+    </row>
+    <row r="391">
+      <c r="E391" s="2" t="n"/>
+    </row>
+    <row r="392">
+      <c r="E392" s="2" t="n"/>
+    </row>
+    <row r="393">
+      <c r="E393" s="2" t="n"/>
+    </row>
+    <row r="394">
+      <c r="E394" s="2" t="n"/>
+    </row>
+    <row r="395">
+      <c r="E395" s="2" t="n"/>
+    </row>
+    <row r="396">
+      <c r="E396" s="2" t="n"/>
+    </row>
+    <row r="397">
+      <c r="E397" s="2" t="n"/>
+    </row>
+    <row r="398">
+      <c r="E398" s="2" t="n"/>
+    </row>
+    <row r="399">
+      <c r="E399" s="2" t="n"/>
+    </row>
+    <row r="400">
+      <c r="E400" s="2" t="n"/>
+    </row>
+    <row r="401">
+      <c r="E401" s="2" t="n"/>
+    </row>
+    <row r="402">
+      <c r="E402" s="2" t="n"/>
+    </row>
+    <row r="403">
+      <c r="E403" s="2" t="n"/>
+    </row>
+    <row r="404">
+      <c r="E404" s="2" t="n"/>
+    </row>
+    <row r="405">
+      <c r="E405" s="2" t="n"/>
+    </row>
+    <row r="406">
+      <c r="E406" s="2" t="n"/>
+    </row>
+    <row r="407">
+      <c r="E407" s="2" t="n"/>
+    </row>
+    <row r="408">
+      <c r="E408" s="2" t="n"/>
+    </row>
+    <row r="409">
+      <c r="E409" s="2" t="n"/>
+    </row>
+    <row r="410">
+      <c r="E410" s="2" t="n"/>
+    </row>
+    <row r="411">
+      <c r="E411" s="2" t="n"/>
+    </row>
+    <row r="412">
+      <c r="E412" s="2" t="n"/>
+    </row>
+    <row r="413">
+      <c r="E413" s="2" t="n"/>
+    </row>
+    <row r="414">
+      <c r="E414" s="2" t="n"/>
+    </row>
+    <row r="415">
+      <c r="E415" s="2" t="n"/>
+    </row>
+    <row r="416">
+      <c r="E416" s="2" t="n"/>
+    </row>
+    <row r="417">
+      <c r="E417" s="2" t="n"/>
+    </row>
+    <row r="418">
+      <c r="E418" s="2" t="n"/>
+    </row>
+    <row r="419">
+      <c r="E419" s="2" t="n"/>
+    </row>
+    <row r="420">
+      <c r="E420" s="2" t="n"/>
+    </row>
+    <row r="421">
+      <c r="E421" s="2" t="n"/>
+    </row>
+    <row r="422">
+      <c r="E422" s="2" t="n"/>
+    </row>
+    <row r="423">
+      <c r="E423" s="2" t="n"/>
+    </row>
+    <row r="424">
+      <c r="E424" s="2" t="n"/>
+    </row>
+    <row r="425">
+      <c r="E425" s="2" t="n"/>
+    </row>
+    <row r="426">
+      <c r="E426" s="2" t="n"/>
+    </row>
+    <row r="427">
+      <c r="E427" s="2" t="n"/>
+    </row>
+    <row r="428">
+      <c r="E428" s="2" t="n"/>
+    </row>
+    <row r="429">
+      <c r="E429" s="2" t="n"/>
+    </row>
+    <row r="430">
+      <c r="E430" s="2" t="n"/>
+    </row>
+    <row r="431">
+      <c r="E431" s="2" t="n"/>
+    </row>
+    <row r="432">
+      <c r="E432" s="2" t="n"/>
+    </row>
+    <row r="433">
+      <c r="E433" s="2" t="n"/>
+    </row>
+    <row r="434">
+      <c r="E434" s="2" t="n"/>
+    </row>
+    <row r="435">
+      <c r="E435" s="2" t="n"/>
+    </row>
+    <row r="436">
+      <c r="E436" s="2" t="n"/>
+    </row>
+    <row r="437">
+      <c r="E437" s="2" t="n"/>
+    </row>
+    <row r="438">
+      <c r="E438" s="2" t="n"/>
+    </row>
+    <row r="439">
+      <c r="E439" s="2" t="n"/>
+    </row>
+    <row r="440">
+      <c r="E440" s="2" t="n"/>
+    </row>
+    <row r="441">
+      <c r="E441" s="2" t="n"/>
+    </row>
+    <row r="442">
+      <c r="E442" s="2" t="n"/>
+    </row>
+    <row r="443">
+      <c r="E443" s="2" t="n"/>
+    </row>
+    <row r="444">
+      <c r="E444" s="2" t="n"/>
+    </row>
+    <row r="445">
+      <c r="E445" s="2" t="n"/>
+    </row>
+    <row r="446">
+      <c r="E446" s="2" t="n"/>
+    </row>
+    <row r="447">
+      <c r="E447" s="2" t="n"/>
+    </row>
+    <row r="448">
+      <c r="E448" s="2" t="n"/>
+    </row>
+    <row r="449">
+      <c r="E449" s="2" t="n"/>
+    </row>
+    <row r="450">
+      <c r="E450" s="2" t="n"/>
+    </row>
+    <row r="451">
+      <c r="E451" s="2" t="n"/>
+    </row>
+    <row r="452">
+      <c r="E452" s="2" t="n"/>
+    </row>
+    <row r="453">
+      <c r="E453" s="2" t="n"/>
+    </row>
+    <row r="454">
+      <c r="E454" s="2" t="n"/>
+    </row>
+    <row r="455">
+      <c r="E455" s="2" t="n"/>
+    </row>
+    <row r="456">
+      <c r="E456" s="2" t="n"/>
+    </row>
+    <row r="457">
+      <c r="E457" s="2" t="n"/>
+    </row>
+    <row r="458">
+      <c r="E458" s="2" t="n"/>
+    </row>
+    <row r="459">
+      <c r="E459" s="2" t="n"/>
+    </row>
+    <row r="460">
+      <c r="E460" s="2" t="n"/>
+    </row>
+    <row r="461">
+      <c r="E461" s="2" t="n"/>
+    </row>
+    <row r="462">
+      <c r="E462" s="2" t="n"/>
+    </row>
+    <row r="463">
+      <c r="E463" s="2" t="n"/>
+    </row>
+    <row r="464">
+      <c r="E464" s="2" t="n"/>
+    </row>
+    <row r="465">
+      <c r="E465" s="2" t="n"/>
+    </row>
+    <row r="466">
+      <c r="E466" s="2" t="n"/>
+    </row>
+    <row r="467">
+      <c r="E467" s="2" t="n"/>
+    </row>
+    <row r="468">
+      <c r="E468" s="2" t="n"/>
+    </row>
+    <row r="469">
+      <c r="E469" s="2" t="n"/>
+    </row>
+    <row r="470">
+      <c r="E470" s="2" t="n"/>
+    </row>
+    <row r="471">
+      <c r="E471" s="2" t="n"/>
+    </row>
+    <row r="472">
+      <c r="E472" s="2" t="n"/>
+    </row>
+    <row r="473">
+      <c r="E473" s="2" t="n"/>
+    </row>
+    <row r="474">
+      <c r="E474" s="2" t="n"/>
+    </row>
+    <row r="475">
+      <c r="E475" s="2" t="n"/>
+    </row>
+    <row r="476">
+      <c r="E476" s="2" t="n"/>
+    </row>
+    <row r="477">
+      <c r="E477" s="2" t="n"/>
+    </row>
+    <row r="478">
+      <c r="E478" s="2" t="n"/>
+    </row>
+    <row r="479">
+      <c r="E479" s="2" t="n"/>
+    </row>
+    <row r="480">
+      <c r="E480" s="2" t="n"/>
+    </row>
+    <row r="481">
+      <c r="E481" s="2" t="n"/>
+    </row>
+    <row r="482">
+      <c r="E482" s="2" t="n"/>
+    </row>
+    <row r="483">
+      <c r="E483" s="2" t="n"/>
+    </row>
+    <row r="484">
+      <c r="E484" s="2" t="n"/>
+    </row>
+    <row r="485">
+      <c r="E485" s="2" t="n"/>
+    </row>
+    <row r="486">
+      <c r="E486" s="2" t="n"/>
+    </row>
+    <row r="487">
+      <c r="E487" s="2" t="n"/>
+    </row>
+    <row r="488">
+      <c r="E488" s="2" t="n"/>
+    </row>
+    <row r="489">
+      <c r="E489" s="2" t="n"/>
+    </row>
+    <row r="490">
+      <c r="E490" s="2" t="n"/>
+    </row>
+    <row r="491">
+      <c r="E491" s="2" t="n"/>
+    </row>
+    <row r="492">
+      <c r="E492" s="2" t="n"/>
+    </row>
+    <row r="493">
+      <c r="E493" s="2" t="n"/>
+    </row>
+    <row r="494">
+      <c r="E494" s="2" t="n"/>
+    </row>
+    <row r="495">
+      <c r="E495" s="2" t="n"/>
+    </row>
+    <row r="496">
+      <c r="E496" s="2" t="n"/>
+    </row>
+    <row r="497">
+      <c r="E497" s="2" t="n"/>
+    </row>
+    <row r="498">
+      <c r="E498" s="2" t="n"/>
+    </row>
+    <row r="499">
+      <c r="E499" s="2" t="n"/>
+    </row>
+    <row r="500">
+      <c r="E500" s="2" t="n"/>
+    </row>
+    <row r="501">
+      <c r="E501" s="2" t="n"/>
+    </row>
+    <row r="502">
+      <c r="E502" s="2" t="n"/>
+    </row>
+    <row r="503">
+      <c r="E503" s="2" t="n"/>
+    </row>
+    <row r="504">
+      <c r="E504" s="2" t="n"/>
+    </row>
+    <row r="505">
+      <c r="E505" s="2" t="n"/>
+    </row>
+    <row r="506">
+      <c r="E506" s="2" t="n"/>
+    </row>
+    <row r="507">
+      <c r="E507" s="2" t="n"/>
+    </row>
+    <row r="508">
+      <c r="E508" s="2" t="n"/>
+    </row>
+    <row r="509">
+      <c r="E509" s="2" t="n"/>
+    </row>
+    <row r="510">
+      <c r="E510" s="2" t="n"/>
+    </row>
+    <row r="511">
+      <c r="E511" s="2" t="n"/>
+    </row>
+    <row r="512">
+      <c r="E512" s="2" t="n"/>
+    </row>
+    <row r="513">
+      <c r="E513" s="2" t="n"/>
+    </row>
+    <row r="514">
+      <c r="E514" s="2" t="n"/>
+    </row>
+    <row r="515">
+      <c r="E515" s="2" t="n"/>
+    </row>
+    <row r="516">
+      <c r="E516" s="2" t="n"/>
+    </row>
+    <row r="517">
+      <c r="E517" s="2" t="n"/>
+    </row>
+    <row r="518">
+      <c r="E518" s="2" t="n"/>
+    </row>
+    <row r="519">
+      <c r="E519" s="2" t="n"/>
+    </row>
+    <row r="520">
+      <c r="E520" s="2" t="n"/>
+    </row>
+    <row r="521">
+      <c r="E521" s="2" t="n"/>
+    </row>
+    <row r="522">
+      <c r="E522" s="2" t="n"/>
+    </row>
+    <row r="523">
+      <c r="E523" s="2" t="n"/>
+    </row>
+    <row r="524">
+      <c r="E524" s="2" t="n"/>
+    </row>
+    <row r="525">
+      <c r="E525" s="2" t="n"/>
+    </row>
+    <row r="526">
+      <c r="E526" s="2" t="n"/>
+    </row>
+    <row r="527">
+      <c r="E527" s="2" t="n"/>
+    </row>
+    <row r="528">
+      <c r="E528" s="2" t="n"/>
+    </row>
+    <row r="529">
+      <c r="E529" s="2" t="n"/>
+    </row>
+    <row r="530">
+      <c r="E530" s="2" t="n"/>
+    </row>
+    <row r="531">
+      <c r="E531" s="2" t="n"/>
+    </row>
+    <row r="532">
+      <c r="E532" s="2" t="n"/>
+    </row>
+    <row r="533">
+      <c r="E533" s="2" t="n"/>
+    </row>
+    <row r="534">
+      <c r="E534" s="2" t="n"/>
+    </row>
+    <row r="535">
+      <c r="E535" s="2" t="n"/>
+    </row>
+    <row r="536">
+      <c r="E536" s="2" t="n"/>
+    </row>
+    <row r="537">
+      <c r="E537" s="2" t="n"/>
+    </row>
+    <row r="538">
+      <c r="E538" s="2" t="n"/>
+    </row>
+    <row r="539">
+      <c r="E539" s="2" t="n"/>
+    </row>
+    <row r="540">
+      <c r="E540" s="2" t="n"/>
+    </row>
+    <row r="541">
+      <c r="E541" s="2" t="n"/>
+    </row>
+    <row r="542">
+      <c r="E542" s="2" t="n"/>
+    </row>
+    <row r="543">
+      <c r="E543" s="2" t="n"/>
+    </row>
+    <row r="544">
+      <c r="E544" s="2" t="n"/>
+    </row>
+    <row r="545">
+      <c r="E545" s="2" t="n"/>
+    </row>
+    <row r="546">
+      <c r="E546" s="2" t="n"/>
+    </row>
+    <row r="547">
+      <c r="E547" s="2" t="n"/>
+    </row>
+    <row r="548">
+      <c r="E548" s="2" t="n"/>
+    </row>
+    <row r="549">
+      <c r="E549" s="2" t="n"/>
+    </row>
+    <row r="550">
+      <c r="E550" s="2" t="n"/>
+    </row>
+    <row r="551">
+      <c r="E551" s="2" t="n"/>
+    </row>
+    <row r="552">
+      <c r="E552" s="2" t="n"/>
+    </row>
+    <row r="553">
+      <c r="E553" s="2" t="n"/>
+    </row>
+    <row r="554">
+      <c r="E554" s="2" t="n"/>
+    </row>
+    <row r="555">
+      <c r="E555" s="2" t="n"/>
+    </row>
+    <row r="556">
+      <c r="E556" s="2" t="n"/>
+    </row>
+    <row r="557">
+      <c r="E557" s="2" t="n"/>
+    </row>
+    <row r="558">
+      <c r="E558" s="2" t="n"/>
+    </row>
+    <row r="559">
+      <c r="E559" s="2" t="n"/>
+    </row>
+    <row r="560">
+      <c r="E560" s="2" t="n"/>
+    </row>
+    <row r="561">
+      <c r="E561" s="2" t="n"/>
+    </row>
+    <row r="562">
+      <c r="E562" s="2" t="n"/>
+    </row>
+    <row r="563">
+      <c r="E563" s="2" t="n"/>
+    </row>
+    <row r="564">
+      <c r="E564" s="2" t="n"/>
+    </row>
+    <row r="565">
+      <c r="E565" s="2" t="n"/>
+    </row>
+    <row r="566">
+      <c r="E566" s="2" t="n"/>
+    </row>
+    <row r="567">
+      <c r="E567" s="2" t="n"/>
+    </row>
+    <row r="568">
+      <c r="E568" s="2" t="n"/>
+    </row>
+    <row r="569">
+      <c r="E569" s="2" t="n"/>
+    </row>
+    <row r="570">
+      <c r="E570" s="2" t="n"/>
+    </row>
+    <row r="571">
+      <c r="E571" s="2" t="n"/>
+    </row>
+    <row r="572">
+      <c r="E572" s="2" t="n"/>
+    </row>
+    <row r="573">
+      <c r="E573" s="2" t="n"/>
+    </row>
+    <row r="574">
+      <c r="E574" s="2" t="n"/>
+    </row>
+    <row r="575">
+      <c r="E575" s="2" t="n"/>
+    </row>
+    <row r="576">
+      <c r="E576" s="2" t="n"/>
+    </row>
+    <row r="577">
+      <c r="E577" s="2" t="n"/>
+    </row>
+    <row r="578">
+      <c r="E578" s="2" t="n"/>
+    </row>
+    <row r="579">
+      <c r="E579" s="2" t="n"/>
+    </row>
+    <row r="580">
+      <c r="E580" s="2" t="n"/>
+    </row>
+    <row r="581">
+      <c r="E581" s="2" t="n"/>
+    </row>
+    <row r="582">
+      <c r="E582" s="2" t="n"/>
+    </row>
+    <row r="583">
+      <c r="E583" s="2" t="n"/>
+    </row>
+    <row r="584">
+      <c r="E584" s="2" t="n"/>
+    </row>
+    <row r="585">
+      <c r="E585" s="2" t="n"/>
+    </row>
+    <row r="586">
+      <c r="E586" s="2" t="n"/>
+    </row>
+    <row r="587">
+      <c r="E587" s="2" t="n"/>
+    </row>
+    <row r="588">
+      <c r="E588" s="2" t="n"/>
+    </row>
+    <row r="589">
+      <c r="E589" s="2" t="n"/>
+    </row>
+    <row r="590">
+      <c r="E590" s="2" t="n"/>
+    </row>
+    <row r="591">
+      <c r="E591" s="2" t="n"/>
+    </row>
+    <row r="592">
+      <c r="E592" s="2" t="n"/>
+    </row>
+    <row r="593">
+      <c r="E593" s="2" t="n"/>
+    </row>
+    <row r="594">
+      <c r="E594" s="2" t="n"/>
+    </row>
+    <row r="595">
+      <c r="E595" s="2" t="n"/>
+    </row>
+    <row r="596">
+      <c r="E596" s="2" t="n"/>
+    </row>
+    <row r="597">
+      <c r="E597" s="2" t="n"/>
+    </row>
+    <row r="598">
+      <c r="E598" s="2" t="n"/>
+    </row>
+    <row r="599">
+      <c r="E599" s="2" t="n"/>
+    </row>
+    <row r="600">
+      <c r="E600" s="2" t="n"/>
+    </row>
+    <row r="601">
+      <c r="E601" s="2" t="n"/>
+    </row>
+    <row r="602">
+      <c r="E602" s="2" t="n"/>
+    </row>
+    <row r="603">
+      <c r="E603" s="2" t="n"/>
+    </row>
+    <row r="604">
+      <c r="E604" s="2" t="n"/>
+    </row>
+    <row r="605">
+      <c r="E605" s="2" t="n"/>
+    </row>
+    <row r="606">
+      <c r="E606" s="2" t="n"/>
+    </row>
+    <row r="607">
+      <c r="E607" s="2" t="n"/>
+    </row>
+    <row r="608">
+      <c r="E608" s="2" t="n"/>
+    </row>
+    <row r="609">
+      <c r="E609" s="2" t="n"/>
+    </row>
+    <row r="610">
+      <c r="E610" s="2" t="n"/>
+    </row>
+    <row r="611">
+      <c r="E611" s="2" t="n"/>
+    </row>
+    <row r="612">
+      <c r="E612" s="2" t="n"/>
+    </row>
+    <row r="613">
+      <c r="E613" s="2" t="n"/>
+    </row>
+    <row r="614">
+      <c r="E614" s="2" t="n"/>
+    </row>
+    <row r="615">
+      <c r="E615" s="2" t="n"/>
+    </row>
+    <row r="616">
+      <c r="E616" s="2" t="n"/>
+    </row>
+    <row r="617">
+      <c r="E617" s="2" t="n"/>
+    </row>
+    <row r="618">
+      <c r="E618" s="2" t="n"/>
+    </row>
+    <row r="619">
+      <c r="E619" s="2" t="n"/>
+    </row>
+    <row r="620">
+      <c r="E620" s="2" t="n"/>
+    </row>
+    <row r="621">
+      <c r="E621" s="2" t="n"/>
+    </row>
+    <row r="622">
+      <c r="E622" s="2" t="n"/>
+    </row>
+    <row r="623">
+      <c r="E623" s="2" t="n"/>
+    </row>
+    <row r="624">
+      <c r="E624" s="2" t="n"/>
+    </row>
+    <row r="625">
+      <c r="E625" s="2" t="n"/>
+    </row>
+    <row r="626">
+      <c r="E626" s="2" t="n"/>
+    </row>
+    <row r="627">
+      <c r="E627" s="2" t="n"/>
+    </row>
+    <row r="628">
+      <c r="E628" s="2" t="n"/>
+    </row>
+    <row r="629">
+      <c r="E629" s="2" t="n"/>
+    </row>
+    <row r="630">
+      <c r="E630" s="2" t="n"/>
+    </row>
+    <row r="631">
+      <c r="E631" s="2" t="n"/>
+    </row>
+    <row r="632">
+      <c r="E632" s="2" t="n"/>
+    </row>
+    <row r="633">
+      <c r="E633" s="2" t="n"/>
+    </row>
+    <row r="634">
+      <c r="E634" s="2" t="n"/>
+    </row>
+    <row r="635">
+      <c r="E635" s="2" t="n"/>
+    </row>
+    <row r="636">
+      <c r="E636" s="2" t="n"/>
+    </row>
+    <row r="637">
+      <c r="E637" s="2" t="n"/>
+    </row>
+    <row r="638">
+      <c r="E638" s="2" t="n"/>
+    </row>
+    <row r="639">
+      <c r="E639" s="2" t="n"/>
+    </row>
+    <row r="640">
+      <c r="E640" s="2" t="n"/>
+    </row>
+    <row r="641">
+      <c r="E641" s="2" t="n"/>
+    </row>
+    <row r="642">
+      <c r="E642" s="2" t="n"/>
+    </row>
+    <row r="643">
+      <c r="E643" s="2" t="n"/>
+    </row>
+    <row r="644">
+      <c r="E644" s="2" t="n"/>
+    </row>
+    <row r="645">
+      <c r="E645" s="2" t="n"/>
+    </row>
+    <row r="646">
+      <c r="E646" s="2" t="n"/>
+    </row>
+    <row r="647">
+      <c r="E647" s="2" t="n"/>
+    </row>
+    <row r="648">
+      <c r="E648" s="2" t="n"/>
+    </row>
+    <row r="649">
+      <c r="E649" s="2" t="n"/>
+    </row>
+    <row r="650">
+      <c r="E650" s="2" t="n"/>
+    </row>
+    <row r="651">
+      <c r="E651" s="2" t="n"/>
+    </row>
+    <row r="652">
+      <c r="E652" s="2" t="n"/>
+    </row>
+    <row r="653">
+      <c r="E653" s="2" t="n"/>
+    </row>
+    <row r="654">
+      <c r="E654" s="2" t="n"/>
+    </row>
+    <row r="655">
+      <c r="E655" s="2" t="n"/>
+    </row>
+    <row r="656">
+      <c r="E656" s="2" t="n"/>
+    </row>
+    <row r="657">
+      <c r="E657" s="2" t="n"/>
+    </row>
+    <row r="658">
+      <c r="E658" s="2" t="n"/>
+    </row>
+    <row r="659">
+      <c r="E659" s="2" t="n"/>
+    </row>
+    <row r="660">
+      <c r="E660" s="2" t="n"/>
+    </row>
+    <row r="661">
+      <c r="E661" s="2" t="n"/>
+    </row>
+    <row r="662">
+      <c r="E662" s="2" t="n"/>
+    </row>
+    <row r="663">
+      <c r="E663" s="2" t="n"/>
+    </row>
+    <row r="664">
+      <c r="E664" s="2" t="n"/>
+    </row>
+    <row r="665">
+      <c r="E665" s="2" t="n"/>
+    </row>
+    <row r="666">
+      <c r="E666" s="2" t="n"/>
+    </row>
+    <row r="667">
+      <c r="E667" s="2" t="n"/>
+    </row>
+    <row r="668">
+      <c r="E668" s="2" t="n"/>
+    </row>
+    <row r="669">
+      <c r="E669" s="2" t="n"/>
+    </row>
+    <row r="670">
+      <c r="E670" s="2" t="n"/>
+    </row>
+    <row r="671">
+      <c r="E671" s="2" t="n"/>
+    </row>
+    <row r="672">
+      <c r="E672" s="2" t="n"/>
+    </row>
+    <row r="673">
+      <c r="E673" s="2" t="n"/>
+    </row>
+    <row r="674">
+      <c r="E674" s="2" t="n"/>
+    </row>
+    <row r="675">
+      <c r="E675" s="2" t="n"/>
+    </row>
+    <row r="676">
+      <c r="E676" s="2" t="n"/>
+    </row>
+    <row r="677">
+      <c r="E677" s="2" t="n"/>
+    </row>
+    <row r="678">
+      <c r="E678" s="2" t="n"/>
+    </row>
+    <row r="679">
+      <c r="E679" s="2" t="n"/>
+    </row>
+    <row r="680">
+      <c r="E680" s="2" t="n"/>
+    </row>
+    <row r="681">
+      <c r="E681" s="2" t="n"/>
+    </row>
+    <row r="682">
+      <c r="E682" s="2" t="n"/>
+    </row>
+    <row r="683">
+      <c r="E683" s="2" t="n"/>
+    </row>
+    <row r="684">
+      <c r="E684" s="2" t="n"/>
+    </row>
+    <row r="685">
+      <c r="E685" s="2" t="n"/>
+    </row>
+    <row r="686">
+      <c r="E686" s="2" t="n"/>
+    </row>
+    <row r="687">
+      <c r="E687" s="2" t="n"/>
+    </row>
+    <row r="688">
+      <c r="E688" s="2" t="n"/>
+    </row>
+    <row r="689">
+      <c r="E689" s="2" t="n"/>
+    </row>
+    <row r="690">
+      <c r="E690" s="2" t="n"/>
+    </row>
+    <row r="691">
+      <c r="E691" s="2" t="n"/>
+    </row>
+    <row r="692">
+      <c r="E692" s="2" t="n"/>
+    </row>
+    <row r="693">
+      <c r="E693" s="2" t="n"/>
+    </row>
+    <row r="694">
+      <c r="E694" s="2" t="n"/>
+    </row>
+    <row r="695">
+      <c r="E695" s="2" t="n"/>
+    </row>
+    <row r="696">
+      <c r="E696" s="2" t="n"/>
+    </row>
+    <row r="697">
+      <c r="E697" s="2" t="n"/>
+    </row>
+    <row r="698">
+      <c r="E698" s="2" t="n"/>
+    </row>
+    <row r="699">
+      <c r="E699" s="2" t="n"/>
+    </row>
+    <row r="700">
+      <c r="E700" s="2" t="n"/>
+    </row>
+    <row r="701">
+      <c r="E701" s="2" t="n"/>
+    </row>
+    <row r="702">
+      <c r="E702" s="2" t="n"/>
+    </row>
+    <row r="703">
+      <c r="E703" s="2" t="n"/>
+    </row>
+    <row r="704">
+      <c r="E704" s="2" t="n"/>
+    </row>
+    <row r="705">
+      <c r="E705" s="2" t="n"/>
+    </row>
+    <row r="706">
+      <c r="E706" s="2" t="n"/>
+    </row>
+    <row r="707">
+      <c r="E707" s="2" t="n"/>
+    </row>
+    <row r="708">
+      <c r="E708" s="2" t="n"/>
+    </row>
+    <row r="709">
+      <c r="E709" s="2" t="n"/>
+    </row>
+    <row r="710">
+      <c r="E710" s="2" t="n"/>
+    </row>
+    <row r="711">
+      <c r="E711" s="2" t="n"/>
+    </row>
+    <row r="712">
+      <c r="E712" s="2" t="n"/>
+    </row>
+    <row r="713">
+      <c r="E713" s="2" t="n"/>
+    </row>
+    <row r="714">
+      <c r="E714" s="2" t="n"/>
+    </row>
+    <row r="715">
+      <c r="E715" s="2" t="n"/>
+    </row>
+    <row r="716">
+      <c r="E716" s="2" t="n"/>
+    </row>
+    <row r="717">
+      <c r="E717" s="2" t="n"/>
+    </row>
+    <row r="718">
+      <c r="E718" s="2" t="n"/>
+    </row>
+    <row r="719">
+      <c r="E719" s="2" t="n"/>
+    </row>
+    <row r="720">
+      <c r="E720" s="2" t="n"/>
+    </row>
+    <row r="721">
+      <c r="E721" s="2" t="n"/>
+    </row>
+    <row r="722">
+      <c r="E722" s="2" t="n"/>
+    </row>
+    <row r="723">
+      <c r="E723" s="2" t="n"/>
+    </row>
+    <row r="724">
+      <c r="E724" s="2" t="n"/>
+    </row>
+    <row r="725">
+      <c r="E725" s="2" t="n"/>
+    </row>
+    <row r="726">
+      <c r="E726" s="2" t="n"/>
+    </row>
+    <row r="727">
+      <c r="E727" s="2" t="n"/>
+    </row>
+    <row r="728">
+      <c r="E728" s="2" t="n"/>
+    </row>
+    <row r="729">
+      <c r="E729" s="2" t="n"/>
+    </row>
+    <row r="730">
+      <c r="E730" s="2" t="n"/>
+    </row>
+    <row r="731">
+      <c r="E731" s="2" t="n"/>
+    </row>
+    <row r="732">
+      <c r="E732" s="2" t="n"/>
+    </row>
+    <row r="733">
+      <c r="E733" s="2" t="n"/>
+    </row>
+    <row r="734">
+      <c r="E734" s="2" t="n"/>
+    </row>
+    <row r="735">
+      <c r="E735" s="2" t="n"/>
+    </row>
+    <row r="736">
+      <c r="E736" s="2" t="n"/>
+    </row>
+    <row r="737">
+      <c r="E737" s="2" t="n"/>
+    </row>
+    <row r="738">
+      <c r="E738" s="2" t="n"/>
+    </row>
+    <row r="739">
+      <c r="E739" s="2" t="n"/>
+    </row>
+    <row r="740">
+      <c r="E740" s="2" t="n"/>
+    </row>
+    <row r="741">
+      <c r="E741" s="2" t="n"/>
+    </row>
+    <row r="742">
+      <c r="E742" s="2" t="n"/>
+    </row>
+    <row r="743">
+      <c r="E743" s="2" t="n"/>
+    </row>
+    <row r="744">
+      <c r="E744" s="2" t="n"/>
+    </row>
+    <row r="745">
+      <c r="E745" s="2" t="n"/>
+    </row>
+    <row r="746">
+      <c r="E746" s="2" t="n"/>
+    </row>
+    <row r="747">
+      <c r="E747" s="2" t="n"/>
+    </row>
+    <row r="748">
+      <c r="E748" s="2" t="n"/>
+    </row>
+    <row r="749">
+      <c r="E749" s="2" t="n"/>
+    </row>
+    <row r="750">
+      <c r="E750" s="2" t="n"/>
+    </row>
+    <row r="751">
+      <c r="E751" s="2" t="n"/>
+    </row>
+    <row r="752">
+      <c r="E752" s="2" t="n"/>
+    </row>
+    <row r="753">
+      <c r="E753" s="2" t="n"/>
+    </row>
+    <row r="754">
+      <c r="E754" s="2" t="n"/>
+    </row>
+    <row r="755">
+      <c r="E755" s="2" t="n"/>
+    </row>
+    <row r="756">
+      <c r="E756" s="2" t="n"/>
+    </row>
+    <row r="757">
+      <c r="E757" s="2" t="n"/>
+    </row>
+    <row r="758">
+      <c r="E758" s="2" t="n"/>
+    </row>
+    <row r="759">
+      <c r="E759" s="2" t="n"/>
+    </row>
+    <row r="760">
+      <c r="E760" s="2" t="n"/>
+    </row>
+    <row r="761">
+      <c r="E761" s="2" t="n"/>
+    </row>
+    <row r="762">
+      <c r="E762" s="2" t="n"/>
+    </row>
+    <row r="763">
+      <c r="E763" s="2" t="n"/>
+    </row>
+    <row r="764">
+      <c r="E764" s="2" t="n"/>
+    </row>
+    <row r="765">
+      <c r="E765" s="2" t="n"/>
+    </row>
+    <row r="766">
+      <c r="E766" s="2" t="n"/>
+    </row>
+    <row r="767">
+      <c r="E767" s="2" t="n"/>
+    </row>
+    <row r="768">
+      <c r="E768" s="2" t="n"/>
+    </row>
+    <row r="769">
+      <c r="E769" s="2" t="n"/>
+    </row>
+    <row r="770">
+      <c r="E770" s="2" t="n"/>
+    </row>
+    <row r="771">
+      <c r="E771" s="2" t="n"/>
+    </row>
+    <row r="772">
+      <c r="E772" s="2" t="n"/>
+    </row>
+    <row r="773">
+      <c r="E773" s="2" t="n"/>
+    </row>
+    <row r="774">
+      <c r="E774" s="2" t="n"/>
+    </row>
+    <row r="775">
+      <c r="E775" s="2" t="n"/>
+    </row>
+    <row r="776">
+      <c r="E776" s="2" t="n"/>
+    </row>
+    <row r="777">
+      <c r="E777" s="2" t="n"/>
+    </row>
+    <row r="778">
+      <c r="E778" s="2" t="n"/>
+    </row>
+    <row r="779">
+      <c r="E779" s="2" t="n"/>
+    </row>
+    <row r="780">
+      <c r="E780" s="2" t="n"/>
+    </row>
+    <row r="781">
+      <c r="E781" s="2" t="n"/>
+    </row>
+    <row r="782">
+      <c r="E782" s="2" t="n"/>
+    </row>
+    <row r="783">
+      <c r="E783" s="2" t="n"/>
+    </row>
+    <row r="784">
+      <c r="E784" s="2" t="n"/>
+    </row>
+    <row r="785">
+      <c r="E785" s="2" t="n"/>
+    </row>
+    <row r="786">
+      <c r="E786" s="2" t="n"/>
+    </row>
+    <row r="787">
+      <c r="E787" s="2" t="n"/>
+    </row>
+    <row r="788">
+      <c r="E788" s="2" t="n"/>
+    </row>
+    <row r="789">
+      <c r="E789" s="2" t="n"/>
+    </row>
+    <row r="790">
+      <c r="E790" s="2" t="n"/>
+    </row>
+    <row r="791">
+      <c r="E791" s="2" t="n"/>
+    </row>
+    <row r="792">
+      <c r="E792" s="2" t="n"/>
+    </row>
+    <row r="793">
+      <c r="E793" s="2" t="n"/>
+    </row>
+    <row r="794">
+      <c r="E794" s="2" t="n"/>
+    </row>
+    <row r="795">
+      <c r="E795" s="2" t="n"/>
+    </row>
+    <row r="796">
+      <c r="E796" s="2" t="n"/>
+    </row>
+    <row r="797">
+      <c r="E797" s="2" t="n"/>
+    </row>
+    <row r="798">
+      <c r="E798" s="2" t="n"/>
+    </row>
+    <row r="799">
+      <c r="E799" s="2" t="n"/>
+    </row>
+    <row r="800">
+      <c r="E800" s="2" t="n"/>
+    </row>
+    <row r="801">
+      <c r="E801" s="2" t="n"/>
+    </row>
+    <row r="802">
+      <c r="E802" s="2" t="n"/>
+    </row>
+    <row r="803">
+      <c r="E803" s="2" t="n"/>
+    </row>
+    <row r="804">
+      <c r="E804" s="2" t="n"/>
+    </row>
+    <row r="805">
+      <c r="E805" s="2" t="n"/>
+    </row>
+    <row r="806">
+      <c r="E806" s="2" t="n"/>
+    </row>
+    <row r="807">
+      <c r="E807" s="2" t="n"/>
+    </row>
+    <row r="808">
+      <c r="E808" s="2" t="n"/>
+    </row>
+    <row r="809">
+      <c r="E809" s="2" t="n"/>
+    </row>
+    <row r="810">
+      <c r="E810" s="2" t="n"/>
+    </row>
+    <row r="811">
+      <c r="E811" s="2" t="n"/>
+    </row>
+    <row r="812">
+      <c r="E812" s="2" t="n"/>
+    </row>
+    <row r="813">
+      <c r="E813" s="2" t="n"/>
+    </row>
+    <row r="814">
+      <c r="E814" s="2" t="n"/>
+    </row>
+    <row r="815">
+      <c r="E815" s="2" t="n"/>
+    </row>
+    <row r="816">
+      <c r="E816" s="2" t="n"/>
+    </row>
+    <row r="817">
+      <c r="E817" s="2" t="n"/>
+    </row>
+    <row r="818">
+      <c r="E818" s="2" t="n"/>
+    </row>
+    <row r="819">
+      <c r="E819" s="2" t="n"/>
+    </row>
+    <row r="820">
+      <c r="E820" s="2" t="n"/>
+    </row>
+    <row r="821">
+      <c r="E821" s="2" t="n"/>
+    </row>
+    <row r="822">
+      <c r="E822" s="2" t="n"/>
+    </row>
+    <row r="823">
+      <c r="E823" s="2" t="n"/>
+    </row>
+    <row r="824">
+      <c r="E824" s="2" t="n"/>
+    </row>
+    <row r="825">
+      <c r="E825" s="2" t="n"/>
+    </row>
+    <row r="826">
+      <c r="E826" s="2" t="n"/>
+    </row>
+    <row r="827">
+      <c r="E827" s="2" t="n"/>
+    </row>
+    <row r="828">
+      <c r="E828" s="2" t="n"/>
+    </row>
+    <row r="829">
+      <c r="E829" s="2" t="n"/>
+    </row>
+    <row r="830">
+      <c r="E830" s="2" t="n"/>
+    </row>
+    <row r="831">
+      <c r="E831" s="2" t="n"/>
+    </row>
+    <row r="832">
+      <c r="E832" s="2" t="n"/>
+    </row>
+    <row r="833">
+      <c r="E833" s="2" t="n"/>
+    </row>
+    <row r="834">
+      <c r="E834" s="2" t="n"/>
+    </row>
+    <row r="835">
+      <c r="E835" s="2" t="n"/>
+    </row>
+    <row r="836">
+      <c r="E836" s="2" t="n"/>
+    </row>
+    <row r="837">
+      <c r="E837" s="2" t="n"/>
+    </row>
+    <row r="838">
+      <c r="E838" s="2" t="n"/>
+    </row>
+    <row r="839">
+      <c r="E839" s="2" t="n"/>
+    </row>
+    <row r="840">
+      <c r="E840" s="2" t="n"/>
+    </row>
+    <row r="841">
+      <c r="E841" s="2" t="n"/>
+    </row>
+    <row r="842">
+      <c r="E842" s="2" t="n"/>
+    </row>
+    <row r="843">
+      <c r="E843" s="2" t="n"/>
+    </row>
+    <row r="844">
+      <c r="E844" s="2" t="n"/>
+    </row>
+    <row r="845">
+      <c r="E845" s="2" t="n"/>
+    </row>
+    <row r="846">
+      <c r="E846" s="2" t="n"/>
+    </row>
+    <row r="847">
+      <c r="E847" s="2" t="n"/>
+    </row>
+    <row r="848">
+      <c r="E848" s="2" t="n"/>
+    </row>
+    <row r="849">
+      <c r="E849" s="2" t="n"/>
+    </row>
+    <row r="850">
+      <c r="E850" s="2" t="n"/>
+    </row>
+    <row r="851">
+      <c r="E851" s="2" t="n"/>
+    </row>
+    <row r="852">
+      <c r="E852" s="2" t="n"/>
+    </row>
+    <row r="853">
+      <c r="E853" s="2" t="n"/>
+    </row>
+    <row r="854">
+      <c r="E854" s="2" t="n"/>
+    </row>
+    <row r="855">
+      <c r="E855" s="2" t="n"/>
+    </row>
+    <row r="856">
+      <c r="E856" s="2" t="n"/>
+    </row>
+    <row r="857">
+      <c r="E857" s="2" t="n"/>
+    </row>
+    <row r="858">
+      <c r="E858" s="2" t="n"/>
+    </row>
+    <row r="859">
+      <c r="E859" s="2" t="n"/>
+    </row>
+    <row r="860">
+      <c r="E860" s="2" t="n"/>
+    </row>
+    <row r="861">
+      <c r="E861" s="2" t="n"/>
+    </row>
+    <row r="862">
+      <c r="E862" s="2" t="n"/>
+    </row>
+    <row r="863">
+      <c r="E863" s="2" t="n"/>
+    </row>
+    <row r="864">
+      <c r="E864" s="2" t="n"/>
+    </row>
+    <row r="865">
+      <c r="E865" s="2" t="n"/>
+    </row>
+    <row r="866">
+      <c r="E866" s="2" t="n"/>
+    </row>
+    <row r="867">
+      <c r="E867" s="2" t="n"/>
+    </row>
+    <row r="868">
+      <c r="E868" s="2" t="n"/>
+    </row>
+    <row r="869">
+      <c r="E869" s="2" t="n"/>
+    </row>
+    <row r="870">
+      <c r="E870" s="2" t="n"/>
+    </row>
+    <row r="871">
+      <c r="E871" s="2" t="n"/>
+    </row>
+    <row r="872">
+      <c r="E872" s="2" t="n"/>
+    </row>
+    <row r="873">
+      <c r="E873" s="2" t="n"/>
+    </row>
+    <row r="874">
+      <c r="E874" s="2" t="n"/>
+    </row>
+    <row r="875">
+      <c r="E875" s="2" t="n"/>
+    </row>
+    <row r="876">
+      <c r="E876" s="2" t="n"/>
+    </row>
+    <row r="877">
+      <c r="E877" s="2" t="n"/>
+    </row>
+    <row r="878">
+      <c r="E878" s="2" t="n"/>
+    </row>
+    <row r="879">
+      <c r="E879" s="2" t="n"/>
+    </row>
+    <row r="880">
+      <c r="E880" s="2" t="n"/>
+    </row>
+    <row r="881">
+      <c r="E881" s="2" t="n"/>
+    </row>
+    <row r="882">
+      <c r="E882" s="2" t="n"/>
+    </row>
+    <row r="883">
+      <c r="E883" s="2" t="n"/>
+    </row>
+    <row r="884">
+      <c r="E884" s="2" t="n"/>
+    </row>
+    <row r="885">
+      <c r="E885" s="2" t="n"/>
+    </row>
+    <row r="886">
+      <c r="E886" s="2" t="n"/>
+    </row>
+    <row r="887">
+      <c r="E887" s="2" t="n"/>
+    </row>
+    <row r="888">
+      <c r="E888" s="2" t="n"/>
+    </row>
+    <row r="889">
+      <c r="E889" s="2" t="n"/>
+    </row>
+    <row r="890">
+      <c r="E890" s="2" t="n"/>
+    </row>
+    <row r="891">
+      <c r="E891" s="2" t="n"/>
+    </row>
+    <row r="892">
+      <c r="E892" s="2" t="n"/>
+    </row>
+    <row r="893">
+      <c r="E893" s="2" t="n"/>
+    </row>
+    <row r="894">
+      <c r="E894" s="2" t="n"/>
+    </row>
+    <row r="895">
+      <c r="E895" s="2" t="n"/>
+    </row>
+    <row r="896">
+      <c r="E896" s="2" t="n"/>
+    </row>
+    <row r="897">
+      <c r="E897" s="2" t="n"/>
+    </row>
+    <row r="898">
+      <c r="E898" s="2" t="n"/>
+    </row>
+    <row r="899">
+      <c r="E899" s="2" t="n"/>
+    </row>
+    <row r="900">
+      <c r="E900" s="2" t="n"/>
+    </row>
+    <row r="901">
+      <c r="E901" s="2" t="n"/>
+    </row>
+    <row r="902">
+      <c r="E902" s="2" t="n"/>
+    </row>
+    <row r="903">
+      <c r="E903" s="2" t="n"/>
+    </row>
+    <row r="904">
+      <c r="E904" s="2" t="n"/>
+    </row>
+    <row r="905">
+      <c r="E905" s="2" t="n"/>
+    </row>
+    <row r="906">
+      <c r="E906" s="2" t="n"/>
+    </row>
+    <row r="907">
+      <c r="E907" s="2" t="n"/>
+    </row>
+    <row r="908">
+      <c r="E908" s="2" t="n"/>
+    </row>
+    <row r="909">
+      <c r="E909" s="2" t="n"/>
+    </row>
+    <row r="910">
+      <c r="E910" s="2" t="n"/>
+    </row>
+    <row r="911">
+      <c r="E911" s="2" t="n"/>
+    </row>
+    <row r="912">
+      <c r="E912" s="2" t="n"/>
+    </row>
+    <row r="913">
+      <c r="E913" s="2" t="n"/>
+    </row>
+    <row r="914">
+      <c r="E914" s="2" t="n"/>
+    </row>
+    <row r="915">
+      <c r="E915" s="2" t="n"/>
+    </row>
+    <row r="916">
+      <c r="E916" s="2" t="n"/>
+    </row>
+    <row r="917">
+      <c r="E917" s="2" t="n"/>
+    </row>
+    <row r="918">
+      <c r="E918" s="2" t="n"/>
+    </row>
+    <row r="919">
+      <c r="E919" s="2" t="n"/>
+    </row>
+    <row r="920">
+      <c r="E920" s="2" t="n"/>
+    </row>
+    <row r="921">
+      <c r="E921" s="2" t="n"/>
+    </row>
+    <row r="922">
+      <c r="E922" s="2" t="n"/>
+    </row>
+    <row r="923">
+      <c r="E923" s="2" t="n"/>
+    </row>
+    <row r="924">
+      <c r="E924" s="2" t="n"/>
+    </row>
+    <row r="925">
+      <c r="E925" s="2" t="n"/>
+    </row>
+    <row r="926">
+      <c r="E926" s="2" t="n"/>
+    </row>
+    <row r="927">
+      <c r="E927" s="2" t="n"/>
+    </row>
+    <row r="928">
+      <c r="E928" s="2" t="n"/>
+    </row>
+    <row r="929">
+      <c r="E929" s="2" t="n"/>
+    </row>
+    <row r="930">
+      <c r="E930" s="2" t="n"/>
+    </row>
+    <row r="931">
+      <c r="E931" s="2" t="n"/>
+    </row>
+    <row r="932">
+      <c r="E932" s="2" t="n"/>
+    </row>
+    <row r="933">
+      <c r="E933" s="2" t="n"/>
+    </row>
+    <row r="934">
+      <c r="E934" s="2" t="n"/>
+    </row>
+    <row r="935">
+      <c r="E935" s="2" t="n"/>
+    </row>
+    <row r="936">
+      <c r="E936" s="2" t="n"/>
+    </row>
+    <row r="937">
+      <c r="E937" s="2" t="n"/>
+    </row>
+    <row r="938">
+      <c r="E938" s="2" t="n"/>
+    </row>
+    <row r="939">
+      <c r="E939" s="2" t="n"/>
+    </row>
+    <row r="940">
+      <c r="E940" s="2" t="n"/>
+    </row>
+    <row r="941">
+      <c r="E941" s="2" t="n"/>
+    </row>
+    <row r="942">
+      <c r="E942" s="2" t="n"/>
+    </row>
+    <row r="943">
+      <c r="E943" s="2" t="n"/>
+    </row>
+    <row r="944">
+      <c r="E944" s="2" t="n"/>
+    </row>
+    <row r="945">
+      <c r="E945" s="2" t="n"/>
+    </row>
+    <row r="946">
+      <c r="E946" s="2" t="n"/>
+    </row>
+    <row r="947">
+      <c r="E947" s="2" t="n"/>
+    </row>
+    <row r="948">
+      <c r="E948" s="2" t="n"/>
+    </row>
+    <row r="949">
+      <c r="E949" s="2" t="n"/>
+    </row>
+    <row r="950">
+      <c r="E950" s="2" t="n"/>
+    </row>
+    <row r="951">
+      <c r="E951" s="2" t="n"/>
+    </row>
+    <row r="952">
+      <c r="E952" s="2" t="n"/>
+    </row>
+    <row r="953">
+      <c r="E953" s="2" t="n"/>
+    </row>
+    <row r="954">
+      <c r="E954" s="2" t="n"/>
+    </row>
+    <row r="955">
+      <c r="E955" s="2" t="n"/>
+    </row>
+    <row r="956">
+      <c r="E956" s="2" t="n"/>
+    </row>
+    <row r="957">
+      <c r="E957" s="2" t="n"/>
+    </row>
+    <row r="958">
+      <c r="E958" s="2" t="n"/>
+    </row>
+    <row r="959">
+      <c r="E959" s="2" t="n"/>
+    </row>
+    <row r="960">
+      <c r="E960" s="2" t="n"/>
+    </row>
+    <row r="961">
+      <c r="E961" s="2" t="n"/>
+    </row>
+    <row r="962">
+      <c r="E962" s="2" t="n"/>
+    </row>
+    <row r="963">
+      <c r="E963" s="2" t="n"/>
+    </row>
+    <row r="964">
+      <c r="E964" s="2" t="n"/>
+    </row>
+    <row r="965">
+      <c r="E965" s="2" t="n"/>
+    </row>
+    <row r="966">
+      <c r="E966" s="2" t="n"/>
+    </row>
+    <row r="967">
+      <c r="E967" s="2" t="n"/>
+    </row>
+    <row r="968">
+      <c r="E968" s="2" t="n"/>
+    </row>
+    <row r="969">
+      <c r="E969" s="2" t="n"/>
+    </row>
+    <row r="970">
+      <c r="E970" s="2" t="n"/>
+    </row>
+    <row r="971">
+      <c r="E971" s="2" t="n"/>
+    </row>
+    <row r="972">
+      <c r="E972" s="2" t="n"/>
+    </row>
+    <row r="973">
+      <c r="E973" s="2" t="n"/>
+    </row>
+    <row r="974">
+      <c r="E974" s="2" t="n"/>
+    </row>
+    <row r="975">
+      <c r="E975" s="2" t="n"/>
+    </row>
+    <row r="976">
+      <c r="E976" s="2" t="n"/>
+    </row>
+    <row r="977">
+      <c r="E977" s="2" t="n"/>
+    </row>
+    <row r="978">
+      <c r="E978" s="2" t="n"/>
+    </row>
+    <row r="979">
+      <c r="E979" s="2" t="n"/>
+    </row>
+    <row r="980">
+      <c r="E980" s="2" t="n"/>
+    </row>
+    <row r="981">
+      <c r="E981" s="2" t="n"/>
+    </row>
+    <row r="982">
+      <c r="E982" s="2" t="n"/>
+    </row>
+    <row r="983">
+      <c r="E983" s="2" t="n"/>
+    </row>
+    <row r="984">
+      <c r="E984" s="2" t="n"/>
+    </row>
+    <row r="985">
+      <c r="E985" s="2" t="n"/>
+    </row>
+    <row r="986">
+      <c r="E986" s="2" t="n"/>
+    </row>
+    <row r="987">
+      <c r="E987" s="2" t="n"/>
+    </row>
+    <row r="988">
+      <c r="E988" s="2" t="n"/>
+    </row>
+    <row r="989">
+      <c r="E989" s="2" t="n"/>
+    </row>
+    <row r="990">
+      <c r="E990" s="2" t="n"/>
+    </row>
+    <row r="991">
+      <c r="E991" s="2" t="n"/>
+    </row>
+    <row r="992">
+      <c r="E992" s="2" t="n"/>
+    </row>
+    <row r="993">
+      <c r="E993" s="2" t="n"/>
+    </row>
+    <row r="994">
+      <c r="E994" s="2" t="n"/>
+    </row>
+    <row r="995">
+      <c r="E995" s="2" t="n"/>
+    </row>
+    <row r="996">
+      <c r="E996" s="2" t="n"/>
+    </row>
+    <row r="997">
+      <c r="E997" s="2" t="n"/>
+    </row>
+    <row r="998">
+      <c r="E998" s="2" t="n"/>
+    </row>
+    <row r="999">
+      <c r="E999" s="2" t="n"/>
+    </row>
+    <row r="1000">
+      <c r="E1000" s="2" t="n"/>
+    </row>
+    <row r="1001">
+      <c r="E1001" s="2" t="n"/>
+    </row>
+    <row r="1002">
+      <c r="E1002" s="2" t="n"/>
+    </row>
+    <row r="1003">
+      <c r="E1003" s="2" t="n"/>
+    </row>
+    <row r="1004">
+      <c r="E1004" s="2" t="n"/>
+    </row>
+    <row r="1005">
+      <c r="E1005" s="2" t="n"/>
+    </row>
+    <row r="1006">
+      <c r="E1006" s="2" t="n"/>
+    </row>
+    <row r="1007">
+      <c r="E1007" s="2" t="n"/>
+    </row>
+    <row r="1008">
+      <c r="E1008" s="2" t="n"/>
+    </row>
+    <row r="1009">
+      <c r="E1009" s="2" t="n"/>
+    </row>
+    <row r="1010">
+      <c r="E1010" s="2" t="n"/>
+    </row>
+    <row r="1011">
+      <c r="E1011" s="2" t="n"/>
+    </row>
+    <row r="1012">
+      <c r="E1012" s="2" t="n"/>
+    </row>
+    <row r="1013">
+      <c r="E1013" s="2" t="n"/>
+    </row>
+    <row r="1014">
+      <c r="E1014" s="2" t="n"/>
+    </row>
+    <row r="1015">
+      <c r="E1015" s="2" t="n"/>
+    </row>
+    <row r="1016">
+      <c r="E1016" s="2" t="n"/>
+    </row>
+    <row r="1017">
+      <c r="E1017" s="2" t="n"/>
+    </row>
+    <row r="1018">
+      <c r="E1018" s="2" t="n"/>
+    </row>
+    <row r="1019">
+      <c r="E1019" s="2" t="n"/>
+    </row>
+    <row r="1020">
+      <c r="E1020" s="2" t="n"/>
+    </row>
+    <row r="1021">
+      <c r="E1021" s="2" t="n"/>
+    </row>
+    <row r="1022">
+      <c r="E1022" s="2" t="n"/>
+    </row>
+    <row r="1023">
+      <c r="E1023" s="2" t="n"/>
+    </row>
+    <row r="1024">
+      <c r="E1024" s="2" t="n"/>
+    </row>
+    <row r="1025">
+      <c r="E1025" s="2" t="n"/>
+    </row>
+    <row r="1026">
+      <c r="E1026" s="2" t="n"/>
+    </row>
+    <row r="1027">
+      <c r="E1027" s="2" t="n"/>
+    </row>
+    <row r="1028">
+      <c r="E1028" s="2" t="n"/>
+    </row>
+    <row r="1029">
+      <c r="E1029" s="2" t="n"/>
+    </row>
+    <row r="1030">
+      <c r="E1030" s="2" t="n"/>
+    </row>
+    <row r="1031">
+      <c r="E1031" s="2" t="n"/>
+    </row>
+    <row r="1032">
+      <c r="E1032" s="2" t="n"/>
+    </row>
+    <row r="1033">
+      <c r="E1033" s="2" t="n"/>
+    </row>
+    <row r="1034">
+      <c r="E1034" s="2" t="n"/>
+    </row>
+    <row r="1035">
+      <c r="E1035" s="2" t="n"/>
+    </row>
+    <row r="1036">
+      <c r="E1036" s="2" t="n"/>
+    </row>
+    <row r="1037">
+      <c r="E1037" s="2" t="n"/>
+    </row>
+    <row r="1038">
+      <c r="E1038" s="2" t="n"/>
+    </row>
+    <row r="1039">
+      <c r="E1039" s="2" t="n"/>
+    </row>
+    <row r="1040">
+      <c r="E1040" s="2" t="n"/>
+    </row>
+    <row r="1041">
+      <c r="E1041" s="2" t="n"/>
+    </row>
+    <row r="1042">
+      <c r="E1042" s="2" t="n"/>
+    </row>
+    <row r="1043">
+      <c r="E1043" s="2" t="n"/>
+    </row>
+    <row r="1044">
+      <c r="E1044" s="2" t="n"/>
+    </row>
+    <row r="1045">
+      <c r="E1045" s="2" t="n"/>
+    </row>
+    <row r="1046">
+      <c r="E1046" s="2" t="n"/>
+    </row>
+    <row r="1047">
+      <c r="E1047" s="2" t="n"/>
+    </row>
+    <row r="1048">
+      <c r="E1048" s="2" t="n"/>
+    </row>
+    <row r="1049">
+      <c r="E1049" s="2" t="n"/>
+    </row>
+    <row r="1050">
+      <c r="E1050" s="2" t="n"/>
+    </row>
+    <row r="1051">
+      <c r="E1051" s="2" t="n"/>
+    </row>
+    <row r="1052">
+      <c r="E1052" s="2" t="n"/>
+    </row>
+    <row r="1053">
+      <c r="E1053" s="2" t="n"/>
+    </row>
+    <row r="1054">
+      <c r="E1054" s="2" t="n"/>
+    </row>
+    <row r="1055">
+      <c r="E1055" s="2" t="n"/>
+    </row>
+    <row r="1056">
+      <c r="E1056" s="2" t="n"/>
+    </row>
+    <row r="1057">
+      <c r="E1057" s="2" t="n"/>
+    </row>
+    <row r="1058">
+      <c r="E1058" s="2" t="n"/>
+    </row>
+    <row r="1059">
+      <c r="E1059" s="2" t="n"/>
+    </row>
+    <row r="1060">
+      <c r="E1060" s="2" t="n"/>
+    </row>
+    <row r="1061">
+      <c r="E1061" s="2" t="n"/>
+    </row>
+    <row r="1062">
+      <c r="E1062" s="2" t="n"/>
+    </row>
+    <row r="1063">
+      <c r="E1063" s="2" t="n"/>
+    </row>
+    <row r="1064">
+      <c r="E1064" s="2" t="n"/>
+    </row>
+    <row r="1065">
+      <c r="E1065" s="2" t="n"/>
+    </row>
+    <row r="1066">
+      <c r="E1066" s="2" t="n"/>
+    </row>
+    <row r="1067">
+      <c r="E1067" s="2" t="n"/>
+    </row>
+    <row r="1068">
+      <c r="E1068" s="2" t="n"/>
+    </row>
+    <row r="1069">
+      <c r="E1069" s="2" t="n"/>
+    </row>
+    <row r="1070">
+      <c r="E1070" s="2" t="n"/>
+    </row>
+    <row r="1071">
+      <c r="E1071" s="2" t="n"/>
+    </row>
+    <row r="1072">
+      <c r="E1072" s="2" t="n"/>
+    </row>
+    <row r="1073">
+      <c r="E1073" s="2" t="n"/>
+    </row>
+    <row r="1074">
+      <c r="E1074" s="2" t="n"/>
+    </row>
+    <row r="1075">
+      <c r="E1075" s="2" t="n"/>
+    </row>
+    <row r="1076">
+      <c r="E1076" s="2" t="n"/>
+    </row>
+    <row r="1077">
+      <c r="E1077" s="2" t="n"/>
+    </row>
+    <row r="1078">
+      <c r="E1078" s="2" t="n"/>
+    </row>
+    <row r="1079">
+      <c r="E1079" s="2" t="n"/>
+    </row>
+    <row r="1080">
+      <c r="E1080" s="2" t="n"/>
+    </row>
+    <row r="1081">
+      <c r="E1081" s="2" t="n"/>
+    </row>
+    <row r="1082">
+      <c r="E1082" s="2" t="n"/>
+    </row>
+    <row r="1083">
+      <c r="E1083" s="2" t="n"/>
+    </row>
+    <row r="1084">
+      <c r="E1084" s="2" t="n"/>
+    </row>
+    <row r="1085">
+      <c r="E1085" s="2" t="n"/>
+    </row>
+    <row r="1086">
+      <c r="E1086" s="2" t="n"/>
+    </row>
+    <row r="1087">
+      <c r="E1087" s="2" t="n"/>
+    </row>
+    <row r="1088">
+      <c r="E1088" s="2" t="n"/>
+    </row>
+    <row r="1089">
+      <c r="E1089" s="2" t="n"/>
+    </row>
+    <row r="1090">
+      <c r="E1090" s="2" t="n"/>
+    </row>
+    <row r="1091">
+      <c r="E1091" s="2" t="n"/>
+    </row>
+    <row r="1092">
+      <c r="E1092" s="2" t="n"/>
+    </row>
+    <row r="1093">
+      <c r="E1093" s="2" t="n"/>
+    </row>
+    <row r="1094">
+      <c r="E1094" s="2" t="n"/>
+    </row>
+    <row r="1095">
+      <c r="E1095" s="2" t="n"/>
+    </row>
+    <row r="1096">
+      <c r="E1096" s="2" t="n"/>
+    </row>
+    <row r="1097">
+      <c r="E1097" s="2" t="n"/>
+    </row>
+    <row r="1098">
+      <c r="E1098" s="2" t="n"/>
+    </row>
+    <row r="1099">
+      <c r="E1099" s="2" t="n"/>
+    </row>
+    <row r="1100">
+      <c r="E1100" s="2" t="n"/>
+    </row>
+    <row r="1101">
+      <c r="E1101" s="2" t="n"/>
+    </row>
+    <row r="1102">
+      <c r="E1102" s="2" t="n"/>
+    </row>
+    <row r="1103">
+      <c r="E1103" s="2" t="n"/>
+    </row>
+    <row r="1104">
+      <c r="E1104" s="2" t="n"/>
+    </row>
+    <row r="1105">
+      <c r="E1105" s="2" t="n"/>
+    </row>
+    <row r="1106">
+      <c r="E1106" s="2" t="n"/>
+    </row>
+    <row r="1107">
+      <c r="E1107" s="2" t="n"/>
+    </row>
+    <row r="1108">
+      <c r="E1108" s="2" t="n"/>
+    </row>
+    <row r="1109">
+      <c r="E1109" s="2" t="n"/>
+    </row>
+    <row r="1110">
+      <c r="E1110" s="2" t="n"/>
+    </row>
+    <row r="1111">
+      <c r="E1111" s="2" t="n"/>
+    </row>
+    <row r="1112">
+      <c r="E1112" s="2" t="n"/>
+    </row>
+    <row r="1113">
+      <c r="E1113" s="2" t="n"/>
+    </row>
+    <row r="1114">
+      <c r="E1114" s="2" t="n"/>
+    </row>
+    <row r="1115">
+      <c r="E1115" s="2" t="n"/>
+    </row>
+    <row r="1116">
+      <c r="E1116" s="2" t="n"/>
+    </row>
+    <row r="1117">
+      <c r="E1117" s="2" t="n"/>
+    </row>
+    <row r="1118">
+      <c r="E1118" s="2" t="n"/>
+    </row>
+    <row r="1119">
+      <c r="E1119" s="2" t="n"/>
+    </row>
+    <row r="1120">
+      <c r="E1120" s="2" t="n"/>
+    </row>
+    <row r="1121">
+      <c r="E1121" s="2" t="n"/>
+    </row>
+    <row r="1122">
+      <c r="E1122" s="2" t="n"/>
+    </row>
+    <row r="1123">
+      <c r="E1123" s="2" t="n"/>
+    </row>
+    <row r="1124">
+      <c r="E1124" s="2" t="n"/>
+    </row>
+    <row r="1125">
+      <c r="E1125" s="2" t="n"/>
+    </row>
+    <row r="1126">
+      <c r="E1126" s="2" t="n"/>
+    </row>
+    <row r="1127">
+      <c r="E1127" s="2" t="n"/>
+    </row>
+    <row r="1128">
+      <c r="E1128" s="2" t="n"/>
+    </row>
+    <row r="1129">
+      <c r="E1129" s="2" t="n"/>
+    </row>
+    <row r="1130">
+      <c r="E1130" s="2" t="n"/>
+    </row>
+    <row r="1131">
+      <c r="E1131" s="2" t="n"/>
+    </row>
+    <row r="1132">
+      <c r="E1132" s="2" t="n"/>
+    </row>
+    <row r="1133">
+      <c r="E1133" s="2" t="n"/>
+    </row>
+    <row r="1134">
+      <c r="E1134" s="2" t="n"/>
+    </row>
+    <row r="1135">
+      <c r="E1135" s="2" t="n"/>
+    </row>
+    <row r="1136">
+      <c r="E1136" s="2" t="n"/>
+    </row>
+    <row r="1137">
+      <c r="E1137" s="2" t="n"/>
+    </row>
+    <row r="1138">
+      <c r="E1138" s="2" t="n"/>
+    </row>
+    <row r="1139">
+      <c r="E1139" s="2" t="n"/>
+    </row>
+    <row r="1140">
+      <c r="E1140" s="2" t="n"/>
+    </row>
+    <row r="1141">
+      <c r="E1141" s="2" t="n"/>
+    </row>
+    <row r="1142">
+      <c r="E1142" s="2" t="n"/>
+    </row>
+    <row r="1143">
+      <c r="E1143" s="2" t="n"/>
+    </row>
+    <row r="1144">
+      <c r="E1144" s="2" t="n"/>
+    </row>
+    <row r="1145">
+      <c r="E1145" s="2" t="n"/>
+    </row>
+    <row r="1146">
+      <c r="E1146" s="2" t="n"/>
+    </row>
+    <row r="1147">
+      <c r="E1147" s="2" t="n"/>
+    </row>
+    <row r="1148">
+      <c r="E1148" s="2" t="n"/>
+    </row>
+    <row r="1149">
+      <c r="E1149" s="2" t="n"/>
+    </row>
+    <row r="1150">
+      <c r="E1150" s="2" t="n"/>
+    </row>
+    <row r="1151">
+      <c r="E1151" s="2" t="n"/>
+    </row>
+    <row r="1152">
+      <c r="E1152" s="2" t="n"/>
+    </row>
+    <row r="1153">
+      <c r="E1153" s="2" t="n"/>
+    </row>
+    <row r="1154">
+      <c r="E1154" s="2" t="n"/>
+    </row>
+    <row r="1155">
+      <c r="E1155" s="2" t="n"/>
+    </row>
+    <row r="1156">
+      <c r="E1156" s="2" t="n"/>
+    </row>
+    <row r="1157">
+      <c r="E1157" s="2" t="n"/>
+    </row>
+    <row r="1158">
+      <c r="E1158" s="2" t="n"/>
+    </row>
+    <row r="1159">
+      <c r="E1159" s="2" t="n"/>
+    </row>
+    <row r="1160">
+      <c r="E1160" s="2" t="n"/>
+    </row>
+    <row r="1161">
+      <c r="E1161" s="2" t="n"/>
+    </row>
+    <row r="1162">
+      <c r="E1162" s="2" t="n"/>
+    </row>
+    <row r="1163">
+      <c r="E1163" s="2" t="n"/>
+    </row>
+    <row r="1164">
+      <c r="E1164" s="2" t="n"/>
+    </row>
+    <row r="1165">
+      <c r="E1165" s="2" t="n"/>
+    </row>
+    <row r="1166">
+      <c r="E1166" s="2" t="n"/>
+    </row>
+    <row r="1167">
+      <c r="E1167" s="2" t="n"/>
+    </row>
+    <row r="1168">
+      <c r="E1168" s="2" t="n"/>
+    </row>
+    <row r="1169">
+      <c r="E1169" s="2" t="n"/>
+    </row>
+    <row r="1170">
+      <c r="E1170" s="2" t="n"/>
+    </row>
+    <row r="1171">
+      <c r="E1171" s="2" t="n"/>
+    </row>
+    <row r="1172">
+      <c r="E1172" s="2" t="n"/>
+    </row>
+    <row r="1173">
+      <c r="E1173" s="2" t="n"/>
+    </row>
+    <row r="1174">
+      <c r="E1174" s="2" t="n"/>
+    </row>
+    <row r="1175">
+      <c r="E1175" s="2" t="n"/>
+    </row>
+    <row r="1176">
+      <c r="E1176" s="2" t="n"/>
+    </row>
+    <row r="1177">
+      <c r="E1177" s="2" t="n"/>
+    </row>
+    <row r="1178">
+      <c r="E1178" s="2" t="n"/>
+    </row>
+    <row r="1179">
+      <c r="E1179" s="2" t="n"/>
+    </row>
+    <row r="1180">
+      <c r="E1180" s="2" t="n"/>
+    </row>
+    <row r="1181">
+      <c r="E1181" s="2" t="n"/>
+    </row>
+    <row r="1182">
+      <c r="E1182" s="2" t="n"/>
+    </row>
+    <row r="1183">
+      <c r="E1183" s="2" t="n"/>
+    </row>
+    <row r="1184">
+      <c r="E1184" s="2" t="n"/>
+    </row>
+    <row r="1185">
+      <c r="E1185" s="2" t="n"/>
+    </row>
+    <row r="1186">
+      <c r="E1186" s="2" t="n"/>
+    </row>
+    <row r="1187">
+      <c r="E1187" s="2" t="n"/>
+    </row>
+    <row r="1188">
+      <c r="E1188" s="2" t="n"/>
+    </row>
+    <row r="1189">
+      <c r="E1189" s="2" t="n"/>
+    </row>
+    <row r="1190">
+      <c r="E1190" s="2" t="n"/>
+    </row>
+    <row r="1191">
+      <c r="E1191" s="2" t="n"/>
+    </row>
+    <row r="1192">
+      <c r="E1192" s="2" t="n"/>
+    </row>
+    <row r="1193">
+      <c r="E1193" s="2" t="n"/>
+    </row>
+    <row r="1194">
+      <c r="E1194" s="2" t="n"/>
+    </row>
+    <row r="1195">
+      <c r="E1195" s="2" t="n"/>
+    </row>
+    <row r="1196">
+      <c r="E1196" s="2" t="n"/>
+    </row>
+    <row r="1197">
+      <c r="E1197" s="2" t="n"/>
+    </row>
+    <row r="1198">
+      <c r="E1198" s="2" t="n"/>
+    </row>
+    <row r="1199">
+      <c r="E1199" s="2" t="n"/>
+    </row>
+    <row r="1200">
+      <c r="E1200" s="2" t="n"/>
+    </row>
+    <row r="1201">
+      <c r="E1201" s="2" t="n"/>
+    </row>
+    <row r="1202">
+      <c r="E1202" s="2" t="n"/>
+    </row>
+    <row r="1203">
+      <c r="E1203" s="2" t="n"/>
+    </row>
+    <row r="1204">
+      <c r="E1204" s="2" t="n"/>
+    </row>
+    <row r="1205">
+      <c r="E1205" s="2" t="n"/>
+    </row>
+    <row r="1206">
+      <c r="E1206" s="2" t="n"/>
+    </row>
+    <row r="1207">
+      <c r="E1207" s="2" t="n"/>
+    </row>
+    <row r="1208">
+      <c r="E1208" s="2" t="n"/>
+    </row>
+    <row r="1209">
+      <c r="E1209" s="2" t="n"/>
+    </row>
+    <row r="1210">
+      <c r="E1210" s="2" t="n"/>
+    </row>
+    <row r="1211">
+      <c r="E1211" s="2" t="n"/>
+    </row>
+    <row r="1212">
+      <c r="E1212" s="2" t="n"/>
+    </row>
+    <row r="1213">
+      <c r="E1213" s="2" t="n"/>
+    </row>
+    <row r="1214">
+      <c r="E1214" s="2" t="n"/>
+    </row>
+    <row r="1215">
+      <c r="E1215" s="2" t="n"/>
+    </row>
+    <row r="1216">
+      <c r="E1216" s="2" t="n"/>
+    </row>
+    <row r="1217">
+      <c r="E1217" s="2" t="n"/>
+    </row>
+    <row r="1218">
+      <c r="E1218" s="2" t="n"/>
+    </row>
+    <row r="1219">
+      <c r="E1219" s="2" t="n"/>
+    </row>
+    <row r="1220">
+      <c r="E1220" s="2" t="n"/>
+    </row>
+    <row r="1221">
+      <c r="E1221" s="2" t="n"/>
+    </row>
+    <row r="1222">
+      <c r="E1222" s="2" t="n"/>
+    </row>
+    <row r="1223">
+      <c r="E1223" s="2" t="n"/>
+    </row>
+    <row r="1224">
+      <c r="E1224" s="2" t="n"/>
+    </row>
+    <row r="1225">
+      <c r="E1225" s="2" t="n"/>
+    </row>
+    <row r="1226">
+      <c r="E1226" s="2" t="n"/>
+    </row>
+    <row r="1227">
+      <c r="E1227" s="2" t="n"/>
+    </row>
+    <row r="1228">
+      <c r="E1228" s="2" t="n"/>
+    </row>
+    <row r="1229">
+      <c r="E1229" s="2" t="n"/>
+    </row>
+    <row r="1230">
+      <c r="E1230" s="2" t="n"/>
+    </row>
+    <row r="1231">
+      <c r="E1231" s="2" t="n"/>
+    </row>
+    <row r="1232">
+      <c r="E1232" s="2" t="n"/>
+    </row>
+    <row r="1233">
+      <c r="E1233" s="2" t="n"/>
+    </row>
+    <row r="1234">
+      <c r="E1234" s="2" t="n"/>
+    </row>
+    <row r="1235">
+      <c r="E1235" s="2" t="n"/>
+    </row>
+    <row r="1236">
+      <c r="E1236" s="2" t="n"/>
+    </row>
+    <row r="1237">
+      <c r="E1237" s="2" t="n"/>
+    </row>
+    <row r="1238">
+      <c r="E1238" s="2" t="n"/>
+    </row>
+    <row r="1239">
+      <c r="E1239" s="2" t="n"/>
+    </row>
+    <row r="1240">
+      <c r="E1240" s="2" t="n"/>
+    </row>
+    <row r="1241">
+      <c r="E1241" s="2" t="n"/>
+    </row>
+    <row r="1242">
+      <c r="E1242" s="2" t="n"/>
+    </row>
+    <row r="1243">
+      <c r="E1243" s="2" t="n"/>
+    </row>
+    <row r="1244">
+      <c r="E1244" s="2" t="n"/>
+    </row>
+    <row r="1245">
+      <c r="E1245" s="2" t="n"/>
+    </row>
+    <row r="1246">
+      <c r="E1246" s="2" t="n"/>
+    </row>
+    <row r="1247">
+      <c r="E1247" s="2" t="n"/>
+    </row>
+    <row r="1248">
+      <c r="E1248" s="2" t="n"/>
+    </row>
+    <row r="1249">
+      <c r="E1249" s="2" t="n"/>
+    </row>
+    <row r="1250">
+      <c r="E1250" s="2" t="n"/>
+    </row>
+    <row r="1251">
+      <c r="E1251" s="2" t="n"/>
+    </row>
+    <row r="1252">
+      <c r="E1252" s="2" t="n"/>
+    </row>
+    <row r="1253">
+      <c r="E1253" s="2" t="n"/>
+    </row>
+    <row r="1254">
+      <c r="E1254" s="2" t="n"/>
+    </row>
+    <row r="1255">
+      <c r="E1255" s="2" t="n"/>
+    </row>
+    <row r="1256">
+      <c r="E1256" s="2" t="n"/>
+    </row>
+    <row r="1257">
+      <c r="E1257" s="2" t="n"/>
+    </row>
+    <row r="1258">
+      <c r="E1258" s="2" t="n"/>
+    </row>
+    <row r="1259">
+      <c r="E1259" s="2" t="n"/>
+    </row>
+    <row r="1260">
+      <c r="E1260" s="2" t="n"/>
+    </row>
+    <row r="1261">
+      <c r="E1261" s="2" t="n"/>
+    </row>
+    <row r="1262">
+      <c r="E1262" s="2" t="n"/>
+    </row>
+    <row r="1263">
+      <c r="E1263" s="2" t="n"/>
+    </row>
+    <row r="1264">
+      <c r="E1264" s="2" t="n"/>
+    </row>
+    <row r="1265">
+      <c r="E1265" s="2" t="n"/>
+    </row>
+    <row r="1266">
+      <c r="E1266" s="2" t="n"/>
+    </row>
+    <row r="1267">
+      <c r="E1267" s="2" t="n"/>
+    </row>
+    <row r="1268">
+      <c r="E1268" s="2" t="n"/>
+    </row>
+    <row r="1269">
+      <c r="E1269" s="2" t="n"/>
+    </row>
+    <row r="1270">
+      <c r="E1270" s="2" t="n"/>
+    </row>
+    <row r="1271">
+      <c r="E1271" s="2" t="n"/>
+    </row>
+    <row r="1272">
+      <c r="E1272" s="2" t="n"/>
+    </row>
+    <row r="1273">
+      <c r="E1273" s="2" t="n"/>
+    </row>
+    <row r="1274">
+      <c r="E1274" s="2" t="n"/>
+    </row>
+    <row r="1275">
+      <c r="E1275" s="2" t="n"/>
+    </row>
+    <row r="1276">
+      <c r="E1276" s="2" t="n"/>
+    </row>
+    <row r="1277">
+      <c r="E1277" s="2" t="n"/>
+    </row>
+    <row r="1278">
+      <c r="E1278" s="2" t="n"/>
+    </row>
+    <row r="1279">
+      <c r="E1279" s="2" t="n"/>
+    </row>
+    <row r="1280">
+      <c r="E1280" s="2" t="n"/>
+    </row>
+    <row r="1281">
+      <c r="E1281" s="2" t="n"/>
+    </row>
+    <row r="1282">
+      <c r="E1282" s="2" t="n"/>
+    </row>
+    <row r="1283">
+      <c r="E1283" s="2" t="n"/>
+    </row>
+    <row r="1284">
+      <c r="E1284" s="2" t="n"/>
+    </row>
+    <row r="1285">
+      <c r="E1285" s="2" t="n"/>
+    </row>
+    <row r="1286">
+      <c r="E1286" s="2" t="n"/>
+    </row>
+    <row r="1287">
+      <c r="E1287" s="2" t="n"/>
+    </row>
+    <row r="1288">
+      <c r="E1288" s="2" t="n"/>
+    </row>
+    <row r="1289">
+      <c r="E1289" s="2" t="n"/>
+    </row>
+    <row r="1290">
+      <c r="E1290" s="2" t="n"/>
+    </row>
+    <row r="1291">
+      <c r="E1291" s="2" t="n"/>
+    </row>
+    <row r="1292">
+      <c r="E1292" s="2" t="n"/>
+    </row>
+    <row r="1293">
+      <c r="E1293" s="2" t="n"/>
+    </row>
+    <row r="1294">
+      <c r="E1294" s="2" t="n"/>
+    </row>
+    <row r="1295">
+      <c r="E1295" s="2" t="n"/>
+    </row>
+    <row r="1296">
+      <c r="E1296" s="2" t="n"/>
+    </row>
+    <row r="1297">
+      <c r="E1297" s="2" t="n"/>
+    </row>
+    <row r="1298">
+      <c r="E1298" s="2" t="n"/>
+    </row>
+    <row r="1299">
+      <c r="E1299" s="2" t="n"/>
+    </row>
+    <row r="1300">
+      <c r="E1300" s="2" t="n"/>
+    </row>
+    <row r="1301">
+      <c r="E1301" s="2" t="n"/>
+    </row>
+    <row r="1302">
+      <c r="E1302" s="2" t="n"/>
+    </row>
+    <row r="1303">
+      <c r="E1303" s="2" t="n"/>
+    </row>
+    <row r="1304">
+      <c r="E1304" s="2" t="n"/>
+    </row>
+    <row r="1305">
+      <c r="E1305" s="2" t="n"/>
+    </row>
+    <row r="1306">
+      <c r="E1306" s="2" t="n"/>
+    </row>
+    <row r="1307">
+      <c r="E1307" s="2" t="n"/>
+    </row>
+    <row r="1308">
+      <c r="E1308" s="2" t="n"/>
+    </row>
+    <row r="1309">
+      <c r="E1309" s="2" t="n"/>
+    </row>
+    <row r="1310">
+      <c r="E1310" s="2" t="n"/>
+    </row>
+    <row r="1311">
+      <c r="E1311" s="2" t="n"/>
+    </row>
+    <row r="1312">
+      <c r="E1312" s="2" t="n"/>
+    </row>
+    <row r="1313">
+      <c r="E1313" s="2" t="n"/>
+    </row>
+    <row r="1314">
+      <c r="E1314" s="2" t="n"/>
+    </row>
+    <row r="1315">
+      <c r="E1315" s="2" t="n"/>
+    </row>
+    <row r="1316">
+      <c r="E1316" s="2" t="n"/>
+    </row>
+    <row r="1317">
+      <c r="E1317" s="2" t="n"/>
+    </row>
+    <row r="1318">
+      <c r="E1318" s="2" t="n"/>
+    </row>
+    <row r="1319">
+      <c r="E1319" s="2" t="n"/>
+    </row>
+    <row r="1320">
+      <c r="E1320" s="2" t="n"/>
+    </row>
+    <row r="1321">
+      <c r="E1321" s="2" t="n"/>
+    </row>
+    <row r="1322">
+      <c r="E1322" s="2" t="n"/>
+    </row>
+    <row r="1323">
+      <c r="E1323" s="2" t="n"/>
+    </row>
+    <row r="1324">
+      <c r="E1324" s="2" t="n"/>
+    </row>
+    <row r="1325">
+      <c r="E1325" s="2" t="n"/>
+    </row>
+    <row r="1326">
+      <c r="E1326" s="2" t="n"/>
+    </row>
+    <row r="1327">
+      <c r="E1327" s="2" t="n"/>
+    </row>
+    <row r="1328">
+      <c r="E1328" s="2" t="n"/>
+    </row>
+    <row r="1329">
+      <c r="E1329" s="2" t="n"/>
+    </row>
+    <row r="1330">
+      <c r="E1330" s="2" t="n"/>
+    </row>
+    <row r="1331">
+      <c r="E1331" s="2" t="n"/>
+    </row>
+    <row r="1332">
+      <c r="E1332" s="2" t="n"/>
+    </row>
+    <row r="1333">
+      <c r="E1333" s="2" t="n"/>
+    </row>
+    <row r="1334">
+      <c r="E1334" s="2" t="n"/>
+    </row>
+    <row r="1335">
+      <c r="E1335" s="2" t="n"/>
+    </row>
+    <row r="1336">
+      <c r="E1336" s="2" t="n"/>
+    </row>
+    <row r="1337">
+      <c r="E1337" s="2" t="n"/>
+    </row>
+    <row r="1338">
+      <c r="E1338" s="2" t="n"/>
+    </row>
+    <row r="1339">
+      <c r="E1339" s="2" t="n"/>
+    </row>
+    <row r="1340">
+      <c r="E1340" s="2" t="n"/>
+    </row>
+    <row r="1341">
+      <c r="E1341" s="2" t="n"/>
+    </row>
+    <row r="1342">
+      <c r="E1342" s="2" t="n"/>
+    </row>
+    <row r="1343">
+      <c r="E1343" s="2" t="n"/>
+    </row>
+    <row r="1344">
+      <c r="E1344" s="2" t="n"/>
+    </row>
+    <row r="1345">
+      <c r="E1345" s="2" t="n"/>
+    </row>
+    <row r="1346">
+      <c r="E1346" s="2" t="n"/>
+    </row>
+    <row r="1347">
+      <c r="E1347" s="2" t="n"/>
+    </row>
+    <row r="1348">
+      <c r="E1348" s="2" t="n"/>
+    </row>
+    <row r="1349">
+      <c r="E1349" s="2" t="n"/>
+    </row>
+    <row r="1350">
+      <c r="E1350" s="2" t="n"/>
+    </row>
+    <row r="1351">
+      <c r="E1351" s="2" t="n"/>
+    </row>
+    <row r="1352">
+      <c r="E1352" s="2" t="n"/>
+    </row>
+    <row r="1353">
+      <c r="E1353" s="2" t="n"/>
+    </row>
+    <row r="1354">
+      <c r="E1354" s="2" t="n"/>
+    </row>
+    <row r="1355">
+      <c r="E1355" s="2" t="n"/>
+    </row>
+    <row r="1356">
+      <c r="E1356" s="2" t="n"/>
+    </row>
+    <row r="1357">
+      <c r="E1357" s="2" t="n"/>
+    </row>
+    <row r="1358">
+      <c r="E1358" s="2" t="n"/>
+    </row>
+    <row r="1359">
+      <c r="E1359" s="2" t="n"/>
+    </row>
+    <row r="1360">
+      <c r="E1360" s="2" t="n"/>
+    </row>
+    <row r="1361">
+      <c r="E1361" s="2" t="n"/>
+    </row>
+    <row r="1362">
+      <c r="E1362" s="2" t="n"/>
+    </row>
+    <row r="1363">
+      <c r="E1363" s="2" t="n"/>
+    </row>
+    <row r="1364">
+      <c r="E1364" s="2" t="n"/>
+    </row>
+    <row r="1365">
+      <c r="E1365" s="2" t="n"/>
+    </row>
+    <row r="1366">
+      <c r="E1366" s="2" t="n"/>
+    </row>
+    <row r="1367">
+      <c r="E1367" s="2" t="n"/>
+    </row>
+    <row r="1368">
+      <c r="E1368" s="2" t="n"/>
+    </row>
+    <row r="1369">
+      <c r="E1369" s="2" t="n"/>
+    </row>
+    <row r="1370">
+      <c r="E1370" s="2" t="n"/>
+    </row>
+    <row r="1371">
+      <c r="E1371" s="2" t="n"/>
+    </row>
+    <row r="1372">
+      <c r="E1372" s="2" t="n"/>
+    </row>
+    <row r="1373">
+      <c r="E1373" s="2" t="n"/>
+    </row>
+    <row r="1374">
+      <c r="E1374" s="2" t="n"/>
+    </row>
+    <row r="1375">
+      <c r="E1375" s="2" t="n"/>
+    </row>
+    <row r="1376">
+      <c r="E1376" s="2" t="n"/>
+    </row>
+    <row r="1377">
+      <c r="E1377" s="2" t="n"/>
+    </row>
+    <row r="1378">
+      <c r="E1378" s="2" t="n"/>
+    </row>
+    <row r="1379">
+      <c r="E1379" s="2" t="n"/>
+    </row>
+    <row r="1380">
+      <c r="E1380" s="2" t="n"/>
+    </row>
+    <row r="1381">
+      <c r="E1381" s="2" t="n"/>
+    </row>
+    <row r="1382">
+      <c r="E1382" s="2" t="n"/>
+    </row>
+    <row r="1383">
+      <c r="E1383" s="2" t="n"/>
+    </row>
+    <row r="1384">
+      <c r="E1384" s="2" t="n"/>
+    </row>
+    <row r="1385">
+      <c r="E1385" s="2" t="n"/>
+    </row>
+    <row r="1386">
+      <c r="E1386" s="2" t="n"/>
+    </row>
+    <row r="1387">
+      <c r="E1387" s="2" t="n"/>
+    </row>
+    <row r="1388">
+      <c r="E1388" s="2" t="n"/>
+    </row>
+    <row r="1389">
+      <c r="E1389" s="2" t="n"/>
+    </row>
+    <row r="1390">
+      <c r="E1390" s="2" t="n"/>
+    </row>
+    <row r="1391">
+      <c r="E1391" s="2" t="n"/>
+    </row>
+    <row r="1392">
+      <c r="E1392" s="2" t="n"/>
+    </row>
+    <row r="1393">
+      <c r="E1393" s="2" t="n"/>
+    </row>
+    <row r="1394">
+      <c r="E1394" s="2" t="n"/>
+    </row>
+    <row r="1395">
+      <c r="E1395" s="2" t="n"/>
+    </row>
+    <row r="1396">
+      <c r="E1396" s="2" t="n"/>
+    </row>
+    <row r="1397">
+      <c r="E1397" s="2" t="n"/>
+    </row>
+    <row r="1398">
+      <c r="E1398" s="2" t="n"/>
+    </row>
+    <row r="1399">
+      <c r="E1399" s="2" t="n"/>
+    </row>
+    <row r="1400">
+      <c r="E1400" s="2" t="n"/>
+    </row>
+    <row r="1401">
+      <c r="E1401" s="2" t="n"/>
+    </row>
+    <row r="1402">
+      <c r="E1402" s="2" t="n"/>
+    </row>
+    <row r="1403">
+      <c r="E1403" s="2" t="n"/>
+    </row>
+    <row r="1404">
+      <c r="E1404" s="2" t="n"/>
+    </row>
+    <row r="1405">
+      <c r="E1405" s="2" t="n"/>
+    </row>
+    <row r="1406">
+      <c r="E1406" s="2" t="n"/>
+    </row>
+    <row r="1407">
+      <c r="E1407" s="2" t="n"/>
+    </row>
+    <row r="1408">
+      <c r="E1408" s="2" t="n"/>
+    </row>
+    <row r="1409">
+      <c r="E1409" s="2" t="n"/>
+    </row>
+    <row r="1410">
+      <c r="E1410" s="2" t="n"/>
+    </row>
+    <row r="1411">
+      <c r="E1411" s="2" t="n"/>
+    </row>
+    <row r="1412">
+      <c r="E1412" s="2" t="n"/>
+    </row>
+    <row r="1413">
+      <c r="E1413" s="2" t="n"/>
+    </row>
+    <row r="1414">
+      <c r="E1414" s="2" t="n"/>
+    </row>
+    <row r="1415">
+      <c r="E1415" s="2" t="n"/>
+    </row>
+    <row r="1416">
+      <c r="E1416" s="2" t="n"/>
+    </row>
+    <row r="1417">
+      <c r="E1417" s="2" t="n"/>
+    </row>
+    <row r="1418">
+      <c r="E1418" s="2" t="n"/>
+    </row>
+    <row r="1419">
+      <c r="E1419" s="2" t="n"/>
+    </row>
+    <row r="1420">
+      <c r="E1420" s="2" t="n"/>
+    </row>
+    <row r="1421">
+      <c r="E1421" s="2" t="n"/>
+    </row>
+    <row r="1422">
+      <c r="E1422" s="2" t="n"/>
+    </row>
+    <row r="1423">
+      <c r="E1423" s="2" t="n"/>
+    </row>
+    <row r="1424">
+      <c r="E1424" s="2" t="n"/>
+    </row>
+    <row r="1425">
+      <c r="E1425" s="2" t="n"/>
+    </row>
+    <row r="1426">
+      <c r="E1426" s="2" t="n"/>
+    </row>
+    <row r="1427">
+      <c r="E1427" s="2" t="n"/>
+    </row>
+    <row r="1428">
+      <c r="E1428" s="2" t="n"/>
+    </row>
+    <row r="1429">
+      <c r="E1429" s="2" t="n"/>
+    </row>
+    <row r="1430">
+      <c r="E1430" s="2" t="n"/>
+    </row>
+    <row r="1431">
+      <c r="E1431" s="2" t="n"/>
+    </row>
+    <row r="1432">
+      <c r="E1432" s="2" t="n"/>
+    </row>
+    <row r="1433">
+      <c r="E1433" s="2" t="n"/>
+    </row>
+    <row r="1434">
+      <c r="E1434" s="2" t="n"/>
+    </row>
+    <row r="1435">
+      <c r="E1435" s="2" t="n"/>
+    </row>
+    <row r="1436">
+      <c r="E1436" s="2" t="n"/>
+    </row>
+    <row r="1437">
+      <c r="E1437" s="2" t="n"/>
+    </row>
+    <row r="1438">
+      <c r="E1438" s="2" t="n"/>
+    </row>
+    <row r="1439">
+      <c r="E1439" s="2" t="n"/>
+    </row>
+    <row r="1440">
+      <c r="E1440" s="2" t="n"/>
+    </row>
+    <row r="1441">
+      <c r="E1441" s="2" t="n"/>
+    </row>
+    <row r="1442">
+      <c r="E1442" s="2" t="n"/>
+    </row>
+    <row r="1443">
+      <c r="E1443" s="2" t="n"/>
+    </row>
+    <row r="1444">
+      <c r="E1444" s="2" t="n"/>
+    </row>
+    <row r="1445">
+      <c r="E1445" s="2" t="n"/>
+    </row>
+    <row r="1446">
+      <c r="E1446" s="2" t="n"/>
+    </row>
+    <row r="1447">
+      <c r="E1447" s="2" t="n"/>
+    </row>
+    <row r="1448">
+      <c r="E1448" s="2" t="n"/>
+    </row>
+    <row r="1449">
+      <c r="E1449" s="2" t="n"/>
+    </row>
+    <row r="1450">
+      <c r="E1450" s="2" t="n"/>
+    </row>
+    <row r="1451">
+      <c r="E1451" s="2" t="n"/>
+    </row>
+    <row r="1452">
+      <c r="E1452" s="2" t="n"/>
+    </row>
+    <row r="1453">
+      <c r="E1453" s="2" t="n"/>
+    </row>
+    <row r="1454">
+      <c r="E1454" s="2" t="n"/>
+    </row>
+    <row r="1455">
+      <c r="E1455" s="2" t="n"/>
+    </row>
+    <row r="1456">
+      <c r="E1456" s="2" t="n"/>
+    </row>
+    <row r="1457">
+      <c r="E1457" s="2" t="n"/>
+    </row>
+    <row r="1458">
+      <c r="E1458" s="2" t="n"/>
+    </row>
+    <row r="1459">
+      <c r="E1459" s="2" t="n"/>
+    </row>
+    <row r="1460">
+      <c r="E1460" s="2" t="n"/>
+    </row>
+    <row r="1461">
+      <c r="E1461" s="2" t="n"/>
+    </row>
+    <row r="1462">
+      <c r="E1462" s="2" t="n"/>
+    </row>
+    <row r="1463">
+      <c r="E1463" s="2" t="n"/>
+    </row>
+    <row r="1464">
+      <c r="E1464" s="2" t="n"/>
+    </row>
+    <row r="1465">
+      <c r="E1465" s="2" t="n"/>
+    </row>
+    <row r="1466">
+      <c r="E1466" s="2" t="n"/>
+    </row>
+    <row r="1467">
+      <c r="E1467" s="2" t="n"/>
+    </row>
+    <row r="1468">
+      <c r="E1468" s="2" t="n"/>
+    </row>
+    <row r="1469">
+      <c r="E1469" s="2" t="n"/>
+    </row>
+    <row r="1470">
+      <c r="E1470" s="2" t="n"/>
+    </row>
+    <row r="1471">
+      <c r="E1471" s="2" t="n"/>
+    </row>
+    <row r="1472">
+      <c r="E1472" s="2" t="n"/>
+    </row>
+    <row r="1473">
+      <c r="E1473" s="2" t="n"/>
+    </row>
+    <row r="1474">
+      <c r="E1474" s="2" t="n"/>
+    </row>
+    <row r="1475">
+      <c r="E1475" s="2" t="n"/>
+    </row>
+    <row r="1476">
+      <c r="E1476" s="2" t="n"/>
+    </row>
+    <row r="1477">
+      <c r="E1477" s="2" t="n"/>
+    </row>
+    <row r="1478">
+      <c r="E1478" s="2" t="n"/>
+    </row>
+    <row r="1479">
+      <c r="E1479" s="2" t="n"/>
+    </row>
+    <row r="1480">
+      <c r="E1480" s="2" t="n"/>
+    </row>
+    <row r="1481">
+      <c r="E1481" s="2" t="n"/>
+    </row>
+    <row r="1482">
+      <c r="E1482" s="2" t="n"/>
+    </row>
+    <row r="1483">
+      <c r="E1483" s="2" t="n"/>
+    </row>
+    <row r="1484">
+      <c r="E1484" s="2" t="n"/>
+    </row>
+    <row r="1485">
+      <c r="E1485" s="2" t="n"/>
+    </row>
+    <row r="1486">
+      <c r="E1486" s="2" t="n"/>
+    </row>
+    <row r="1487">
+      <c r="E1487" s="2" t="n"/>
+    </row>
+    <row r="1488">
+      <c r="E1488" s="2" t="n"/>
+    </row>
+    <row r="1489">
+      <c r="E1489" s="2" t="n"/>
+    </row>
+    <row r="1490">
+      <c r="E1490" s="2" t="n"/>
+    </row>
+    <row r="1491">
+      <c r="E1491" s="2" t="n"/>
+    </row>
+    <row r="1492">
+      <c r="E1492" s="2" t="n"/>
+    </row>
+    <row r="1493">
+      <c r="E1493" s="2" t="n"/>
+    </row>
+    <row r="1494">
+      <c r="E1494" s="2" t="n"/>
+    </row>
+    <row r="1495">
+      <c r="E1495" s="2" t="n"/>
+    </row>
+    <row r="1496">
+      <c r="E1496" s="2" t="n"/>
+    </row>
+    <row r="1497">
+      <c r="E1497" s="2" t="n"/>
+    </row>
+    <row r="1498">
+      <c r="E1498" s="2" t="n"/>
+    </row>
+    <row r="1499">
+      <c r="E1499" s="2" t="n"/>
+    </row>
+    <row r="1500">
+      <c r="E1500" s="2" t="n"/>
+    </row>
+    <row r="1501">
+      <c r="E1501" s="2" t="n"/>
+    </row>
+    <row r="1502">
+      <c r="E1502" s="2" t="n"/>
+    </row>
+    <row r="1503">
+      <c r="E1503" s="2" t="n"/>
+    </row>
+    <row r="1504">
+      <c r="E1504" s="2" t="n"/>
+    </row>
+    <row r="1505">
+      <c r="E1505" s="2" t="n"/>
+    </row>
+    <row r="1506">
+      <c r="E1506" s="2" t="n"/>
+    </row>
+    <row r="1507">
+      <c r="E1507" s="2" t="n"/>
+    </row>
+    <row r="1508">
+      <c r="E1508" s="2" t="n"/>
+    </row>
+    <row r="1509">
+      <c r="E1509" s="2" t="n"/>
+    </row>
+    <row r="1510">
+      <c r="E1510" s="2" t="n"/>
+    </row>
+    <row r="1511">
+      <c r="E1511" s="2" t="n"/>
+    </row>
+    <row r="1512">
+      <c r="E1512" s="2" t="n"/>
+    </row>
+    <row r="1513">
+      <c r="E1513" s="2" t="n"/>
+    </row>
+    <row r="1514">
+      <c r="E1514" s="2" t="n"/>
+    </row>
+    <row r="1515">
+      <c r="E1515" s="2" t="n"/>
+    </row>
+    <row r="1516">
+      <c r="E1516" s="2" t="n"/>
+    </row>
+    <row r="1517">
+      <c r="E1517" s="2" t="n"/>
+    </row>
+    <row r="1518">
+      <c r="E1518" s="2" t="n"/>
+    </row>
+    <row r="1519">
+      <c r="E1519" s="2" t="n"/>
+    </row>
+    <row r="1520">
+      <c r="E1520" s="2" t="n"/>
+    </row>
+    <row r="1521">
+      <c r="E1521" s="2" t="n"/>
+    </row>
+    <row r="1522">
+      <c r="E1522" s="2" t="n"/>
+    </row>
+    <row r="1523">
+      <c r="E1523" s="2" t="n"/>
+    </row>
+    <row r="1524">
+      <c r="E1524" s="2" t="n"/>
+    </row>
+    <row r="1525">
+      <c r="E1525" s="2" t="n"/>
+    </row>
+    <row r="1526">
+      <c r="E1526" s="2" t="n"/>
+    </row>
+    <row r="1527">
+      <c r="E1527" s="2" t="n"/>
+    </row>
+    <row r="1528">
+      <c r="E1528" s="2" t="n"/>
+    </row>
+    <row r="1529">
+      <c r="E1529" s="2" t="n"/>
+    </row>
+    <row r="1530">
+      <c r="E1530" s="2" t="n"/>
+    </row>
+    <row r="1531">
+      <c r="E1531" s="2" t="n"/>
+    </row>
+    <row r="1532">
+      <c r="E1532" s="2" t="n"/>
+    </row>
+    <row r="1533">
+      <c r="E1533" s="2" t="n"/>
+    </row>
+    <row r="1534">
+      <c r="E1534" s="2" t="n"/>
+    </row>
+    <row r="1535">
+      <c r="E1535" s="2" t="n"/>
+    </row>
+    <row r="1536">
+      <c r="E1536" s="2" t="n"/>
+    </row>
+    <row r="1537">
+      <c r="E1537" s="2" t="n"/>
+    </row>
+    <row r="1538">
+      <c r="E1538" s="2" t="n"/>
+    </row>
+    <row r="1539">
+      <c r="E1539" s="2" t="n"/>
+    </row>
+    <row r="1540">
+      <c r="E1540" s="2" t="n"/>
+    </row>
+    <row r="1541">
+      <c r="E1541" s="2" t="n"/>
+    </row>
+    <row r="1542">
+      <c r="E1542" s="2" t="n"/>
+    </row>
+    <row r="1543">
+      <c r="E1543" s="2" t="n"/>
+    </row>
+    <row r="1544">
+      <c r="E1544" s="2" t="n"/>
+    </row>
+    <row r="1545">
+      <c r="E1545" s="2" t="n"/>
+    </row>
+    <row r="1546">
+      <c r="E1546" s="2" t="n"/>
+    </row>
+    <row r="1547">
+      <c r="E1547" s="2" t="n"/>
+    </row>
+    <row r="1548">
+      <c r="E1548" s="2" t="n"/>
+    </row>
+    <row r="1549">
+      <c r="E1549" s="2" t="n"/>
+    </row>
+    <row r="1550">
+      <c r="E1550" s="2" t="n"/>
+    </row>
+    <row r="1551">
+      <c r="E1551" s="2" t="n"/>
+    </row>
+    <row r="1552">
+      <c r="E1552" s="2" t="n"/>
+    </row>
+    <row r="1553">
+      <c r="E1553" s="2" t="n"/>
+    </row>
+    <row r="1554">
+      <c r="E1554" s="2" t="n"/>
+    </row>
+    <row r="1555">
+      <c r="E1555" s="2" t="n"/>
+    </row>
+    <row r="1556">
+      <c r="E1556" s="2" t="n"/>
+    </row>
+    <row r="1557">
+      <c r="E1557" s="2" t="n"/>
+    </row>
+    <row r="1558">
+      <c r="E1558" s="2" t="n"/>
+    </row>
+    <row r="1559">
+      <c r="E1559" s="2" t="n"/>
+    </row>
+    <row r="1560">
+      <c r="E1560" s="2" t="n"/>
+    </row>
+    <row r="1561">
+      <c r="E1561" s="2" t="n"/>
+    </row>
+    <row r="1562">
+      <c r="E1562" s="2" t="n"/>
+    </row>
+    <row r="1563">
+      <c r="E1563" s="2" t="n"/>
+    </row>
+    <row r="1564">
+      <c r="E1564" s="2" t="n"/>
+    </row>
+    <row r="1565">
+      <c r="E1565" s="2" t="n"/>
+    </row>
+    <row r="1566">
+      <c r="E1566" s="2" t="n"/>
+    </row>
+    <row r="1567">
+      <c r="E1567" s="2" t="n"/>
+    </row>
+    <row r="1568">
+      <c r="E1568" s="2" t="n"/>
+    </row>
+    <row r="1569">
+      <c r="E1569" s="2" t="n"/>
+    </row>
+    <row r="1570">
+      <c r="E1570" s="2" t="n"/>
+    </row>
+    <row r="1571">
+      <c r="E1571" s="2" t="n"/>
+    </row>
+    <row r="1572">
+      <c r="E1572" s="2" t="n"/>
+    </row>
+    <row r="1573">
+      <c r="E1573" s="2" t="n"/>
+    </row>
+    <row r="1574">
+      <c r="E1574" s="2" t="n"/>
+    </row>
+    <row r="1575">
+      <c r="E1575" s="2" t="n"/>
+    </row>
+    <row r="1576">
+      <c r="E1576" s="2" t="n"/>
+    </row>
+    <row r="1577">
+      <c r="E1577" s="2" t="n"/>
+    </row>
+    <row r="1578">
+      <c r="E1578" s="2" t="n"/>
+    </row>
+    <row r="1579">
+      <c r="E1579" s="2" t="n"/>
+    </row>
+    <row r="1580">
+      <c r="E1580" s="2" t="n"/>
+    </row>
+    <row r="1581">
+      <c r="E1581" s="2" t="n"/>
+    </row>
+    <row r="1582">
+      <c r="E1582" s="2" t="n"/>
+    </row>
+    <row r="1583">
+      <c r="E1583" s="2" t="n"/>
+    </row>
+    <row r="1584">
+      <c r="E1584" s="2" t="n"/>
+    </row>
+    <row r="1585">
+      <c r="E1585" s="2" t="n"/>
+    </row>
+    <row r="1586">
+      <c r="E1586" s="2" t="n"/>
+    </row>
+    <row r="1587">
+      <c r="E1587" s="2" t="n"/>
+    </row>
+    <row r="1588">
+      <c r="E1588" s="2" t="n"/>
+    </row>
+    <row r="1589">
+      <c r="E1589" s="2" t="n"/>
+    </row>
+    <row r="1590">
+      <c r="E1590" s="2" t="n"/>
+    </row>
+    <row r="1591">
+      <c r="E1591" s="2" t="n"/>
+    </row>
+    <row r="1592">
+      <c r="E1592" s="2" t="n"/>
+    </row>
+    <row r="1593">
+      <c r="E1593" s="2" t="n"/>
+    </row>
+    <row r="1594">
+      <c r="E1594" s="2" t="n"/>
+    </row>
+    <row r="1595">
+      <c r="E1595" s="2" t="n"/>
+    </row>
+    <row r="1596">
+      <c r="E1596" s="2" t="n"/>
+    </row>
+    <row r="1597">
+      <c r="E1597" s="2" t="n"/>
+    </row>
+    <row r="1598">
+      <c r="E1598" s="2" t="n"/>
+    </row>
+    <row r="1599">
+      <c r="E1599" s="2" t="n"/>
+    </row>
+    <row r="1600">
+      <c r="E1600" s="2" t="n"/>
+    </row>
+    <row r="1601">
+      <c r="E1601" s="2" t="n"/>
+    </row>
+    <row r="1602">
+      <c r="E1602" s="2" t="n"/>
+    </row>
+    <row r="1603">
+      <c r="E1603" s="2" t="n"/>
+    </row>
+    <row r="1604">
+      <c r="E1604" s="2" t="n"/>
+    </row>
+    <row r="1605">
+      <c r="E1605" s="2" t="n"/>
+    </row>
+    <row r="1606">
+      <c r="E1606" s="2" t="n"/>
+    </row>
+    <row r="1607">
+      <c r="E1607" s="2" t="n"/>
+    </row>
+    <row r="1608">
+      <c r="E1608" s="2" t="n"/>
+    </row>
+    <row r="1609">
+      <c r="E1609" s="2" t="n"/>
+    </row>
+    <row r="1610">
+      <c r="E1610" s="2" t="n"/>
+    </row>
+    <row r="1611">
+      <c r="E1611" s="2" t="n"/>
+    </row>
+    <row r="1612">
+      <c r="E1612" s="2" t="n"/>
+    </row>
+    <row r="1613">
+      <c r="E1613" s="2" t="n"/>
+    </row>
+    <row r="1614">
+      <c r="E1614" s="2" t="n"/>
+    </row>
+    <row r="1615">
+      <c r="E1615" s="2" t="n"/>
+    </row>
+    <row r="1616">
+      <c r="E1616" s="2" t="n"/>
+    </row>
+    <row r="1617">
+      <c r="E1617" s="2" t="n"/>
+    </row>
+    <row r="1618">
+      <c r="E1618" s="2" t="n"/>
+    </row>
+    <row r="1619">
+      <c r="E1619" s="2" t="n"/>
+    </row>
+    <row r="1620">
+      <c r="E1620" s="2" t="n"/>
+    </row>
+    <row r="1621">
+      <c r="E1621" s="2" t="n"/>
+    </row>
+    <row r="1622">
+      <c r="E1622" s="2" t="n"/>
+    </row>
+    <row r="1623">
+      <c r="E1623" s="2" t="n"/>
+    </row>
+    <row r="1624">
+      <c r="E1624" s="2" t="n"/>
+    </row>
+    <row r="1625">
+      <c r="E1625" s="2" t="n"/>
+    </row>
+    <row r="1626">
+      <c r="E1626" s="2" t="n"/>
+    </row>
+    <row r="1627">
+      <c r="E1627" s="2" t="n"/>
+    </row>
+    <row r="1628">
+      <c r="E1628" s="2" t="n"/>
+    </row>
+    <row r="1629">
+      <c r="E1629" s="2" t="n"/>
+    </row>
+    <row r="1630">
+      <c r="E1630" s="2" t="n"/>
+    </row>
+    <row r="1631">
+      <c r="E1631" s="2" t="n"/>
+    </row>
+    <row r="1632">
+      <c r="E1632" s="2" t="n"/>
+    </row>
+    <row r="1633">
+      <c r="E1633" s="2" t="n"/>
+    </row>
+    <row r="1634">
+      <c r="E1634" s="2" t="n"/>
+    </row>
+    <row r="1635">
+      <c r="E1635" s="2" t="n"/>
+    </row>
+    <row r="1636">
+      <c r="E1636" s="2" t="n"/>
+    </row>
+    <row r="1637">
+      <c r="E1637" s="2" t="n"/>
+    </row>
+    <row r="1638">
+      <c r="E1638" s="2" t="n"/>
+    </row>
+    <row r="1639">
+      <c r="E1639" s="2" t="n"/>
+    </row>
+    <row r="1640">
+      <c r="E1640" s="2" t="n"/>
+    </row>
+    <row r="1641">
+      <c r="E1641" s="2" t="n"/>
+    </row>
+    <row r="1642">
+      <c r="E1642" s="2" t="n"/>
+    </row>
+    <row r="1643">
+      <c r="E1643" s="2" t="n"/>
+    </row>
+    <row r="1644">
+      <c r="E1644" s="2" t="n"/>
+    </row>
+    <row r="1645">
+      <c r="E1645" s="2" t="n"/>
+    </row>
+    <row r="1646">
+      <c r="E1646" s="2" t="n"/>
+    </row>
+    <row r="1647">
+      <c r="E1647" s="2" t="n"/>
+    </row>
+    <row r="1648">
+      <c r="E1648" s="2" t="n"/>
+    </row>
+    <row r="1649">
+      <c r="E1649" s="2" t="n"/>
+    </row>
+    <row r="1650">
+      <c r="E1650" s="2" t="n"/>
+    </row>
+    <row r="1651">
+      <c r="E1651" s="2" t="n"/>
+    </row>
+    <row r="1652">
+      <c r="E1652" s="2" t="n"/>
+    </row>
+    <row r="1653">
+      <c r="E1653" s="2" t="n"/>
+    </row>
+    <row r="1654">
+      <c r="E1654" s="2" t="n"/>
+    </row>
+    <row r="1655">
+      <c r="E1655" s="2" t="n"/>
+    </row>
+    <row r="1656">
+      <c r="E1656" s="2" t="n"/>
+    </row>
+    <row r="1657">
+      <c r="E1657" s="2" t="n"/>
+    </row>
+    <row r="1658">
+      <c r="E1658" s="2" t="n"/>
+    </row>
+    <row r="1659">
+      <c r="E1659" s="2" t="n"/>
+    </row>
+    <row r="1660">
+      <c r="E1660" s="2" t="n"/>
+    </row>
+    <row r="1661">
+      <c r="E1661" s="2" t="n"/>
+    </row>
+    <row r="1662">
+      <c r="E1662" s="2" t="n"/>
+    </row>
+    <row r="1663">
+      <c r="E1663" s="2" t="n"/>
+    </row>
+    <row r="1664">
+      <c r="E1664" s="2" t="n"/>
+    </row>
+    <row r="1665">
+      <c r="E1665" s="2" t="n"/>
+    </row>
+    <row r="1666">
+      <c r="E1666" s="2" t="n"/>
+    </row>
+    <row r="1667">
+      <c r="E1667" s="2" t="n"/>
+    </row>
+    <row r="1668">
+      <c r="E1668" s="2" t="n"/>
+    </row>
+    <row r="1669">
+      <c r="E1669" s="2" t="n"/>
+    </row>
+    <row r="1670">
+      <c r="E1670" s="2" t="n"/>
+    </row>
+    <row r="1671">
+      <c r="E1671" s="2" t="n"/>
+    </row>
+    <row r="1672">
+      <c r="E1672" s="2" t="n"/>
+    </row>
+    <row r="1673">
+      <c r="E1673" s="2" t="n"/>
+    </row>
+    <row r="1674">
+      <c r="E1674" s="2" t="n"/>
+    </row>
+    <row r="1675">
+      <c r="E1675" s="2" t="n"/>
+    </row>
+    <row r="1676">
+      <c r="E1676" s="2" t="n"/>
+    </row>
+    <row r="1677">
+      <c r="E1677" s="2" t="n"/>
+    </row>
+    <row r="1678">
+      <c r="E1678" s="2" t="n"/>
+    </row>
+    <row r="1679">
+      <c r="E1679" s="2" t="n"/>
+    </row>
+    <row r="1680">
+      <c r="E1680" s="2" t="n"/>
+    </row>
+    <row r="1681">
+      <c r="E1681" s="2" t="n"/>
+    </row>
+    <row r="1682">
+      <c r="E1682" s="2" t="n"/>
+    </row>
+    <row r="1683">
+      <c r="E1683" s="2" t="n"/>
+    </row>
+    <row r="1684">
+      <c r="E1684" s="2" t="n"/>
+    </row>
+    <row r="1685">
+      <c r="E1685" s="2" t="n"/>
+    </row>
+    <row r="1686">
+      <c r="E1686" s="2" t="n"/>
+    </row>
+    <row r="1687">
+      <c r="E1687" s="2" t="n"/>
+    </row>
+    <row r="1688">
+      <c r="E1688" s="2" t="n"/>
+    </row>
+    <row r="1689">
+      <c r="E1689" s="2" t="n"/>
+    </row>
+    <row r="1690">
+      <c r="E1690" s="2" t="n"/>
+    </row>
+    <row r="1691">
+      <c r="E1691" s="2" t="n"/>
+    </row>
+    <row r="1692">
+      <c r="E1692" s="2" t="n"/>
+    </row>
+    <row r="1693">
+      <c r="E1693" s="2" t="n"/>
+    </row>
+    <row r="1694">
+      <c r="E1694" s="2" t="n"/>
+    </row>
+    <row r="1695">
+      <c r="E1695" s="2" t="n"/>
+    </row>
+    <row r="1696">
+      <c r="E1696" s="2" t="n"/>
+    </row>
+    <row r="1697">
+      <c r="E1697" s="2" t="n"/>
+    </row>
+    <row r="1698">
+      <c r="E1698" s="2" t="n"/>
+    </row>
+    <row r="1699">
+      <c r="E1699" s="2" t="n"/>
+    </row>
+    <row r="1700">
+      <c r="E1700" s="2" t="n"/>
+    </row>
+    <row r="1701">
+      <c r="E1701" s="2" t="n"/>
+    </row>
+    <row r="1702">
+      <c r="E1702" s="2" t="n"/>
+    </row>
+    <row r="1703">
+      <c r="E1703" s="2" t="n"/>
+    </row>
+    <row r="1704">
+      <c r="E1704" s="2" t="n"/>
+    </row>
+    <row r="1705">
+      <c r="E1705" s="2" t="n"/>
+    </row>
+    <row r="1706">
+      <c r="E1706" s="2" t="n"/>
+    </row>
+    <row r="1707">
+      <c r="E1707" s="2" t="n"/>
+    </row>
+    <row r="1708">
+      <c r="E1708" s="2" t="n"/>
+    </row>
+    <row r="1709">
+      <c r="E1709" s="2" t="n"/>
+    </row>
+    <row r="1710">
+      <c r="E1710" s="2" t="n"/>
+    </row>
+    <row r="1711">
+      <c r="E1711" s="2" t="n"/>
+    </row>
+    <row r="1712">
+      <c r="E1712" s="2" t="n"/>
+    </row>
+    <row r="1713">
+      <c r="E1713" s="2" t="n"/>
+    </row>
+    <row r="1714">
+      <c r="E1714" s="2" t="n"/>
+    </row>
+    <row r="1715">
+      <c r="E1715" s="2" t="n"/>
+    </row>
+    <row r="1716">
+      <c r="E1716" s="2" t="n"/>
+    </row>
+    <row r="1717">
+      <c r="E1717" s="2" t="n"/>
+    </row>
+    <row r="1718">
+      <c r="E1718" s="2" t="n"/>
+    </row>
+    <row r="1719">
+      <c r="E1719" s="2" t="n"/>
+    </row>
+    <row r="1720">
+      <c r="E1720" s="2" t="n"/>
+    </row>
+    <row r="1721">
+      <c r="E1721" s="2" t="n"/>
+    </row>
+    <row r="1722">
+      <c r="E1722" s="2" t="n"/>
+    </row>
+    <row r="1723">
+      <c r="E1723" s="2" t="n"/>
+    </row>
+    <row r="1724">
+      <c r="E1724" s="2" t="n"/>
+    </row>
+    <row r="1725">
+      <c r="E1725" s="2" t="n"/>
+    </row>
+    <row r="1726">
+      <c r="E1726" s="2" t="n"/>
+    </row>
+    <row r="1727">
+      <c r="E1727" s="2" t="n"/>
+    </row>
+    <row r="1728">
+      <c r="E1728" s="2" t="n"/>
+    </row>
+    <row r="1729">
+      <c r="E1729" s="2" t="n"/>
+    </row>
+    <row r="1730">
+      <c r="E1730" s="2" t="n"/>
+    </row>
+    <row r="1731">
+      <c r="E1731" s="2" t="n"/>
+    </row>
+    <row r="1732">
+      <c r="E1732" s="2" t="n"/>
+    </row>
+    <row r="1733">
+      <c r="E1733" s="2" t="n"/>
+    </row>
+    <row r="1734">
+      <c r="E1734" s="2" t="n"/>
+    </row>
+    <row r="1735">
+      <c r="E1735" s="2" t="n"/>
+    </row>
+    <row r="1736">
+      <c r="E1736" s="2" t="n"/>
+    </row>
+    <row r="1737">
+      <c r="E1737" s="2" t="n"/>
+    </row>
+    <row r="1738">
+      <c r="E1738" s="2" t="n"/>
+    </row>
+    <row r="1739">
+      <c r="E1739" s="2" t="n"/>
+    </row>
+    <row r="1740">
+      <c r="E1740" s="2" t="n"/>
+    </row>
+    <row r="1741">
+      <c r="E1741" s="2" t="n"/>
+    </row>
+    <row r="1742">
+      <c r="E1742" s="2" t="n"/>
+    </row>
+    <row r="1743">
+      <c r="E1743" s="2" t="n"/>
+    </row>
+    <row r="1744">
+      <c r="E1744" s="2" t="n"/>
+    </row>
+    <row r="1745">
+      <c r="E1745" s="2" t="n"/>
+    </row>
+    <row r="1746">
+      <c r="E1746" s="2" t="n"/>
+    </row>
+    <row r="1747">
+      <c r="E1747" s="2" t="n"/>
+    </row>
+    <row r="1748">
+      <c r="E1748" s="2" t="n"/>
+    </row>
+    <row r="1749">
+      <c r="E1749" s="2" t="n"/>
+    </row>
+    <row r="1750">
+      <c r="E1750" s="2" t="n"/>
+    </row>
+    <row r="1751">
+      <c r="E1751" s="2" t="n"/>
+    </row>
+    <row r="1752">
+      <c r="E1752" s="2" t="n"/>
+    </row>
+    <row r="1753">
+      <c r="E1753" s="2" t="n"/>
+    </row>
+    <row r="1754">
+      <c r="E1754" s="2" t="n"/>
+    </row>
+    <row r="1755">
+      <c r="E1755" s="2" t="n"/>
+    </row>
+    <row r="1756">
+      <c r="E1756" s="2" t="n"/>
+    </row>
+    <row r="1757">
+      <c r="E1757" s="2" t="n"/>
+    </row>
+    <row r="1758">
+      <c r="E1758" s="2" t="n"/>
+    </row>
+    <row r="1759">
+      <c r="E1759" s="2" t="n"/>
+    </row>
+    <row r="1760">
+      <c r="E1760" s="2" t="n"/>
+    </row>
+    <row r="1761">
+      <c r="E1761" s="2" t="n"/>
+    </row>
+    <row r="1762">
+      <c r="E1762" s="2" t="n"/>
+    </row>
+    <row r="1763">
+      <c r="E1763" s="2" t="n"/>
+    </row>
+    <row r="1764">
+      <c r="E1764" s="2" t="n"/>
+    </row>
+    <row r="1765">
+      <c r="E1765" s="2" t="n"/>
+    </row>
+    <row r="1766">
+      <c r="E1766" s="2" t="n"/>
+    </row>
+    <row r="1767">
+      <c r="E1767" s="2" t="n"/>
+    </row>
+    <row r="1768">
+      <c r="E1768" s="2" t="n"/>
+    </row>
+    <row r="1769">
+      <c r="E1769" s="2" t="n"/>
+    </row>
+    <row r="1770">
+      <c r="E1770" s="2" t="n"/>
+    </row>
+    <row r="1771">
+      <c r="E1771" s="2" t="n"/>
+    </row>
+    <row r="1772">
+      <c r="E1772" s="2" t="n"/>
+    </row>
+    <row r="1773">
+      <c r="E1773" s="2" t="n"/>
+    </row>
+    <row r="1774">
+      <c r="E1774" s="2" t="n"/>
+    </row>
+    <row r="1775">
+      <c r="E1775" s="2" t="n"/>
+    </row>
+    <row r="1776">
+      <c r="E1776" s="2" t="n"/>
+    </row>
+    <row r="1777">
+      <c r="E1777" s="2" t="n"/>
+    </row>
+    <row r="1778">
+      <c r="E1778" s="2" t="n"/>
+    </row>
+    <row r="1779">
+      <c r="E1779" s="2" t="n"/>
+    </row>
+    <row r="1780">
+      <c r="E1780" s="2" t="n"/>
+    </row>
+    <row r="1781">
+      <c r="E1781" s="2" t="n"/>
+    </row>
+    <row r="1782">
+      <c r="E1782" s="2" t="n"/>
+    </row>
+    <row r="1783">
+      <c r="E1783" s="2" t="n"/>
+    </row>
+    <row r="1784">
+      <c r="E1784" s="2" t="n"/>
+    </row>
+    <row r="1785">
+      <c r="E1785" s="2" t="n"/>
+    </row>
+    <row r="1786">
+      <c r="E1786" s="2" t="n"/>
+    </row>
+    <row r="1787">
+      <c r="E1787" s="2" t="n"/>
+    </row>
+    <row r="1788">
+      <c r="E1788" s="2" t="n"/>
+    </row>
+    <row r="1789">
+      <c r="E1789" s="2" t="n"/>
+    </row>
+    <row r="1790">
+      <c r="E1790" s="2" t="n"/>
+    </row>
+    <row r="1791">
+      <c r="E1791" s="2" t="n"/>
+    </row>
+    <row r="1792">
+      <c r="E1792" s="2" t="n"/>
+    </row>
+    <row r="1793">
+      <c r="E1793" s="2" t="n"/>
+    </row>
+    <row r="1794">
+      <c r="E1794" s="2" t="n"/>
+    </row>
+    <row r="1795">
+      <c r="E1795" s="2" t="n"/>
+    </row>
+    <row r="1796">
+      <c r="E1796" s="2" t="n"/>
+    </row>
+    <row r="1797">
+      <c r="E1797" s="2" t="n"/>
+    </row>
+    <row r="1798">
+      <c r="E1798" s="2" t="n"/>
+    </row>
+    <row r="1799">
+      <c r="E1799" s="2" t="n"/>
+    </row>
+    <row r="1800">
+      <c r="E1800" s="2" t="n"/>
+    </row>
+    <row r="1801">
+      <c r="E1801" s="2" t="n"/>
+    </row>
+    <row r="1802">
+      <c r="E1802" s="2" t="n"/>
+    </row>
+    <row r="1803">
+      <c r="E1803" s="2" t="n"/>
+    </row>
+    <row r="1804">
+      <c r="E1804" s="2" t="n"/>
+    </row>
+    <row r="1805">
+      <c r="E1805" s="2" t="n"/>
+    </row>
+    <row r="1806">
+      <c r="E1806" s="2" t="n"/>
+    </row>
+    <row r="1807">
+      <c r="E1807" s="2" t="n"/>
+    </row>
+    <row r="1808">
+      <c r="E1808" s="2" t="n"/>
+    </row>
+    <row r="1809">
+      <c r="E1809" s="2" t="n"/>
+    </row>
+    <row r="1810">
+      <c r="E1810" s="2" t="n"/>
+    </row>
+    <row r="1811">
+      <c r="E1811" s="2" t="n"/>
+    </row>
+    <row r="1812">
+      <c r="E1812" s="2" t="n"/>
+    </row>
+    <row r="1813">
+      <c r="E1813" s="2" t="n"/>
+    </row>
+    <row r="1814">
+      <c r="E1814" s="2" t="n"/>
+    </row>
+    <row r="1815">
+      <c r="E1815" s="2" t="n"/>
+    </row>
+    <row r="1816">
+      <c r="E1816" s="2" t="n"/>
+    </row>
+    <row r="1817">
+      <c r="E1817" s="2" t="n"/>
+    </row>
+    <row r="1818">
+      <c r="E1818" s="2" t="n"/>
+    </row>
+    <row r="1819">
+      <c r="E1819" s="2" t="n"/>
+    </row>
+    <row r="1820">
+      <c r="E1820" s="2" t="n"/>
+    </row>
+    <row r="1821">
+      <c r="E1821" s="2" t="n"/>
+    </row>
+    <row r="1822">
+      <c r="E1822" s="2" t="n"/>
+    </row>
+    <row r="1823">
+      <c r="E1823" s="2" t="n"/>
+    </row>
+    <row r="1824">
+      <c r="E1824" s="2" t="n"/>
+    </row>
+    <row r="1825">
+      <c r="E1825" s="2" t="n"/>
+    </row>
+    <row r="1826">
+      <c r="E1826" s="2" t="n"/>
+    </row>
+    <row r="1827">
+      <c r="E1827" s="2" t="n"/>
+    </row>
+    <row r="1828">
+      <c r="E1828" s="2" t="n"/>
+    </row>
+    <row r="1829">
+      <c r="E1829" s="2" t="n"/>
+    </row>
+    <row r="1830">
+      <c r="E1830" s="2" t="n"/>
+    </row>
+    <row r="1831">
+      <c r="E1831" s="2" t="n"/>
+    </row>
+    <row r="1832">
+      <c r="E1832" s="2" t="n"/>
+    </row>
+    <row r="1833">
+      <c r="E1833" s="2" t="n"/>
+    </row>
+    <row r="1834">
+      <c r="E1834" s="2" t="n"/>
+    </row>
+    <row r="1835">
+      <c r="E1835" s="2" t="n"/>
+    </row>
+    <row r="1836">
+      <c r="E1836" s="2" t="n"/>
+    </row>
+    <row r="1837">
+      <c r="E1837" s="2" t="n"/>
+    </row>
+    <row r="1838">
+      <c r="E1838" s="2" t="n"/>
+    </row>
+    <row r="1839">
+      <c r="E1839" s="2" t="n"/>
+    </row>
+    <row r="1840">
+      <c r="E1840" s="2" t="n"/>
+    </row>
+    <row r="1841">
+      <c r="E1841" s="2" t="n"/>
+    </row>
+    <row r="1842">
+      <c r="E1842" s="2" t="n"/>
+    </row>
+    <row r="1843">
+      <c r="E1843" s="2" t="n"/>
+    </row>
+    <row r="1844">
+      <c r="E1844" s="2" t="n"/>
+    </row>
+    <row r="1845">
+      <c r="E1845" s="2" t="n"/>
+    </row>
+    <row r="1846">
+      <c r="E1846" s="2" t="n"/>
+    </row>
+    <row r="1847">
+      <c r="E1847" s="2" t="n"/>
+    </row>
+    <row r="1848">
+      <c r="E1848" s="2" t="n"/>
+    </row>
+    <row r="1849">
+      <c r="E1849" s="2" t="n"/>
+    </row>
+    <row r="1850">
+      <c r="E1850" s="2" t="n"/>
+    </row>
+    <row r="1851">
+      <c r="E1851" s="2" t="n"/>
+    </row>
+    <row r="1852">
+      <c r="E1852" s="2" t="n"/>
+    </row>
+    <row r="1853">
+      <c r="E1853" s="2" t="n"/>
+    </row>
+    <row r="1854">
+      <c r="E1854" s="2" t="n"/>
+    </row>
+    <row r="1855">
+      <c r="E1855" s="2" t="n"/>
+    </row>
+    <row r="1856">
+      <c r="E1856" s="2" t="n"/>
+    </row>
+    <row r="1857">
+      <c r="E1857" s="2" t="n"/>
+    </row>
+    <row r="1858">
+      <c r="E1858" s="2" t="n"/>
+    </row>
+    <row r="1859">
+      <c r="E1859" s="2" t="n"/>
+    </row>
+    <row r="1860">
+      <c r="E1860" s="2" t="n"/>
+    </row>
+    <row r="1861">
+      <c r="E1861" s="2" t="n"/>
+    </row>
+    <row r="1862">
+      <c r="E1862" s="2" t="n"/>
+    </row>
+    <row r="1863">
+      <c r="E1863" s="2" t="n"/>
+    </row>
+    <row r="1864">
+      <c r="E1864" s="2" t="n"/>
+    </row>
+    <row r="1865">
+      <c r="E1865" s="2" t="n"/>
+    </row>
+    <row r="1866">
+      <c r="E1866" s="2" t="n"/>
+    </row>
+    <row r="1867">
+      <c r="E1867" s="2" t="n"/>
+    </row>
+    <row r="1868">
+      <c r="E1868" s="2" t="n"/>
+    </row>
+    <row r="1869">
+      <c r="E1869" s="2" t="n"/>
+    </row>
+    <row r="1870">
+      <c r="E1870" s="2" t="n"/>
+    </row>
+    <row r="1871">
+      <c r="E1871" s="2" t="n"/>
+    </row>
+    <row r="1872">
+      <c r="E1872" s="2" t="n"/>
+    </row>
+    <row r="1873">
+      <c r="E1873" s="2" t="n"/>
+    </row>
+    <row r="1874">
+      <c r="E1874" s="2" t="n"/>
+    </row>
+    <row r="1875">
+      <c r="E1875" s="2" t="n"/>
+    </row>
+    <row r="1876">
+      <c r="E1876" s="2" t="n"/>
+    </row>
+    <row r="1877">
+      <c r="E1877" s="2" t="n"/>
+    </row>
+    <row r="1878">
+      <c r="E1878" s="2" t="n"/>
+    </row>
+    <row r="1879">
+      <c r="E1879" s="2" t="n"/>
+    </row>
+    <row r="1880">
+      <c r="E1880" s="2" t="n"/>
+    </row>
+    <row r="1881">
+      <c r="E1881" s="2" t="n"/>
+    </row>
+    <row r="1882">
+      <c r="E1882" s="2" t="n"/>
+    </row>
+    <row r="1883">
+      <c r="E1883" s="2" t="n"/>
+    </row>
+    <row r="1884">
+      <c r="E1884" s="2" t="n"/>
+    </row>
+    <row r="1885">
+      <c r="E1885" s="2" t="n"/>
+    </row>
+    <row r="1886">
+      <c r="E1886" s="2" t="n"/>
+    </row>
+    <row r="1887">
+      <c r="E1887" s="2" t="n"/>
+    </row>
+    <row r="1888">
+      <c r="E1888" s="2" t="n"/>
+    </row>
+    <row r="1889">
+      <c r="E1889" s="2" t="n"/>
+    </row>
+    <row r="1890">
+      <c r="E1890" s="2" t="n"/>
+    </row>
+    <row r="1891">
+      <c r="E1891" s="2" t="n"/>
+    </row>
+    <row r="1892">
+      <c r="E1892" s="2" t="n"/>
+    </row>
+    <row r="1893">
+      <c r="E1893" s="2" t="n"/>
+    </row>
+    <row r="1894">
+      <c r="E1894" s="2" t="n"/>
+    </row>
+    <row r="1895">
+      <c r="E1895" s="2" t="n"/>
+    </row>
+    <row r="1896">
+      <c r="E1896" s="2" t="n"/>
+    </row>
+    <row r="1897">
+      <c r="E1897" s="2" t="n"/>
+    </row>
+    <row r="1898">
+      <c r="E1898" s="2" t="n"/>
+    </row>
+    <row r="1899">
+      <c r="E1899" s="2" t="n"/>
+    </row>
+    <row r="1900">
+      <c r="E1900" s="2" t="n"/>
+    </row>
+    <row r="1901">
+      <c r="E1901" s="2" t="n"/>
+    </row>
+    <row r="1902">
+      <c r="E1902" s="2" t="n"/>
+    </row>
+    <row r="1903">
+      <c r="E1903" s="2" t="n"/>
+    </row>
+    <row r="1904">
+      <c r="E1904" s="2" t="n"/>
+    </row>
+    <row r="1905">
+      <c r="E1905" s="2" t="n"/>
+    </row>
+    <row r="1906">
+      <c r="E1906" s="2" t="n"/>
+    </row>
+    <row r="1907">
+      <c r="E1907" s="2" t="n"/>
+    </row>
+    <row r="1908">
+      <c r="E1908" s="2" t="n"/>
+    </row>
+    <row r="1909">
+      <c r="E1909" s="2" t="n"/>
+    </row>
+    <row r="1910">
+      <c r="E1910" s="2" t="n"/>
+    </row>
+    <row r="1911">
+      <c r="E1911" s="2" t="n"/>
+    </row>
+    <row r="1912">
+      <c r="E1912" s="2" t="n"/>
+    </row>
+    <row r="1913">
+      <c r="E1913" s="2" t="n"/>
+    </row>
+    <row r="1914">
+      <c r="E1914" s="2" t="n"/>
+    </row>
+    <row r="1915">
+      <c r="E1915" s="2" t="n"/>
+    </row>
+    <row r="1916">
+      <c r="E1916" s="2" t="n"/>
+    </row>
+    <row r="1917">
+      <c r="E1917" s="2" t="n"/>
+    </row>
+    <row r="1918">
+      <c r="E1918" s="2" t="n"/>
+    </row>
+    <row r="1919">
+      <c r="E1919" s="2" t="n"/>
+    </row>
+    <row r="1920">
+      <c r="E1920" s="2" t="n"/>
+    </row>
+    <row r="1921">
+      <c r="E1921" s="2" t="n"/>
+    </row>
+    <row r="1922">
+      <c r="E1922" s="2" t="n"/>
+    </row>
+    <row r="1923">
+      <c r="E1923" s="2" t="n"/>
+    </row>
+    <row r="1924">
+      <c r="E1924" s="2" t="n"/>
+    </row>
+    <row r="1925">
+      <c r="E1925" s="2" t="n"/>
+    </row>
+    <row r="1926">
+      <c r="E1926" s="2" t="n"/>
+    </row>
+    <row r="1927">
+      <c r="E1927" s="2" t="n"/>
+    </row>
+    <row r="1928">
+      <c r="E1928" s="2" t="n"/>
+    </row>
+    <row r="1929">
+      <c r="E1929" s="2" t="n"/>
+    </row>
+    <row r="1930">
+      <c r="E1930" s="2" t="n"/>
+    </row>
+    <row r="1931">
+      <c r="E1931" s="2" t="n"/>
+    </row>
+    <row r="1932">
+      <c r="E1932" s="2" t="n"/>
+    </row>
+    <row r="1933">
+      <c r="E1933" s="2" t="n"/>
+    </row>
+    <row r="1934">
+      <c r="E1934" s="2" t="n"/>
+    </row>
+    <row r="1935">
+      <c r="E1935" s="2" t="n"/>
+    </row>
+    <row r="1936">
+      <c r="E1936" s="2" t="n"/>
+    </row>
+    <row r="1937">
+      <c r="E1937" s="2" t="n"/>
+    </row>
+    <row r="1938">
+      <c r="E1938" s="2" t="n"/>
+    </row>
+    <row r="1939">
+      <c r="E1939" s="2" t="n"/>
+    </row>
+    <row r="1940">
+      <c r="E1940" s="2" t="n"/>
+    </row>
+    <row r="1941">
+      <c r="E1941" s="2" t="n"/>
+    </row>
+    <row r="1942">
+      <c r="E1942" s="2" t="n"/>
+    </row>
+    <row r="1943">
+      <c r="E1943" s="2" t="n"/>
+    </row>
+    <row r="1944">
+      <c r="E1944" s="2" t="n"/>
+    </row>
+    <row r="1945">
+      <c r="E1945" s="2" t="n"/>
+    </row>
+    <row r="1946">
+      <c r="E1946" s="2" t="n"/>
+    </row>
+    <row r="1947">
+      <c r="E1947" s="2" t="n"/>
+    </row>
+    <row r="1948">
+      <c r="E1948" s="2" t="n"/>
+    </row>
+    <row r="1949">
+      <c r="E1949" s="2" t="n"/>
+    </row>
+    <row r="1950">
+      <c r="E1950" s="2" t="n"/>
+    </row>
+    <row r="1951">
+      <c r="E1951" s="2" t="n"/>
+    </row>
+    <row r="1952">
+      <c r="E1952" s="2" t="n"/>
+    </row>
+    <row r="1953">
+      <c r="E1953" s="2" t="n"/>
+    </row>
+    <row r="1954">
+      <c r="E1954" s="2" t="n"/>
+    </row>
+    <row r="1955">
+      <c r="E1955" s="2" t="n"/>
+    </row>
+    <row r="1956">
+      <c r="E1956" s="2" t="n"/>
+    </row>
+    <row r="1957">
+      <c r="E1957" s="2" t="n"/>
+    </row>
+    <row r="1958">
+      <c r="E1958" s="2" t="n"/>
+    </row>
+    <row r="1959">
+      <c r="E1959" s="2" t="n"/>
+    </row>
+    <row r="1960">
+      <c r="E1960" s="2" t="n"/>
+    </row>
+    <row r="1961">
+      <c r="E1961" s="2" t="n"/>
+    </row>
+    <row r="1962">
+      <c r="E1962" s="2" t="n"/>
+    </row>
+    <row r="1963">
+      <c r="E1963" s="2" t="n"/>
+    </row>
+    <row r="1964">
+      <c r="E1964" s="2" t="n"/>
+    </row>
+    <row r="1965">
+      <c r="E1965" s="2" t="n"/>
+    </row>
+    <row r="1966">
+      <c r="E1966" s="2" t="n"/>
+    </row>
+    <row r="1967">
+      <c r="E1967" s="2" t="n"/>
+    </row>
+    <row r="1968">
+      <c r="E1968" s="2" t="n"/>
+    </row>
+    <row r="1969">
+      <c r="E1969" s="2" t="n"/>
+    </row>
+    <row r="1970">
+      <c r="E1970" s="2" t="n"/>
+    </row>
+    <row r="1971">
+      <c r="E1971" s="2" t="n"/>
+    </row>
+    <row r="1972">
+      <c r="E1972" s="2" t="n"/>
+    </row>
+    <row r="1973">
+      <c r="E1973" s="2" t="n"/>
+    </row>
+    <row r="1974">
+      <c r="E1974" s="2" t="n"/>
+    </row>
+    <row r="1975">
+      <c r="E1975" s="2" t="n"/>
+    </row>
+    <row r="1976">
+      <c r="E1976" s="2" t="n"/>
+    </row>
+    <row r="1977">
+      <c r="E1977" s="2" t="n"/>
+    </row>
+    <row r="1978">
+      <c r="E1978" s="2" t="n"/>
+    </row>
+    <row r="1979">
+      <c r="E1979" s="2" t="n"/>
+    </row>
+    <row r="1980">
+      <c r="E1980" s="2" t="n"/>
+    </row>
+    <row r="1981">
+      <c r="E1981" s="2" t="n"/>
+    </row>
+    <row r="1982">
+      <c r="E1982" s="2" t="n"/>
+    </row>
+    <row r="1983">
+      <c r="E1983" s="2" t="n"/>
+    </row>
+    <row r="1984">
+      <c r="E1984" s="2" t="n"/>
+    </row>
+    <row r="1985">
+      <c r="E1985" s="2" t="n"/>
+    </row>
+    <row r="1986">
+      <c r="E1986" s="2" t="n"/>
+    </row>
+    <row r="1987">
+      <c r="E1987" s="2" t="n"/>
+    </row>
+    <row r="1988">
+      <c r="E1988" s="2" t="n"/>
+    </row>
+    <row r="1989">
+      <c r="E1989" s="2" t="n"/>
+    </row>
+    <row r="1990">
+      <c r="E1990" s="2" t="n"/>
+    </row>
+    <row r="1991">
+      <c r="E1991" s="2" t="n"/>
+    </row>
+    <row r="1992">
+      <c r="E1992" s="2" t="n"/>
+    </row>
+    <row r="1993">
+      <c r="E1993" s="2" t="n"/>
+    </row>
+    <row r="1994">
+      <c r="E1994" s="2" t="n"/>
+    </row>
+    <row r="1995">
+      <c r="E1995" s="2" t="n"/>
+    </row>
+    <row r="1996">
+      <c r="E1996" s="2" t="n"/>
+    </row>
+    <row r="1997">
+      <c r="E1997" s="2" t="n"/>
+    </row>
+    <row r="1998">
+      <c r="E1998" s="2" t="n"/>
+    </row>
+    <row r="1999">
+      <c r="E1999" s="2" t="n"/>
+    </row>
+    <row r="2000">
+      <c r="E2000" s="2" t="n"/>
+    </row>
+    <row r="2001">
+      <c r="E2001" s="2" t="n"/>
+    </row>
+    <row r="2002">
+      <c r="E2002" s="2" t="n"/>
+    </row>
+    <row r="2003">
+      <c r="E2003" s="2" t="n"/>
+    </row>
+    <row r="2004">
+      <c r="E2004" s="2" t="n"/>
+    </row>
+    <row r="2005">
+      <c r="E2005" s="2" t="n"/>
+    </row>
+    <row r="2006">
+      <c r="E2006" s="2" t="n"/>
+    </row>
+    <row r="2007">
+      <c r="E2007" s="2" t="n"/>
+    </row>
+    <row r="2008">
+      <c r="E2008" s="2" t="n"/>
+    </row>
+    <row r="2009">
+      <c r="E2009" s="2" t="n"/>
+    </row>
+    <row r="2010">
+      <c r="E2010" s="2" t="n"/>
+    </row>
+    <row r="2011">
+      <c r="E2011" s="2" t="n"/>
+    </row>
+    <row r="2012">
+      <c r="E2012" s="2" t="n"/>
+    </row>
+    <row r="2013">
+      <c r="E2013" s="2" t="n"/>
+    </row>
+    <row r="2014">
+      <c r="E2014" s="2" t="n"/>
+    </row>
+    <row r="2015">
+      <c r="E2015" s="2" t="n"/>
+    </row>
+    <row r="2016">
+      <c r="E2016" s="2" t="n"/>
+    </row>
+    <row r="2017">
+      <c r="E2017" s="2" t="n"/>
+    </row>
+    <row r="2018">
+      <c r="E2018" s="2" t="n"/>
+    </row>
+    <row r="2019">
+      <c r="E2019" s="2" t="n"/>
+    </row>
+    <row r="2020">
+      <c r="E2020" s="2" t="n"/>
+    </row>
+    <row r="2021">
+      <c r="E2021" s="2" t="n"/>
+    </row>
+    <row r="2022">
+      <c r="E2022" s="2" t="n"/>
+    </row>
+    <row r="2023">
+      <c r="E2023" s="2" t="n"/>
+    </row>
+    <row r="2024">
+      <c r="E2024" s="2" t="n"/>
+    </row>
+    <row r="2025">
+      <c r="E2025" s="2" t="n"/>
+    </row>
+    <row r="2026">
+      <c r="E2026" s="2" t="n"/>
+    </row>
+    <row r="2027">
+      <c r="E2027" s="2" t="n"/>
+    </row>
+    <row r="2028">
+      <c r="E2028" s="2" t="n"/>
+    </row>
+    <row r="2029">
+      <c r="E2029" s="2" t="n"/>
+    </row>
+    <row r="2030">
+      <c r="E2030" s="2" t="n"/>
+    </row>
+    <row r="2031">
+      <c r="E2031" s="2" t="n"/>
+    </row>
+    <row r="2032">
+      <c r="E2032" s="2" t="n"/>
+    </row>
+    <row r="2033">
+      <c r="E2033" s="2" t="n"/>
+    </row>
+    <row r="2034">
+      <c r="E2034" s="2" t="n"/>
+    </row>
+    <row r="2035">
+      <c r="E2035" s="2" t="n"/>
+    </row>
+    <row r="2036">
+      <c r="E2036" s="2" t="n"/>
+    </row>
+    <row r="2037">
+      <c r="E2037" s="2" t="n"/>
+    </row>
+    <row r="2038">
+      <c r="E2038" s="2" t="n"/>
+    </row>
+    <row r="2039">
+      <c r="E2039" s="2" t="n"/>
+    </row>
+    <row r="2040">
+      <c r="E2040" s="2" t="n"/>
+    </row>
+    <row r="2041">
+      <c r="E2041" s="2" t="n"/>
+    </row>
+    <row r="2042">
+      <c r="E2042" s="2" t="n"/>
+    </row>
+    <row r="2043">
+      <c r="E2043" s="2" t="n"/>
+    </row>
+    <row r="2044">
+      <c r="E2044" s="2" t="n"/>
+    </row>
+    <row r="2045">
+      <c r="E2045" s="2" t="n"/>
+    </row>
+    <row r="2046">
+      <c r="E2046" s="2" t="n"/>
+    </row>
+    <row r="2047">
+      <c r="E2047" s="2" t="n"/>
+    </row>
+    <row r="2048">
+      <c r="E2048" s="2" t="n"/>
+    </row>
+    <row r="2049">
+      <c r="E2049" s="2" t="n"/>
+    </row>
+    <row r="2050">
+      <c r="E2050" s="2" t="n"/>
+    </row>
+    <row r="2051">
+      <c r="E2051" s="2" t="n"/>
+    </row>
+    <row r="2052">
+      <c r="E2052" s="2" t="n"/>
+    </row>
+    <row r="2053">
+      <c r="E2053" s="2" t="n"/>
+    </row>
+    <row r="2054">
+      <c r="E2054" s="2" t="n"/>
+    </row>
+    <row r="2055">
+      <c r="E2055" s="2" t="n"/>
+    </row>
+    <row r="2056">
+      <c r="E2056" s="2" t="n"/>
+    </row>
+    <row r="2057">
+      <c r="E2057" s="2" t="n"/>
+    </row>
+    <row r="2058">
+      <c r="E2058" s="2" t="n"/>
+    </row>
+    <row r="2059">
+      <c r="E2059" s="2" t="n"/>
+    </row>
+    <row r="2060">
+      <c r="E2060" s="2" t="n"/>
+    </row>
+    <row r="2061">
+      <c r="E2061" s="2" t="n"/>
+    </row>
+    <row r="2062">
+      <c r="E2062" s="2" t="n"/>
+    </row>
+    <row r="2063">
+      <c r="E2063" s="2" t="n"/>
+    </row>
+    <row r="2064">
+      <c r="E2064" s="2" t="n"/>
+    </row>
+    <row r="2065">
+      <c r="E2065" s="2" t="n"/>
+    </row>
+    <row r="2066">
+      <c r="E2066" s="2" t="n"/>
+    </row>
+    <row r="2067">
+      <c r="E2067" s="2" t="n"/>
+    </row>
+    <row r="2068">
+      <c r="E2068" s="2" t="n"/>
+    </row>
+    <row r="2069">
+      <c r="E2069" s="2" t="n"/>
+    </row>
+    <row r="2070">
+      <c r="E2070" s="2" t="n"/>
+    </row>
+    <row r="2071">
+      <c r="E2071" s="2" t="n"/>
+    </row>
+    <row r="2072">
+      <c r="E2072" s="2" t="n"/>
+    </row>
+    <row r="2073">
+      <c r="E2073" s="2" t="n"/>
+    </row>
+    <row r="2074">
+      <c r="E2074" s="2" t="n"/>
+    </row>
+    <row r="2075">
+      <c r="E2075" s="2" t="n"/>
+    </row>
+    <row r="2076">
+      <c r="E2076" s="2" t="n"/>
+    </row>
+    <row r="2077">
+      <c r="E2077" s="2" t="n"/>
+    </row>
+    <row r="2078">
+      <c r="E2078" s="2" t="n"/>
+    </row>
+    <row r="2079">
+      <c r="E2079" s="2" t="n"/>
+    </row>
+    <row r="2080">
+      <c r="E2080" s="2" t="n"/>
+    </row>
+    <row r="2081">
+      <c r="E2081" s="2" t="n"/>
+    </row>
+    <row r="2082">
+      <c r="E2082" s="2" t="n"/>
+    </row>
+    <row r="2083">
+      <c r="E2083" s="2" t="n"/>
+    </row>
+    <row r="2084">
+      <c r="E2084" s="2" t="n"/>
+    </row>
+    <row r="2085">
+      <c r="E2085" s="2" t="n"/>
+    </row>
+    <row r="2086">
+      <c r="E2086" s="2" t="n"/>
+    </row>
+    <row r="2087">
+      <c r="E2087" s="2" t="n"/>
+    </row>
+    <row r="2088">
+      <c r="E2088" s="2" t="n"/>
+    </row>
+    <row r="2089">
+      <c r="E2089" s="2" t="n"/>
+    </row>
+    <row r="2090">
+      <c r="E2090" s="2" t="n"/>
+    </row>
+    <row r="2091">
+      <c r="E2091" s="2" t="n"/>
+    </row>
+    <row r="2092">
+      <c r="E2092" s="2" t="n"/>
+    </row>
+    <row r="2093">
+      <c r="E2093" s="2" t="n"/>
+    </row>
+    <row r="2094">
+      <c r="E2094" s="2" t="n"/>
+    </row>
+    <row r="2095">
+      <c r="E2095" s="2" t="n"/>
+    </row>
+    <row r="2096">
+      <c r="E2096" s="2" t="n"/>
+    </row>
+    <row r="2097">
+      <c r="E2097" s="2" t="n"/>
+    </row>
+    <row r="2098">
+      <c r="E2098" s="2" t="n"/>
+    </row>
+    <row r="2099">
+      <c r="E2099" s="2" t="n"/>
+    </row>
+    <row r="2100">
+      <c r="E2100" s="2" t="n"/>
+    </row>
+    <row r="2101">
+      <c r="E2101" s="2" t="n"/>
+    </row>
+    <row r="2102">
+      <c r="E2102" s="2" t="n"/>
+    </row>
+    <row r="2103">
+      <c r="E2103" s="2" t="n"/>
+    </row>
+    <row r="2104">
+      <c r="E2104" s="2" t="n"/>
+    </row>
+    <row r="2105">
+      <c r="E2105" s="2" t="n"/>
+    </row>
+    <row r="2106">
+      <c r="E2106" s="2" t="n"/>
+    </row>
+    <row r="2107">
+      <c r="E2107" s="2" t="n"/>
+    </row>
+    <row r="2108">
+      <c r="E2108" s="2" t="n"/>
+    </row>
+    <row r="2109">
+      <c r="E2109" s="2" t="n"/>
+    </row>
+    <row r="2110">
+      <c r="E2110" s="2" t="n"/>
+    </row>
+    <row r="2111">
+      <c r="E2111" s="2" t="n"/>
+    </row>
+    <row r="2112">
+      <c r="E2112" s="2" t="n"/>
+    </row>
+    <row r="2113">
+      <c r="E2113" s="2" t="n"/>
+    </row>
+    <row r="2114">
+      <c r="E2114" s="2" t="n"/>
+    </row>
+    <row r="2115">
+      <c r="E2115" s="2" t="n"/>
+    </row>
+    <row r="2116">
+      <c r="E2116" s="2" t="n"/>
+    </row>
+    <row r="2117">
+      <c r="E2117" s="2" t="n"/>
+    </row>
+    <row r="2118">
+      <c r="E2118" s="2" t="n"/>
+    </row>
+    <row r="2119">
+      <c r="E2119" s="2" t="n"/>
+    </row>
+    <row r="2120">
+      <c r="E2120" s="2" t="n"/>
+    </row>
+    <row r="2121">
+      <c r="E2121" s="2" t="n"/>
+    </row>
+    <row r="2122">
+      <c r="E2122" s="2" t="n"/>
+    </row>
+    <row r="2123">
+      <c r="E2123" s="2" t="n"/>
+    </row>
+    <row r="2124">
+      <c r="E2124" s="2" t="n"/>
+    </row>
+    <row r="2125">
+      <c r="E2125" s="2" t="n"/>
+    </row>
+    <row r="2126">
+      <c r="E2126" s="2" t="n"/>
+    </row>
+    <row r="2127">
+      <c r="E2127" s="2" t="n"/>
+    </row>
+    <row r="2128">
+      <c r="E2128" s="2" t="n"/>
+    </row>
+    <row r="2129">
+      <c r="E2129" s="2" t="n"/>
+    </row>
+    <row r="2130">
+      <c r="E2130" s="2" t="n"/>
+    </row>
+    <row r="2131">
+      <c r="E2131" s="2" t="n"/>
+    </row>
+    <row r="2132">
+      <c r="E2132" s="2" t="n"/>
+    </row>
+    <row r="2133">
+      <c r="E2133" s="2" t="n"/>
+    </row>
+    <row r="2134">
+      <c r="E2134" s="2" t="n"/>
+    </row>
+    <row r="2135">
+      <c r="E2135" s="2" t="n"/>
+    </row>
+    <row r="2136">
+      <c r="E2136" s="2" t="n"/>
+    </row>
+    <row r="2137">
+      <c r="E2137" s="2" t="n"/>
+    </row>
+    <row r="2138">
+      <c r="E2138" s="2" t="n"/>
+    </row>
+    <row r="2139">
+      <c r="E2139" s="2" t="n"/>
+    </row>
+    <row r="2140">
+      <c r="E2140" s="2" t="n"/>
+    </row>
+    <row r="2141">
+      <c r="E2141" s="2" t="n"/>
+    </row>
+    <row r="2142">
+      <c r="E2142" s="2" t="n"/>
+    </row>
+    <row r="2143">
+      <c r="E2143" s="2" t="n"/>
+    </row>
+    <row r="2144">
+      <c r="E2144" s="2" t="n"/>
+    </row>
+    <row r="2145">
+      <c r="E2145" s="2" t="n"/>
+    </row>
+    <row r="2146">
+      <c r="E2146" s="2" t="n"/>
+    </row>
+    <row r="2147">
+      <c r="E2147" s="2" t="n"/>
+    </row>
+    <row r="2148">
+      <c r="E2148" s="2" t="n"/>
+    </row>
+    <row r="2149">
+      <c r="E2149" s="2" t="n"/>
+    </row>
+    <row r="2150">
+      <c r="E2150" s="2" t="n"/>
+    </row>
+    <row r="2151">
+      <c r="E2151" s="2" t="n"/>
+    </row>
+    <row r="2152">
+      <c r="E2152" s="2" t="n"/>
+    </row>
+    <row r="2153">
+      <c r="E2153" s="2" t="n"/>
+    </row>
+    <row r="2154">
+      <c r="E2154" s="2" t="n"/>
+    </row>
+    <row r="2155">
+      <c r="E2155" s="2" t="n"/>
+    </row>
+    <row r="2156">
+      <c r="E2156" s="2" t="n"/>
+    </row>
+    <row r="2157">
+      <c r="E2157" s="2" t="n"/>
+    </row>
+    <row r="2158">
+      <c r="E2158" s="2" t="n"/>
+    </row>
+    <row r="2159">
+      <c r="E2159" s="2" t="n"/>
+    </row>
+    <row r="2160">
+      <c r="E2160" s="2" t="n"/>
+    </row>
+    <row r="2161">
+      <c r="E2161" s="2" t="n"/>
+    </row>
+    <row r="2162">
+      <c r="E2162" s="2" t="n"/>
+    </row>
+    <row r="2163">
+      <c r="E2163" s="2" t="n"/>
+    </row>
+    <row r="2164">
+      <c r="E2164" s="2" t="n"/>
+    </row>
+    <row r="2165">
+      <c r="E2165" s="2" t="n"/>
+    </row>
+    <row r="2166">
+      <c r="E2166" s="2" t="n"/>
+    </row>
+    <row r="2167">
+      <c r="E2167" s="2" t="n"/>
+    </row>
+    <row r="2168">
+      <c r="E2168" s="2" t="n"/>
+    </row>
+    <row r="2169">
+      <c r="E2169" s="2" t="n"/>
+    </row>
+    <row r="2170">
+      <c r="E2170" s="2" t="n"/>
+    </row>
+    <row r="2171">
+      <c r="E2171" s="2" t="n"/>
+    </row>
+    <row r="2172">
+      <c r="E2172" s="2" t="n"/>
+    </row>
+    <row r="2173">
+      <c r="E2173" s="2" t="n"/>
+    </row>
+    <row r="2174">
+      <c r="E2174" s="2" t="n"/>
+    </row>
+    <row r="2175">
+      <c r="E2175" s="2" t="n"/>
+    </row>
+    <row r="2176">
+      <c r="E2176" s="2" t="n"/>
+    </row>
+    <row r="2177">
+      <c r="E2177" s="2" t="n"/>
+    </row>
+    <row r="2178">
+      <c r="E2178" s="2" t="n"/>
+    </row>
+    <row r="2179">
+      <c r="E2179" s="2" t="n"/>
+    </row>
+    <row r="2180">
+      <c r="E2180" s="2" t="n"/>
+    </row>
+    <row r="2181">
+      <c r="E2181" s="2" t="n"/>
+    </row>
+    <row r="2182">
+      <c r="E2182" s="2" t="n"/>
+    </row>
+    <row r="2183">
+      <c r="E2183" s="2" t="n"/>
+    </row>
+    <row r="2184">
+      <c r="E2184" s="2" t="n"/>
+    </row>
+    <row r="2185">
+      <c r="E2185" s="2" t="n"/>
+    </row>
+    <row r="2186">
+      <c r="E2186" s="2" t="n"/>
+    </row>
+    <row r="2187">
+      <c r="E2187" s="2" t="n"/>
+    </row>
+    <row r="2188">
+      <c r="E2188" s="2" t="n"/>
+    </row>
+    <row r="2189">
+      <c r="E2189" s="2" t="n"/>
+    </row>
+    <row r="2190">
+      <c r="E2190" s="2" t="n"/>
+    </row>
+    <row r="2191">
+      <c r="E2191" s="2" t="n"/>
+    </row>
+    <row r="2192">
+      <c r="E2192" s="2" t="n"/>
+    </row>
+    <row r="2193">
+      <c r="E2193" s="2" t="n"/>
+    </row>
+    <row r="2194">
+      <c r="E2194" s="2" t="n"/>
+    </row>
+    <row r="2195">
+      <c r="E2195" s="2" t="n"/>
+    </row>
+    <row r="2196">
+      <c r="E2196" s="2" t="n"/>
+    </row>
+    <row r="2197">
+      <c r="E2197" s="2" t="n"/>
+    </row>
+    <row r="2198">
+      <c r="E2198" s="2" t="n"/>
+    </row>
+    <row r="2199">
+      <c r="E2199" s="2" t="n"/>
+    </row>
+    <row r="2200">
+      <c r="E2200" s="2" t="n"/>
+    </row>
+    <row r="2201">
+      <c r="E2201" s="2" t="n"/>
+    </row>
+    <row r="2202">
+      <c r="E2202" s="2" t="n"/>
+    </row>
+    <row r="2203">
+      <c r="E2203" s="2" t="n"/>
+    </row>
+    <row r="2204">
+      <c r="E2204" s="2" t="n"/>
+    </row>
+    <row r="2205">
+      <c r="E2205" s="2" t="n"/>
+    </row>
+    <row r="2206">
+      <c r="E2206" s="2" t="n"/>
+    </row>
+    <row r="2207">
+      <c r="E2207" s="2" t="n"/>
+    </row>
+    <row r="2208">
+      <c r="E2208" s="2" t="n"/>
+    </row>
+    <row r="2209">
+      <c r="E2209" s="2" t="n"/>
+    </row>
+    <row r="2210">
+      <c r="E2210" s="2" t="n"/>
+    </row>
+    <row r="2211">
+      <c r="E2211" s="2" t="n"/>
+    </row>
+    <row r="2212">
+      <c r="E2212" s="2" t="n"/>
+    </row>
+    <row r="2213">
+      <c r="E2213" s="2" t="n"/>
+    </row>
+    <row r="2214">
+      <c r="E2214" s="2" t="n"/>
+    </row>
+    <row r="2215">
+      <c r="E2215" s="2" t="n"/>
+    </row>
+    <row r="2216">
+      <c r="E2216" s="2" t="n"/>
+    </row>
+    <row r="2217">
+      <c r="E2217" s="2" t="n"/>
+    </row>
+    <row r="2218">
+      <c r="E2218" s="2" t="n"/>
+    </row>
+    <row r="2219">
+      <c r="E2219" s="2" t="n"/>
+    </row>
+    <row r="2220">
+      <c r="E2220" s="2" t="n"/>
+    </row>
+    <row r="2221">
+      <c r="E2221" s="2" t="n"/>
+    </row>
+    <row r="2222">
+      <c r="E2222" s="2" t="n"/>
+    </row>
+    <row r="2223">
+      <c r="E2223" s="2" t="n"/>
+    </row>
+    <row r="2224">
+      <c r="E2224" s="2" t="n"/>
+    </row>
+    <row r="2225">
+      <c r="E2225" s="2" t="n"/>
+    </row>
+    <row r="2226">
+      <c r="E2226" s="2" t="n"/>
+    </row>
+    <row r="2227">
+      <c r="E2227" s="2" t="n"/>
+    </row>
+    <row r="2228">
+      <c r="E2228" s="2" t="n"/>
+    </row>
+    <row r="2229">
+      <c r="E2229" s="2" t="n"/>
+    </row>
+    <row r="2230">
+      <c r="E2230" s="2" t="n"/>
+    </row>
+    <row r="2231">
+      <c r="E2231" s="2" t="n"/>
+    </row>
+    <row r="2232">
+      <c r="E2232" s="2" t="n"/>
+    </row>
+    <row r="2233">
+      <c r="E2233" s="2" t="n"/>
+    </row>
+    <row r="2234">
+      <c r="E2234" s="2" t="n"/>
+    </row>
+    <row r="2235">
+      <c r="E2235" s="2" t="n"/>
+    </row>
+    <row r="2236">
+      <c r="E2236" s="2" t="n"/>
+    </row>
+    <row r="2237">
+      <c r="E2237" s="2" t="n"/>
+    </row>
+    <row r="2238">
+      <c r="E2238" s="2" t="n"/>
+    </row>
+    <row r="2239">
+      <c r="E2239" s="2" t="n"/>
+    </row>
+    <row r="2240">
+      <c r="E2240" s="2" t="n"/>
+    </row>
+    <row r="2241">
+      <c r="E2241" s="2" t="n"/>
+    </row>
+    <row r="2242">
+      <c r="E2242" s="2" t="n"/>
+    </row>
+    <row r="2243">
+      <c r="E2243" s="2" t="n"/>
+    </row>
+    <row r="2244">
+      <c r="E2244" s="2" t="n"/>
+    </row>
+    <row r="2245">
+      <c r="E2245" s="2" t="n"/>
+    </row>
+    <row r="2246">
+      <c r="E2246" s="2" t="n"/>
+    </row>
+    <row r="2247">
+      <c r="E2247" s="2" t="n"/>
+    </row>
+    <row r="2248">
+      <c r="E2248" s="2" t="n"/>
+    </row>
+    <row r="2249">
+      <c r="E2249" s="2" t="n"/>
+    </row>
+    <row r="2250">
+      <c r="E2250" s="2" t="n"/>
+    </row>
+    <row r="2251">
+      <c r="E2251" s="2" t="n"/>
+    </row>
+    <row r="2252">
+      <c r="E2252" s="2" t="n"/>
+    </row>
+    <row r="2253">
+      <c r="E2253" s="2" t="n"/>
+    </row>
+    <row r="2254">
+      <c r="E2254" s="2" t="n"/>
+    </row>
+    <row r="2255">
+      <c r="E2255" s="2" t="n"/>
+    </row>
+    <row r="2256">
+      <c r="E2256" s="2" t="n"/>
+    </row>
+    <row r="2257">
+      <c r="E2257" s="2" t="n"/>
+    </row>
+    <row r="2258">
+      <c r="E2258" s="2" t="n"/>
+    </row>
+    <row r="2259">
+      <c r="E2259" s="2" t="n"/>
+    </row>
+    <row r="2260">
+      <c r="E2260" s="2" t="n"/>
+    </row>
+    <row r="2261">
+      <c r="E2261" s="2" t="n"/>
+    </row>
+    <row r="2262">
+      <c r="E2262" s="2" t="n"/>
+    </row>
+    <row r="2263">
+      <c r="E2263" s="2" t="n"/>
+    </row>
+    <row r="2264">
+      <c r="E2264" s="2" t="n"/>
+    </row>
+    <row r="2265">
+      <c r="E2265" s="2" t="n"/>
+    </row>
+    <row r="2266">
+      <c r="E2266" s="2" t="n"/>
+    </row>
+    <row r="2267">
+      <c r="E2267" s="2" t="n"/>
+    </row>
+    <row r="2268">
+      <c r="E2268" s="2" t="n"/>
+    </row>
+    <row r="2269">
+      <c r="E2269" s="2" t="n"/>
+    </row>
+    <row r="2270">
+      <c r="E2270" s="2" t="n"/>
+    </row>
+    <row r="2271">
+      <c r="E2271" s="2" t="n"/>
+    </row>
+    <row r="2272">
+      <c r="E2272" s="2" t="n"/>
+    </row>
+    <row r="2273">
+      <c r="E2273" s="2" t="n"/>
+    </row>
+    <row r="2274">
+      <c r="E2274" s="2" t="n"/>
+    </row>
+    <row r="2275">
+      <c r="E2275" s="2" t="n"/>
+    </row>
+    <row r="2276">
+      <c r="E2276" s="2" t="n"/>
+    </row>
+    <row r="2277">
+      <c r="E2277" s="2" t="n"/>
+    </row>
+    <row r="2278">
+      <c r="E2278" s="2" t="n"/>
+    </row>
+    <row r="2279">
+      <c r="E2279" s="2" t="n"/>
+    </row>
+    <row r="2280">
+      <c r="E2280" s="2" t="n"/>
+    </row>
+    <row r="2281">
+      <c r="E2281" s="2" t="n"/>
+    </row>
+    <row r="2282">
+      <c r="E2282" s="2" t="n"/>
+    </row>
+    <row r="2283">
+      <c r="E2283" s="2" t="n"/>
+    </row>
+    <row r="2284">
+      <c r="E2284" s="2" t="n"/>
+    </row>
+    <row r="2285">
+      <c r="E2285" s="2" t="n"/>
+    </row>
+    <row r="2286">
+      <c r="E2286" s="2" t="n"/>
+    </row>
+    <row r="2287">
+      <c r="E2287" s="2" t="n"/>
+    </row>
+    <row r="2288">
+      <c r="E2288" s="2" t="n"/>
+    </row>
+    <row r="2289">
+      <c r="E2289" s="2" t="n"/>
+    </row>
+    <row r="2290">
+      <c r="E2290" s="2" t="n"/>
+    </row>
+    <row r="2291">
+      <c r="E2291" s="2" t="n"/>
+    </row>
+    <row r="2292">
+      <c r="E2292" s="2" t="n"/>
+    </row>
+    <row r="2293">
+      <c r="E2293" s="2" t="n"/>
+    </row>
+    <row r="2294">
+      <c r="E2294" s="2" t="n"/>
+    </row>
+    <row r="2295">
+      <c r="E2295" s="2" t="n"/>
+    </row>
+    <row r="2296">
+      <c r="E2296" s="2" t="n"/>
+    </row>
+    <row r="2297">
+      <c r="E2297" s="2" t="n"/>
+    </row>
+    <row r="2298">
+      <c r="E2298" s="2" t="n"/>
+    </row>
+    <row r="2299">
+      <c r="E2299" s="2" t="n"/>
+    </row>
+    <row r="2300">
+      <c r="E2300" s="2" t="n"/>
+    </row>
+    <row r="2301">
+      <c r="E2301" s="2" t="n"/>
+    </row>
+    <row r="2302">
+      <c r="E2302" s="2" t="n"/>
+    </row>
+    <row r="2303">
+      <c r="E2303" s="2" t="n"/>
+    </row>
+    <row r="2304">
+      <c r="E2304" s="2" t="n"/>
+    </row>
+    <row r="2305">
+      <c r="E2305" s="2" t="n"/>
+    </row>
+    <row r="2306">
+      <c r="E2306" s="2" t="n"/>
+    </row>
+    <row r="2307">
+      <c r="E2307" s="2" t="n"/>
+    </row>
+    <row r="2308">
+      <c r="E2308" s="2" t="n"/>
+    </row>
+    <row r="2309">
+      <c r="E2309" s="2" t="n"/>
+    </row>
+    <row r="2310">
+      <c r="E2310" s="2" t="n"/>
+    </row>
+    <row r="2311">
+      <c r="E2311" s="2" t="n"/>
+    </row>
+    <row r="2312">
+      <c r="E2312" s="2" t="n"/>
+    </row>
+    <row r="2313">
+      <c r="E2313" s="2" t="n"/>
+    </row>
+    <row r="2314">
+      <c r="E2314" s="2" t="n"/>
+    </row>
+    <row r="2315">
+      <c r="E2315" s="2" t="n"/>
+    </row>
+    <row r="2316">
+      <c r="E2316" s="2" t="n"/>
+    </row>
+    <row r="2317">
+      <c r="E2317" s="2" t="n"/>
+    </row>
+    <row r="2318">
+      <c r="E2318" s="2" t="n"/>
+    </row>
+    <row r="2319">
+      <c r="E2319" s="2" t="n"/>
+    </row>
+    <row r="2320">
+      <c r="E2320" s="2" t="n"/>
+    </row>
+    <row r="2321">
+      <c r="E2321" s="2" t="n"/>
+    </row>
+    <row r="2322">
+      <c r="E2322" s="2" t="n"/>
+    </row>
+    <row r="2323">
+      <c r="E2323" s="2" t="n"/>
+    </row>
+    <row r="2324">
+      <c r="E2324" s="2" t="n"/>
+    </row>
+    <row r="2325">
+      <c r="E2325" s="2" t="n"/>
+    </row>
+    <row r="2326">
+      <c r="E2326" s="2" t="n"/>
+    </row>
+    <row r="2327">
+      <c r="E2327" s="2" t="n"/>
+    </row>
+    <row r="2328">
+      <c r="E2328" s="2" t="n"/>
+    </row>
+    <row r="2329">
+      <c r="E2329" s="2" t="n"/>
+    </row>
+    <row r="2330">
+      <c r="E2330" s="2" t="n"/>
+    </row>
+    <row r="2331">
+      <c r="E2331" s="2" t="n"/>
+    </row>
+    <row r="2332">
+      <c r="E2332" s="2" t="n"/>
+    </row>
+    <row r="2333">
+      <c r="E2333" s="2" t="n"/>
+    </row>
+    <row r="2334">
+      <c r="E2334" s="2" t="n"/>
+    </row>
+    <row r="2335">
+      <c r="E2335" s="2" t="n"/>
+    </row>
+    <row r="2336">
+      <c r="E2336" s="2" t="n"/>
+    </row>
+    <row r="2337">
+      <c r="E2337" s="2" t="n"/>
+    </row>
+    <row r="2338">
+      <c r="E2338" s="2" t="n"/>
+    </row>
+    <row r="2339">
+      <c r="E2339" s="2" t="n"/>
+    </row>
+    <row r="2340">
+      <c r="E2340" s="2" t="n"/>
+    </row>
+    <row r="2341">
+      <c r="E2341" s="2" t="n"/>
+    </row>
+    <row r="2342">
+      <c r="E2342" s="2" t="n"/>
+    </row>
+    <row r="2343">
+      <c r="E2343" s="2" t="n"/>
+    </row>
+    <row r="2344">
+      <c r="E2344" s="2" t="n"/>
+    </row>
+    <row r="2345">
+      <c r="E2345" s="2" t="n"/>
+    </row>
+    <row r="2346">
+      <c r="E2346" s="2" t="n"/>
+    </row>
+    <row r="2347">
+      <c r="E2347" s="2" t="n"/>
+    </row>
+    <row r="2348">
+      <c r="E2348" s="2" t="n"/>
+    </row>
+    <row r="2349">
+      <c r="E2349" s="2" t="n"/>
+    </row>
+    <row r="2350">
+      <c r="E2350" s="2" t="n"/>
+    </row>
+    <row r="2351">
+      <c r="E2351" s="2" t="n"/>
+    </row>
+    <row r="2352">
+      <c r="E2352" s="2" t="n"/>
+    </row>
+    <row r="2353">
+      <c r="E2353" s="2" t="n"/>
+    </row>
+    <row r="2354">
+      <c r="E2354" s="2" t="n"/>
+    </row>
+    <row r="2355">
+      <c r="E2355" s="2" t="n"/>
+    </row>
+    <row r="2356">
+      <c r="E2356" s="2" t="n"/>
+    </row>
+    <row r="2357">
+      <c r="E2357" s="2" t="n"/>
+    </row>
+    <row r="2358">
+      <c r="E2358" s="2" t="n"/>
+    </row>
+    <row r="2359">
+      <c r="E2359" s="2" t="n"/>
+    </row>
+    <row r="2360">
+      <c r="E2360" s="2" t="n"/>
+    </row>
+    <row r="2361">
+      <c r="E2361" s="2" t="n"/>
+    </row>
+    <row r="2362">
+      <c r="E2362" s="2" t="n"/>
+    </row>
+    <row r="2363">
+      <c r="E2363" s="2" t="n"/>
+    </row>
+    <row r="2364">
+      <c r="E2364" s="2" t="n"/>
+    </row>
+    <row r="2365">
+      <c r="E2365" s="2" t="n"/>
+    </row>
+    <row r="2366">
+      <c r="E2366" s="2" t="n"/>
+    </row>
+    <row r="2367">
+      <c r="E2367" s="2" t="n"/>
+    </row>
+    <row r="2368">
+      <c r="E2368" s="2" t="n"/>
+    </row>
+    <row r="2369">
+      <c r="E2369" s="2" t="n"/>
+    </row>
+    <row r="2370">
+      <c r="E2370" s="2" t="n"/>
+    </row>
+    <row r="2371">
+      <c r="E2371" s="2" t="n"/>
+    </row>
+    <row r="2372">
+      <c r="E2372" s="2" t="n"/>
+    </row>
+    <row r="2373">
+      <c r="E2373" s="2" t="n"/>
+    </row>
+    <row r="2374">
+      <c r="E2374" s="2" t="n"/>
+    </row>
+    <row r="2375">
+      <c r="E2375" s="2" t="n"/>
+    </row>
+    <row r="2376">
+      <c r="E2376" s="2" t="n"/>
+    </row>
+    <row r="2377">
+      <c r="E2377" s="2" t="n"/>
+    </row>
+    <row r="2378">
+      <c r="E2378" s="2" t="n"/>
+    </row>
+    <row r="2379">
+      <c r="E2379" s="2" t="n"/>
+    </row>
+    <row r="2380">
+      <c r="E2380" s="2" t="n"/>
+    </row>
+    <row r="2381">
+      <c r="E2381" s="2" t="n"/>
+    </row>
+    <row r="2382">
+      <c r="E2382" s="2" t="n"/>
+    </row>
+    <row r="2383">
+      <c r="E2383" s="2" t="n"/>
+    </row>
+    <row r="2384">
+      <c r="E2384" s="2" t="n"/>
+    </row>
+    <row r="2385">
+      <c r="E2385" s="2" t="n"/>
+    </row>
+    <row r="2386">
+      <c r="E2386" s="2" t="n"/>
+    </row>
+    <row r="2387">
+      <c r="E2387" s="2" t="n"/>
+    </row>
+    <row r="2388">
+      <c r="E2388" s="2" t="n"/>
+    </row>
+    <row r="2389">
+      <c r="E2389" s="2" t="n"/>
+    </row>
+    <row r="2390">
+      <c r="E2390" s="2" t="n"/>
+    </row>
+    <row r="2391">
+      <c r="E2391" s="2" t="n"/>
+    </row>
+    <row r="2392">
+      <c r="E2392" s="2" t="n"/>
+    </row>
+    <row r="2393">
+      <c r="E2393" s="2" t="n"/>
+    </row>
+    <row r="2394">
+      <c r="E2394" s="2" t="n"/>
+    </row>
+    <row r="2395">
+      <c r="E2395" s="2" t="n"/>
+    </row>
+    <row r="2396">
+      <c r="E2396" s="2" t="n"/>
+    </row>
+    <row r="2397">
+      <c r="E2397" s="2" t="n"/>
+    </row>
+    <row r="2398">
+      <c r="E2398" s="2" t="n"/>
+    </row>
+    <row r="2399">
+      <c r="E2399" s="2" t="n"/>
+    </row>
+    <row r="2400">
+      <c r="E2400" s="2" t="n"/>
+    </row>
+    <row r="2401">
+      <c r="E2401" s="2" t="n"/>
+    </row>
+    <row r="2402">
+      <c r="E2402" s="2" t="n"/>
+    </row>
+    <row r="2403">
+      <c r="E2403" s="2" t="n"/>
+    </row>
+    <row r="2404">
+      <c r="E2404" s="2" t="n"/>
+    </row>
+    <row r="2405">
+      <c r="E2405" s="2" t="n"/>
+    </row>
+    <row r="2406">
+      <c r="E2406" s="2" t="n"/>
+    </row>
+    <row r="2407">
+      <c r="E2407" s="2" t="n"/>
+    </row>
+    <row r="2408">
+      <c r="E2408" s="2" t="n"/>
+    </row>
+    <row r="2409">
+      <c r="E2409" s="2" t="n"/>
+    </row>
+    <row r="2410">
+      <c r="E2410" s="2" t="n"/>
+    </row>
+    <row r="2411">
+      <c r="E2411" s="2" t="n"/>
+    </row>
+    <row r="2412">
+      <c r="E2412" s="2" t="n"/>
+    </row>
+    <row r="2413">
+      <c r="E2413" s="2" t="n"/>
+    </row>
+    <row r="2414">
+      <c r="E2414" s="2" t="n"/>
+    </row>
+    <row r="2415">
+      <c r="E2415" s="2" t="n"/>
+    </row>
+    <row r="2416">
+      <c r="E2416" s="2" t="n"/>
+    </row>
+    <row r="2417">
+      <c r="E2417" s="2" t="n"/>
+    </row>
+    <row r="2418">
+      <c r="E2418" s="2" t="n"/>
+    </row>
+    <row r="2419">
+      <c r="E2419" s="2" t="n"/>
+    </row>
+    <row r="2420">
+      <c r="E2420" s="2" t="n"/>
+    </row>
+    <row r="2421">
+      <c r="E2421" s="2" t="n"/>
+    </row>
+    <row r="2422">
+      <c r="E2422" s="2" t="n"/>
+    </row>
+    <row r="2423">
+      <c r="E2423" s="2" t="n"/>
+    </row>
+    <row r="2424">
+      <c r="E2424" s="2" t="n"/>
+    </row>
+    <row r="2425">
+      <c r="E2425" s="2" t="n"/>
+    </row>
+    <row r="2426">
+      <c r="E2426" s="2" t="n"/>
+    </row>
+    <row r="2427">
+      <c r="E2427" s="2" t="n"/>
+    </row>
+    <row r="2428">
+      <c r="E2428" s="2" t="n"/>
+    </row>
+    <row r="2429">
+      <c r="E2429" s="2" t="n"/>
+    </row>
+    <row r="2430">
+      <c r="E2430" s="2" t="n"/>
+    </row>
+    <row r="2431">
+      <c r="E2431" s="2" t="n"/>
+    </row>
+    <row r="2432">
+      <c r="E2432" s="2" t="n"/>
+    </row>
+    <row r="2433">
+      <c r="E2433" s="2" t="n"/>
+    </row>
+    <row r="2434">
+      <c r="E2434" s="2" t="n"/>
+    </row>
+    <row r="2435">
+      <c r="E2435" s="2" t="n"/>
+    </row>
+    <row r="2436">
+      <c r="E2436" s="2" t="n"/>
+    </row>
+    <row r="2437">
+      <c r="E2437" s="2" t="n"/>
+    </row>
+    <row r="2438">
+      <c r="E2438" s="2" t="n"/>
+    </row>
+    <row r="2439">
+      <c r="E2439" s="2" t="n"/>
+    </row>
+    <row r="2440">
+      <c r="E2440" s="2" t="n"/>
+    </row>
+    <row r="2441">
+      <c r="E2441" s="2" t="n"/>
+    </row>
+    <row r="2442">
+      <c r="E2442" s="2" t="n"/>
+    </row>
+    <row r="2443">
+      <c r="E2443" s="2" t="n"/>
+    </row>
+    <row r="2444">
+      <c r="E2444" s="2" t="n"/>
+    </row>
+    <row r="2445">
+      <c r="E2445" s="2" t="n"/>
+    </row>
+    <row r="2446">
+      <c r="E2446" s="2" t="n"/>
+    </row>
+    <row r="2447">
+      <c r="E2447" s="2" t="n"/>
+    </row>
+    <row r="2448">
+      <c r="E2448" s="2" t="n"/>
+    </row>
+    <row r="2449">
+      <c r="E2449" s="2" t="n"/>
+    </row>
+    <row r="2450">
+      <c r="E2450" s="2" t="n"/>
+    </row>
+    <row r="2451">
+      <c r="E2451" s="2" t="n"/>
+    </row>
+    <row r="2452">
+      <c r="E2452" s="2" t="n"/>
+    </row>
+    <row r="2453">
+      <c r="E2453" s="2" t="n"/>
+    </row>
+    <row r="2454">
+      <c r="E2454" s="2" t="n"/>
+    </row>
+    <row r="2455">
+      <c r="E2455" s="2" t="n"/>
+    </row>
+    <row r="2456">
+      <c r="E2456" s="2" t="n"/>
+    </row>
+    <row r="2457">
+      <c r="E2457" s="2" t="n"/>
+    </row>
+    <row r="2458">
+      <c r="E2458" s="2" t="n"/>
+    </row>
+    <row r="2459">
+      <c r="E2459" s="2" t="n"/>
+    </row>
+    <row r="2460">
+      <c r="E2460" s="2" t="n"/>
+    </row>
+    <row r="2461">
+      <c r="E2461" s="2" t="n"/>
+    </row>
+    <row r="2462">
+      <c r="E2462" s="2" t="n"/>
+    </row>
+    <row r="2463">
+      <c r="E2463" s="2" t="n"/>
+    </row>
+    <row r="2464">
+      <c r="E2464" s="2" t="n"/>
+    </row>
+    <row r="2465">
+      <c r="E2465" s="2" t="n"/>
+    </row>
+    <row r="2466">
+      <c r="E2466" s="2" t="n"/>
+    </row>
+    <row r="2467">
+      <c r="E2467" s="2" t="n"/>
+    </row>
+    <row r="2468">
+      <c r="E2468" s="2" t="n"/>
+    </row>
+    <row r="2469">
+      <c r="E2469" s="2" t="n"/>
+    </row>
+    <row r="2470">
+      <c r="E2470" s="2" t="n"/>
+    </row>
+    <row r="2471">
+      <c r="E2471" s="2" t="n"/>
+    </row>
+    <row r="2472">
+      <c r="E2472" s="2" t="n"/>
+    </row>
+    <row r="2473">
+      <c r="E2473" s="2" t="n"/>
+    </row>
+    <row r="2474">
+      <c r="E2474" s="2" t="n"/>
+    </row>
+    <row r="2475">
+      <c r="E2475" s="2" t="n"/>
+    </row>
+    <row r="2476">
+      <c r="E2476" s="2" t="n"/>
+    </row>
+    <row r="2477">
+      <c r="E2477" s="2" t="n"/>
+    </row>
+    <row r="2478">
+      <c r="E2478" s="2" t="n"/>
+    </row>
+    <row r="2479">
+      <c r="E2479" s="2" t="n"/>
+    </row>
+    <row r="2480">
+      <c r="E2480" s="2" t="n"/>
+    </row>
+    <row r="2481">
+      <c r="E2481" s="2" t="n"/>
+    </row>
+    <row r="2482">
+      <c r="E2482" s="2" t="n"/>
+    </row>
+    <row r="2483">
+      <c r="E2483" s="2" t="n"/>
+    </row>
+    <row r="2484">
+      <c r="E2484" s="2" t="n"/>
+    </row>
+    <row r="2485">
+      <c r="E2485" s="2" t="n"/>
+    </row>
+    <row r="2486">
+      <c r="E2486" s="2" t="n"/>
+    </row>
+    <row r="2487">
+      <c r="E2487" s="2" t="n"/>
+    </row>
+    <row r="2488">
+      <c r="E2488" s="2" t="n"/>
+    </row>
+    <row r="2489">
+      <c r="E2489" s="2" t="n"/>
+    </row>
+    <row r="2490">
+      <c r="E2490" s="2" t="n"/>
+    </row>
+    <row r="2491">
+      <c r="E2491" s="2" t="n"/>
+    </row>
+    <row r="2492">
+      <c r="E2492" s="2" t="n"/>
+    </row>
+    <row r="2493">
+      <c r="E2493" s="2" t="n"/>
+    </row>
+    <row r="2494">
+      <c r="E2494" s="2" t="n"/>
+    </row>
+    <row r="2495">
+      <c r="E2495" s="2" t="n"/>
+    </row>
+    <row r="2496">
+      <c r="E2496" s="2" t="n"/>
+    </row>
+    <row r="2497">
+      <c r="E2497" s="2" t="n"/>
+    </row>
+    <row r="2498">
+      <c r="E2498" s="2" t="n"/>
+    </row>
+    <row r="2499">
+      <c r="E2499" s="2" t="n"/>
+    </row>
+    <row r="2500">
+      <c r="E2500" s="2" t="n"/>
+    </row>
+    <row r="2501">
+      <c r="E2501" s="2" t="n"/>
+    </row>
+    <row r="2502">
+      <c r="E2502" s="2" t="n"/>
+    </row>
+    <row r="2503">
+      <c r="E2503" s="2" t="n"/>
+    </row>
+    <row r="2504">
+      <c r="E2504" s="2" t="n"/>
+    </row>
+    <row r="2505">
+      <c r="E2505" s="2" t="n"/>
+    </row>
+    <row r="2506">
+      <c r="E2506" s="2" t="n"/>
+    </row>
+    <row r="2507">
+      <c r="E2507" s="2" t="n"/>
+    </row>
+    <row r="2508">
+      <c r="E2508" s="2" t="n"/>
+    </row>
+    <row r="2509">
+      <c r="E2509" s="2" t="n"/>
+    </row>
+    <row r="2510">
+      <c r="E2510" s="2" t="n"/>
+    </row>
+    <row r="2511">
+      <c r="E2511" s="2" t="n"/>
+    </row>
+    <row r="2512">
+      <c r="E2512" s="2" t="n"/>
+    </row>
+    <row r="2513">
+      <c r="E2513" s="2" t="n"/>
+    </row>
+    <row r="2514">
+      <c r="E2514" s="2" t="n"/>
+    </row>
+    <row r="2515">
+      <c r="E2515" s="2" t="n"/>
+    </row>
+    <row r="2516">
+      <c r="E2516" s="2" t="n"/>
+    </row>
+    <row r="2517">
+      <c r="E2517" s="2" t="n"/>
+    </row>
+    <row r="2518">
+      <c r="E2518" s="2" t="n"/>
+    </row>
+    <row r="2519">
+      <c r="E2519" s="2" t="n"/>
+    </row>
+    <row r="2520">
+      <c r="E2520" s="2" t="n"/>
+    </row>
+    <row r="2521">
+      <c r="E2521" s="2" t="n"/>
+    </row>
+    <row r="2522">
+      <c r="E2522" s="2" t="n"/>
+    </row>
+    <row r="2523">
+      <c r="E2523" s="2" t="n"/>
+    </row>
+    <row r="2524">
+      <c r="E2524" s="2" t="n"/>
+    </row>
+    <row r="2525">
+      <c r="E2525" s="2" t="n"/>
+    </row>
+    <row r="2526">
+      <c r="E2526" s="2" t="n"/>
+    </row>
+    <row r="2527">
+      <c r="E2527" s="2" t="n"/>
+    </row>
+    <row r="2528">
+      <c r="E2528" s="2" t="n"/>
+    </row>
+    <row r="2529">
+      <c r="E2529" s="2" t="n"/>
+    </row>
+    <row r="2530">
+      <c r="E2530" s="2" t="n"/>
+    </row>
+    <row r="2531">
+      <c r="E2531" s="2" t="n"/>
+    </row>
+    <row r="2532">
+      <c r="E2532" s="2" t="n"/>
+    </row>
+    <row r="2533">
+      <c r="E2533" s="2" t="n"/>
+    </row>
+    <row r="2534">
+      <c r="E2534" s="2" t="n"/>
+    </row>
+    <row r="2535">
+      <c r="E2535" s="2" t="n"/>
+    </row>
+    <row r="2536">
+      <c r="E2536" s="2" t="n"/>
+    </row>
+    <row r="2537">
+      <c r="E2537" s="2" t="n"/>
+    </row>
+    <row r="2538">
+      <c r="E2538" s="2" t="n"/>
+    </row>
+    <row r="2539">
+      <c r="E2539" s="2" t="n"/>
+    </row>
+    <row r="2540">
+      <c r="E2540" s="2" t="n"/>
+    </row>
+    <row r="2541">
+      <c r="E2541" s="2" t="n"/>
+    </row>
+    <row r="2542">
+      <c r="E2542" s="2" t="n"/>
+    </row>
+    <row r="2543">
+      <c r="E2543" s="2" t="n"/>
+    </row>
+    <row r="2544">
+      <c r="E2544" s="2" t="n"/>
+    </row>
+    <row r="2545">
+      <c r="E2545" s="2" t="n"/>
+    </row>
+    <row r="2546">
+      <c r="E2546" s="2" t="n"/>
+    </row>
+    <row r="2547">
+      <c r="E2547" s="2" t="n"/>
+    </row>
+    <row r="2548">
+      <c r="E2548" s="2" t="n"/>
+    </row>
+    <row r="2549">
+      <c r="E2549" s="2" t="n"/>
+    </row>
+    <row r="2550">
+      <c r="E2550" s="2" t="n"/>
+    </row>
+    <row r="2551">
+      <c r="E2551" s="2" t="n"/>
+    </row>
+    <row r="2552">
+      <c r="E2552" s="2" t="n"/>
+    </row>
+    <row r="2553">
+      <c r="E2553" s="2" t="n"/>
+    </row>
+    <row r="2554">
+      <c r="E2554" s="2" t="n"/>
+    </row>
+    <row r="2555">
+      <c r="E2555" s="2" t="n"/>
+    </row>
+    <row r="2556">
+      <c r="E2556" s="2" t="n"/>
+    </row>
+    <row r="2557">
+      <c r="E2557" s="2" t="n"/>
+    </row>
+    <row r="2558">
+      <c r="E2558" s="2" t="n"/>
+    </row>
+    <row r="2559">
+      <c r="E2559" s="2" t="n"/>
+    </row>
+    <row r="2560">
+      <c r="E2560" s="2" t="n"/>
+    </row>
+    <row r="2561">
+      <c r="E2561" s="2" t="n"/>
+    </row>
+    <row r="2562">
+      <c r="E2562" s="2" t="n"/>
+    </row>
+    <row r="2563">
+      <c r="E2563" s="2" t="n"/>
+    </row>
+    <row r="2564">
+      <c r="E2564" s="2" t="n"/>
+    </row>
+    <row r="2565">
+      <c r="E2565" s="2" t="n"/>
+    </row>
+    <row r="2566">
+      <c r="E2566" s="2" t="n"/>
+    </row>
+    <row r="2567">
+      <c r="E2567" s="2" t="n"/>
+    </row>
+    <row r="2568">
+      <c r="E2568" s="2" t="n"/>
+    </row>
+    <row r="2569">
+      <c r="E2569" s="2" t="n"/>
+    </row>
+    <row r="2570">
+      <c r="E2570" s="2" t="n"/>
+    </row>
+    <row r="2571">
+      <c r="E2571" s="2" t="n"/>
+    </row>
+    <row r="2572">
+      <c r="E2572" s="2" t="n"/>
+    </row>
+    <row r="2573">
+      <c r="E2573" s="2" t="n"/>
+    </row>
+    <row r="2574">
+      <c r="E2574" s="2" t="n"/>
+    </row>
+    <row r="2575">
+      <c r="E2575" s="2" t="n"/>
+    </row>
+    <row r="2576">
+      <c r="E2576" s="2" t="n"/>
+    </row>
+    <row r="2577">
+      <c r="E2577" s="2" t="n"/>
+    </row>
+    <row r="2578">
+      <c r="E2578" s="2" t="n"/>
+    </row>
+    <row r="2579">
+      <c r="E2579" s="2" t="n"/>
+    </row>
+    <row r="2580">
+      <c r="E2580" s="2" t="n"/>
+    </row>
+    <row r="2581">
+      <c r="E2581" s="2" t="n"/>
+    </row>
+    <row r="2582">
+      <c r="E2582" s="2" t="n"/>
+    </row>
+    <row r="2583">
+      <c r="E2583" s="2" t="n"/>
+    </row>
+    <row r="2584">
+      <c r="E2584" s="2" t="n"/>
+    </row>
+    <row r="2585">
+      <c r="E2585" s="2" t="n"/>
+    </row>
+    <row r="2586">
+      <c r="E2586" s="2" t="n"/>
+    </row>
+    <row r="2587">
+      <c r="E2587" s="2" t="n"/>
+    </row>
+    <row r="2588">
+      <c r="E2588" s="2" t="n"/>
+    </row>
+    <row r="2589">
+      <c r="E2589" s="2" t="n"/>
+    </row>
+    <row r="2590">
+      <c r="E2590" s="2" t="n"/>
+    </row>
+    <row r="2591">
+      <c r="E2591" s="2" t="n"/>
+    </row>
+    <row r="2592">
+      <c r="E2592" s="2" t="n"/>
+    </row>
+    <row r="2593">
+      <c r="E2593" s="2" t="n"/>
+    </row>
+    <row r="2594">
+      <c r="E2594" s="2" t="n"/>
+    </row>
+    <row r="2595">
+      <c r="E2595" s="2" t="n"/>
+    </row>
+    <row r="2596">
+      <c r="E2596" s="2" t="n"/>
+    </row>
+    <row r="2597">
+      <c r="E2597" s="2" t="n"/>
+    </row>
+    <row r="2598">
+      <c r="E2598" s="2" t="n"/>
+    </row>
+    <row r="2599">
+      <c r="E2599" s="2" t="n"/>
+    </row>
+    <row r="2600">
+      <c r="E2600" s="2" t="n"/>
+    </row>
+    <row r="2601">
+      <c r="E2601" s="2" t="n"/>
+    </row>
+    <row r="2602">
+      <c r="E2602" s="2" t="n"/>
+    </row>
+    <row r="2603">
+      <c r="E2603" s="2" t="n"/>
+    </row>
+    <row r="2604">
+      <c r="E2604" s="2" t="n"/>
+    </row>
+    <row r="2605">
+      <c r="E2605" s="2" t="n"/>
+    </row>
+    <row r="2606">
+      <c r="E2606" s="2" t="n"/>
+    </row>
+    <row r="2607">
+      <c r="E2607" s="2" t="n"/>
+    </row>
+    <row r="2608">
+      <c r="E2608" s="2" t="n"/>
+    </row>
+    <row r="2609">
+      <c r="E2609" s="2" t="n"/>
+    </row>
+    <row r="2610">
+      <c r="E2610" s="2" t="n"/>
+    </row>
+    <row r="2611">
+      <c r="E2611" s="2" t="n"/>
+    </row>
+    <row r="2612">
+      <c r="E2612" s="2" t="n"/>
+    </row>
+    <row r="2613">
+      <c r="E2613" s="2" t="n"/>
+    </row>
+    <row r="2614">
+      <c r="E2614" s="2" t="n"/>
+    </row>
+    <row r="2615">
+      <c r="E2615" s="2" t="n"/>
+    </row>
+    <row r="2616">
+      <c r="E2616" s="2" t="n"/>
+    </row>
+    <row r="2617">
+      <c r="E2617" s="2" t="n"/>
+    </row>
+    <row r="2618">
+      <c r="E2618" s="2" t="n"/>
+    </row>
+    <row r="2619">
+      <c r="E2619" s="2" t="n"/>
+    </row>
+    <row r="2620">
+      <c r="E2620" s="2" t="n"/>
+    </row>
+    <row r="2621">
+      <c r="E2621" s="2" t="n"/>
+    </row>
+    <row r="2622">
+      <c r="E2622" s="2" t="n"/>
+    </row>
+    <row r="2623">
+      <c r="E2623" s="2" t="n"/>
+    </row>
+    <row r="2624">
+      <c r="E2624" s="2" t="n"/>
+    </row>
+    <row r="2625">
+      <c r="E2625" s="2" t="n"/>
+    </row>
+    <row r="2626">
+      <c r="E2626" s="2" t="n"/>
+    </row>
+    <row r="2627">
+      <c r="E2627" s="2" t="n"/>
+    </row>
+    <row r="2628">
+      <c r="E2628" s="2" t="n"/>
+    </row>
+    <row r="2629">
+      <c r="E2629" s="2" t="n"/>
+    </row>
+    <row r="2630">
+      <c r="E2630" s="2" t="n"/>
+    </row>
+    <row r="2631">
+      <c r="E2631" s="2" t="n"/>
+    </row>
+    <row r="2632">
+      <c r="E2632" s="2" t="n"/>
+    </row>
+    <row r="2633">
+      <c r="E2633" s="2" t="n"/>
+    </row>
+    <row r="2634">
+      <c r="E2634" s="2" t="n"/>
+    </row>
+    <row r="2635">
+      <c r="E2635" s="2" t="n"/>
+    </row>
+    <row r="2636">
+      <c r="E2636" s="2" t="n"/>
+    </row>
+    <row r="2637">
+      <c r="E2637" s="2" t="n"/>
+    </row>
+    <row r="2638">
+      <c r="E2638" s="2" t="n"/>
+    </row>
+    <row r="2639">
+      <c r="E2639" s="2" t="n"/>
+    </row>
+    <row r="2640">
+      <c r="E2640" s="2" t="n"/>
+    </row>
+    <row r="2641">
+      <c r="E2641" s="2" t="n"/>
+    </row>
+    <row r="2642">
+      <c r="E2642" s="2" t="n"/>
+    </row>
+    <row r="2643">
+      <c r="E2643" s="2" t="n"/>
+    </row>
+    <row r="2644">
+      <c r="E2644" s="2" t="n"/>
+    </row>
+    <row r="2645">
+      <c r="E2645" s="2" t="n"/>
+    </row>
+    <row r="2646">
+      <c r="E2646" s="2" t="n"/>
+    </row>
+    <row r="2647">
+      <c r="E2647" s="2" t="n"/>
+    </row>
+    <row r="2648">
+      <c r="E2648" s="2" t="n"/>
+    </row>
+    <row r="2649">
+      <c r="E2649" s="2" t="n"/>
+    </row>
+    <row r="2650">
+      <c r="E2650" s="2" t="n"/>
+    </row>
+    <row r="2651">
+      <c r="E2651" s="2" t="n"/>
+    </row>
+    <row r="2652">
+      <c r="E2652" s="2" t="n"/>
+    </row>
+    <row r="2653">
+      <c r="E2653" s="2" t="n"/>
+    </row>
+    <row r="2654">
+      <c r="E2654" s="2" t="n"/>
+    </row>
+    <row r="2655">
+      <c r="E2655" s="2" t="n"/>
+    </row>
+    <row r="2656">
+      <c r="E2656" s="2" t="n"/>
+    </row>
+    <row r="2657">
+      <c r="E2657" s="2" t="n"/>
+    </row>
+    <row r="2658">
+      <c r="E2658" s="2" t="n"/>
+    </row>
+    <row r="2659">
+      <c r="E2659" s="2" t="n"/>
+    </row>
+    <row r="2660">
+      <c r="E2660" s="2" t="n"/>
+    </row>
+    <row r="2661">
+      <c r="E2661" s="2" t="n"/>
+    </row>
+    <row r="2662">
+      <c r="E2662" s="2" t="n"/>
+    </row>
+    <row r="2663">
+      <c r="E2663" s="2" t="n"/>
+    </row>
+    <row r="2664">
+      <c r="E2664" s="2" t="n"/>
+    </row>
+    <row r="2665">
+      <c r="E2665" s="2" t="n"/>
+    </row>
+    <row r="2666">
+      <c r="E2666" s="2" t="n"/>
+    </row>
+    <row r="2667">
+      <c r="E2667" s="2" t="n"/>
+    </row>
+    <row r="2668">
+      <c r="E2668" s="2" t="n"/>
+    </row>
+    <row r="2669">
+      <c r="E2669" s="2" t="n"/>
+    </row>
+    <row r="2670">
+      <c r="E2670" s="2" t="n"/>
+    </row>
+    <row r="2671">
+      <c r="E2671" s="2" t="n"/>
+    </row>
+    <row r="2672">
+      <c r="E2672" s="2" t="n"/>
+    </row>
+    <row r="2673">
+      <c r="E2673" s="2" t="n"/>
+    </row>
+    <row r="2674">
+      <c r="E2674" s="2" t="n"/>
+    </row>
+    <row r="2675">
+      <c r="E2675" s="2" t="n"/>
+    </row>
+    <row r="2676">
+      <c r="E2676" s="2" t="n"/>
+    </row>
+    <row r="2677">
+      <c r="E2677" s="2" t="n"/>
+    </row>
+    <row r="2678">
+      <c r="E2678" s="2" t="n"/>
+    </row>
+    <row r="2679">
+      <c r="E2679" s="2" t="n"/>
+    </row>
+    <row r="2680">
+      <c r="E2680" s="2" t="n"/>
+    </row>
+    <row r="2681">
+      <c r="E2681" s="2" t="n"/>
+    </row>
+    <row r="2682">
+      <c r="E2682" s="2" t="n"/>
+    </row>
+    <row r="2683">
+      <c r="E2683" s="2" t="n"/>
+    </row>
+    <row r="2684">
+      <c r="E2684" s="2" t="n"/>
+    </row>
+    <row r="2685">
+      <c r="E2685" s="2" t="n"/>
+    </row>
+    <row r="2686">
+      <c r="E2686" s="2" t="n"/>
+    </row>
+    <row r="2687">
+      <c r="E2687" s="2" t="n"/>
+    </row>
+    <row r="2688">
+      <c r="E2688" s="2" t="n"/>
+    </row>
+    <row r="2689">
+      <c r="E2689" s="2" t="n"/>
+    </row>
+    <row r="2690">
+      <c r="E2690" s="2" t="n"/>
+    </row>
+    <row r="2691">
+      <c r="E2691" s="2" t="n"/>
+    </row>
+    <row r="2692">
+      <c r="E2692" s="2" t="n"/>
+    </row>
+    <row r="2693">
+      <c r="E2693" s="2" t="n"/>
+    </row>
+    <row r="2694">
+      <c r="E2694" s="2" t="n"/>
+    </row>
+    <row r="2695">
+      <c r="E2695" s="2" t="n"/>
+    </row>
+    <row r="2696">
+      <c r="E2696" s="2" t="n"/>
+    </row>
+    <row r="2697">
+      <c r="E2697" s="2" t="n"/>
+    </row>
+    <row r="2698">
+      <c r="E2698" s="2" t="n"/>
+    </row>
+    <row r="2699">
+      <c r="E2699" s="2" t="n"/>
+    </row>
+    <row r="2700">
+      <c r="E2700" s="2" t="n"/>
+    </row>
+    <row r="2701">
+      <c r="E2701" s="2" t="n"/>
+    </row>
+    <row r="2702">
+      <c r="E2702" s="2" t="n"/>
+    </row>
+    <row r="2703">
+      <c r="E2703" s="2" t="n"/>
+    </row>
+    <row r="2704">
+      <c r="E2704" s="2" t="n"/>
+    </row>
+    <row r="2705">
+      <c r="E2705" s="2" t="n"/>
+    </row>
+    <row r="2706">
+      <c r="E2706" s="2" t="n"/>
+    </row>
+    <row r="2707">
+      <c r="E2707" s="2" t="n"/>
+    </row>
+    <row r="2708">
+      <c r="E2708" s="2" t="n"/>
+    </row>
+    <row r="2709">
+      <c r="E2709" s="2" t="n"/>
+    </row>
+    <row r="2710">
+      <c r="E2710" s="2" t="n"/>
+    </row>
+    <row r="2711">
+      <c r="E2711" s="2" t="n"/>
+    </row>
+    <row r="2712">
+      <c r="E2712" s="2" t="n"/>
+    </row>
+    <row r="2713">
+      <c r="E2713" s="2" t="n"/>
+    </row>
+    <row r="2714">
+      <c r="E2714" s="2" t="n"/>
+    </row>
+    <row r="2715">
+      <c r="E2715" s="2" t="n"/>
+    </row>
+    <row r="2716">
+      <c r="E2716" s="2" t="n"/>
+    </row>
+    <row r="2717">
+      <c r="E2717" s="2" t="n"/>
+    </row>
+    <row r="2718">
+      <c r="E2718" s="2" t="n"/>
+    </row>
+    <row r="2719">
+      <c r="E2719" s="2" t="n"/>
+    </row>
+    <row r="2720">
+      <c r="E2720" s="2" t="n"/>
+    </row>
+    <row r="2721">
+      <c r="E2721" s="2" t="n"/>
+    </row>
+    <row r="2722">
+      <c r="E2722" s="2" t="n"/>
+    </row>
+    <row r="2723">
+      <c r="E2723" s="2" t="n"/>
+    </row>
+    <row r="2724">
+      <c r="E2724" s="2" t="n"/>
+    </row>
+    <row r="2725">
+      <c r="E2725" s="2" t="n"/>
+    </row>
+    <row r="2726">
+      <c r="E2726" s="2" t="n"/>
+    </row>
+    <row r="2727">
+      <c r="E2727" s="2" t="n"/>
+    </row>
+    <row r="2728">
+      <c r="E2728" s="2" t="n"/>
+    </row>
+    <row r="2729">
+      <c r="E2729" s="2" t="n"/>
+    </row>
+    <row r="2730">
+      <c r="E2730" s="2" t="n"/>
+    </row>
+    <row r="2731">
+      <c r="E2731" s="2" t="n"/>
+    </row>
+    <row r="2732">
+      <c r="E2732" s="2" t="n"/>
+    </row>
+    <row r="2733">
+      <c r="E2733" s="2" t="n"/>
+    </row>
+    <row r="2734">
+      <c r="E2734" s="2" t="n"/>
+    </row>
+    <row r="2735">
+      <c r="E2735" s="2" t="n"/>
+    </row>
+    <row r="2736">
+      <c r="E2736" s="2" t="n"/>
+    </row>
+    <row r="2737">
+      <c r="E2737" s="2" t="n"/>
+    </row>
+    <row r="2738">
+      <c r="E2738" s="2" t="n"/>
+    </row>
+    <row r="2739">
+      <c r="E2739" s="2" t="n"/>
+    </row>
+    <row r="2740">
+      <c r="E2740" s="2" t="n"/>
+    </row>
+    <row r="2741">
+      <c r="E2741" s="2" t="n"/>
+    </row>
+    <row r="2742">
+      <c r="E2742" s="2" t="n"/>
+    </row>
+    <row r="2743">
+      <c r="E2743" s="2" t="n"/>
+    </row>
+    <row r="2744">
+      <c r="E2744" s="2" t="n"/>
+    </row>
+    <row r="2745">
+      <c r="E2745" s="2" t="n"/>
+    </row>
+    <row r="2746">
+      <c r="E2746" s="2" t="n"/>
+    </row>
+    <row r="2747">
+      <c r="E2747" s="2" t="n"/>
+    </row>
+    <row r="2748">
+      <c r="E2748" s="2" t="n"/>
+    </row>
+    <row r="2749">
+      <c r="E2749" s="2" t="n"/>
+    </row>
+    <row r="2750">
+      <c r="E2750" s="2" t="n"/>
+    </row>
+    <row r="2751">
+      <c r="E2751" s="2" t="n"/>
+    </row>
+    <row r="2752">
+      <c r="E2752" s="2" t="n"/>
+    </row>
+    <row r="2753">
+      <c r="E2753" s="2" t="n"/>
+    </row>
+    <row r="2754">
+      <c r="E2754" s="2" t="n"/>
+    </row>
+    <row r="2755">
+      <c r="E2755" s="2" t="n"/>
+    </row>
+    <row r="2756">
+      <c r="E2756" s="2" t="n"/>
+    </row>
+    <row r="2757">
+      <c r="E2757" s="2" t="n"/>
+    </row>
+    <row r="2758">
+      <c r="E2758" s="2" t="n"/>
+    </row>
+    <row r="2759">
+      <c r="E2759" s="2" t="n"/>
+    </row>
+    <row r="2760">
+      <c r="E2760" s="2" t="n"/>
+    </row>
+    <row r="2761">
+      <c r="E2761" s="2" t="n"/>
+    </row>
+    <row r="2762">
+      <c r="E2762" s="2" t="n"/>
+    </row>
+    <row r="2763">
+      <c r="E2763" s="2" t="n"/>
+    </row>
+    <row r="2764">
+      <c r="E2764" s="2" t="n"/>
+    </row>
+    <row r="2765">
+      <c r="E2765" s="2" t="n"/>
+    </row>
+    <row r="2766">
+      <c r="E2766" s="2" t="n"/>
+    </row>
+    <row r="2767">
+      <c r="E2767" s="2" t="n"/>
+    </row>
+    <row r="2768">
+      <c r="E2768" s="2" t="n"/>
+    </row>
+    <row r="2769">
+      <c r="E2769" s="2" t="n"/>
+    </row>
+    <row r="2770">
+      <c r="E2770" s="2" t="n"/>
+    </row>
+    <row r="2771">
+      <c r="E2771" s="2" t="n"/>
+    </row>
+    <row r="2772">
+      <c r="E2772" s="2" t="n"/>
+    </row>
+    <row r="2773">
+      <c r="E2773" s="2" t="n"/>
+    </row>
+    <row r="2774">
+      <c r="E2774" s="2" t="n"/>
+    </row>
+    <row r="2775">
+      <c r="E2775" s="2" t="n"/>
+    </row>
+    <row r="2776">
+      <c r="E2776" s="2" t="n"/>
+    </row>
+    <row r="2777">
+      <c r="E2777" s="2" t="n"/>
+    </row>
+    <row r="2778">
+      <c r="E2778" s="2" t="n"/>
+    </row>
+    <row r="2779">
+      <c r="E2779" s="2" t="n"/>
+    </row>
+    <row r="2780">
+      <c r="E2780" s="2" t="n"/>
+    </row>
+    <row r="2781">
+      <c r="E2781" s="2" t="n"/>
+    </row>
+    <row r="2782">
+      <c r="E2782" s="2" t="n"/>
+    </row>
+    <row r="2783">
+      <c r="E2783" s="2" t="n"/>
+    </row>
+    <row r="2784">
+      <c r="E2784" s="2" t="n"/>
+    </row>
+    <row r="2785">
+      <c r="E2785" s="2" t="n"/>
+    </row>
+    <row r="2786">
+      <c r="E2786" s="2" t="n"/>
+    </row>
+    <row r="2787">
+      <c r="E2787" s="2" t="n"/>
+    </row>
+    <row r="2788">
+      <c r="E2788" s="2" t="n"/>
+    </row>
+    <row r="2789">
+      <c r="E2789" s="2" t="n"/>
+    </row>
+    <row r="2790">
+      <c r="E2790" s="2" t="n"/>
+    </row>
+    <row r="2791">
+      <c r="E2791" s="2" t="n"/>
+    </row>
+    <row r="2792">
+      <c r="E2792" s="2" t="n"/>
+    </row>
+    <row r="2793">
+      <c r="E2793" s="2" t="n"/>
+    </row>
+    <row r="2794">
+      <c r="E2794" s="2" t="n"/>
+    </row>
+    <row r="2795">
+      <c r="E2795" s="2" t="n"/>
+    </row>
+    <row r="2796">
+      <c r="E2796" s="2" t="n"/>
+    </row>
+    <row r="2797">
+      <c r="E2797" s="2" t="n"/>
+    </row>
+    <row r="2798">
+      <c r="E2798" s="2" t="n"/>
+    </row>
+    <row r="2799">
+      <c r="E2799" s="2" t="n"/>
+    </row>
+    <row r="2800">
+      <c r="E2800" s="2" t="n"/>
+    </row>
+    <row r="2801">
+      <c r="E2801" s="2" t="n"/>
+    </row>
+    <row r="2802">
+      <c r="E2802" s="2" t="n"/>
+    </row>
+    <row r="2803">
+      <c r="E2803" s="2" t="n"/>
+    </row>
+    <row r="2804">
+      <c r="E2804" s="2" t="n"/>
+    </row>
+    <row r="2805">
+      <c r="E2805" s="2" t="n"/>
+    </row>
+    <row r="2806">
+      <c r="E2806" s="2" t="n"/>
+    </row>
+    <row r="2807">
+      <c r="E2807" s="2" t="n"/>
+    </row>
+    <row r="2808">
+      <c r="E2808" s="2" t="n"/>
+    </row>
+    <row r="2809">
+      <c r="E2809" s="2" t="n"/>
+    </row>
+    <row r="2810">
+      <c r="E2810" s="2" t="n"/>
+    </row>
+    <row r="2811">
+      <c r="E2811" s="2" t="n"/>
+    </row>
+    <row r="2812">
+      <c r="E2812" s="2" t="n"/>
+    </row>
+    <row r="2813">
+      <c r="E2813" s="2" t="n"/>
+    </row>
+    <row r="2814">
+      <c r="E2814" s="2" t="n"/>
+    </row>
+    <row r="2815">
+      <c r="E2815" s="2" t="n"/>
+    </row>
+    <row r="2816">
+      <c r="E2816" s="2" t="n"/>
+    </row>
+    <row r="2817">
+      <c r="E2817" s="2" t="n"/>
+    </row>
+    <row r="2818">
+      <c r="E2818" s="2" t="n"/>
+    </row>
+    <row r="2819">
+      <c r="E2819" s="2" t="n"/>
+    </row>
+    <row r="2820">
+      <c r="E2820" s="2" t="n"/>
+    </row>
+    <row r="2821">
+      <c r="E2821" s="2" t="n"/>
+    </row>
+    <row r="2822">
+      <c r="E2822" s="2" t="n"/>
+    </row>
+    <row r="2823">
+      <c r="E2823" s="2" t="n"/>
+    </row>
+    <row r="2824">
+      <c r="E2824" s="2" t="n"/>
+    </row>
+    <row r="2825">
+      <c r="E2825" s="2" t="n"/>
+    </row>
+    <row r="2826">
+      <c r="E2826" s="2" t="n"/>
+    </row>
+    <row r="2827">
+      <c r="E2827" s="2" t="n"/>
+    </row>
+    <row r="2828">
+      <c r="E2828" s="2" t="n"/>
+    </row>
+    <row r="2829">
+      <c r="E2829" s="2" t="n"/>
+    </row>
+    <row r="2830">
+      <c r="E2830" s="2" t="n"/>
+    </row>
+    <row r="2831">
+      <c r="E2831" s="2" t="n"/>
+    </row>
+    <row r="2832">
+      <c r="E2832" s="2" t="n"/>
+    </row>
+    <row r="2833">
+      <c r="E2833" s="2" t="n"/>
+    </row>
+    <row r="2834">
+      <c r="E2834" s="2" t="n"/>
+    </row>
+    <row r="2835">
+      <c r="E2835" s="2" t="n"/>
+    </row>
+    <row r="2836">
+      <c r="E2836" s="2" t="n"/>
+    </row>
+    <row r="2837">
+      <c r="E2837" s="2" t="n"/>
+    </row>
+    <row r="2838">
+      <c r="E2838" s="2" t="n"/>
+    </row>
+    <row r="2839">
+      <c r="E2839" s="2" t="n"/>
+    </row>
+    <row r="2840">
+      <c r="E2840" s="2" t="n"/>
+    </row>
+    <row r="2841">
+      <c r="E2841" s="2" t="n"/>
+    </row>
+    <row r="2842">
+      <c r="E2842" s="2" t="n"/>
+    </row>
+    <row r="2843">
+      <c r="E2843" s="2" t="n"/>
+    </row>
+    <row r="2844">
+      <c r="E2844" s="2" t="n"/>
+    </row>
+    <row r="2845">
+      <c r="E2845" s="2" t="n"/>
+    </row>
+    <row r="2846">
+      <c r="E2846" s="2" t="n"/>
+    </row>
+    <row r="2847">
+      <c r="E2847" s="2" t="n"/>
+    </row>
+    <row r="2848">
+      <c r="E2848" s="2" t="n"/>
+    </row>
+    <row r="2849">
+      <c r="E2849" s="2" t="n"/>
+    </row>
+    <row r="2850">
+      <c r="E2850" s="2" t="n"/>
+    </row>
+    <row r="2851">
+      <c r="E2851" s="2" t="n"/>
+    </row>
+    <row r="2852">
+      <c r="E2852" s="2" t="n"/>
+    </row>
+    <row r="2853">
+      <c r="E2853" s="2" t="n"/>
+    </row>
+    <row r="2854">
+      <c r="E2854" s="2" t="n"/>
+    </row>
+    <row r="2855">
+      <c r="E2855" s="2" t="n"/>
+    </row>
+    <row r="2856">
+      <c r="E2856" s="2" t="n"/>
+    </row>
+    <row r="2857">
+      <c r="E2857" s="2" t="n"/>
+    </row>
+    <row r="2858">
+      <c r="E2858" s="2" t="n"/>
+    </row>
+    <row r="2859">
+      <c r="E2859" s="2" t="n"/>
+    </row>
+    <row r="2860">
+      <c r="E2860" s="2" t="n"/>
+    </row>
+    <row r="2861">
+      <c r="E2861" s="2" t="n"/>
+    </row>
+    <row r="2862">
+      <c r="E2862" s="2" t="n"/>
+    </row>
+    <row r="2863">
+      <c r="E2863" s="2" t="n"/>
+    </row>
+    <row r="2864">
+      <c r="E2864" s="2" t="n"/>
+    </row>
+    <row r="2865">
+      <c r="E2865" s="2" t="n"/>
+    </row>
+    <row r="2866">
+      <c r="E2866" s="2" t="n"/>
+    </row>
+    <row r="2867">
+      <c r="E2867" s="2" t="n"/>
+    </row>
+    <row r="2868">
+      <c r="E2868" s="2" t="n"/>
+    </row>
+    <row r="2869">
+      <c r="E2869" s="2" t="n"/>
+    </row>
+    <row r="2870">
+      <c r="E2870" s="2" t="n"/>
+    </row>
+    <row r="2871">
+      <c r="E2871" s="2" t="n"/>
+    </row>
+    <row r="2872">
+      <c r="E2872" s="2" t="n"/>
+    </row>
+    <row r="2873">
+      <c r="E2873" s="2" t="n"/>
+    </row>
+    <row r="2874">
+      <c r="E2874" s="2" t="n"/>
+    </row>
+    <row r="2875">
+      <c r="E2875" s="2" t="n"/>
+    </row>
+    <row r="2876">
+      <c r="E2876" s="2" t="n"/>
+    </row>
+    <row r="2877">
+      <c r="E2877" s="2" t="n"/>
+    </row>
+    <row r="2878">
+      <c r="E2878" s="2" t="n"/>
+    </row>
+    <row r="2879">
+      <c r="E2879" s="2" t="n"/>
+    </row>
+    <row r="2880">
+      <c r="E2880" s="2" t="n"/>
+    </row>
+    <row r="2881">
+      <c r="E2881" s="2" t="n"/>
+    </row>
+    <row r="2882">
+      <c r="E2882" s="2" t="n"/>
+    </row>
+    <row r="2883">
+      <c r="E2883" s="2" t="n"/>
+    </row>
+    <row r="2884">
+      <c r="E2884" s="2" t="n"/>
+    </row>
+    <row r="2885">
+      <c r="E2885" s="2" t="n"/>
+    </row>
+    <row r="2886">
+      <c r="E2886" s="2" t="n"/>
+    </row>
+    <row r="2887">
+      <c r="E2887" s="2" t="n"/>
+    </row>
+    <row r="2888">
+      <c r="E2888" s="2" t="n"/>
+    </row>
+    <row r="2889">
+      <c r="E2889" s="2" t="n"/>
+    </row>
+    <row r="2890">
+      <c r="E2890" s="2" t="n"/>
+    </row>
+    <row r="2891">
+      <c r="E2891" s="2" t="n"/>
+    </row>
+    <row r="2892">
+      <c r="E2892" s="2" t="n"/>
+    </row>
+    <row r="2893">
+      <c r="E2893" s="2" t="n"/>
+    </row>
+    <row r="2894">
+      <c r="E2894" s="2" t="n"/>
+    </row>
+    <row r="2895">
+      <c r="E2895" s="2" t="n"/>
+    </row>
+    <row r="2896">
+      <c r="E2896" s="2" t="n"/>
+    </row>
+    <row r="2897">
+      <c r="E2897" s="2" t="n"/>
+    </row>
+    <row r="2898">
+      <c r="E2898" s="2" t="n"/>
+    </row>
+    <row r="2899">
+      <c r="E2899" s="2" t="n"/>
+    </row>
+    <row r="2900">
+      <c r="E2900" s="2" t="n"/>
+    </row>
+    <row r="2901">
+      <c r="E2901" s="2" t="n"/>
+    </row>
+    <row r="2902">
+      <c r="E2902" s="2" t="n"/>
+    </row>
+    <row r="2903">
+      <c r="E2903" s="2" t="n"/>
+    </row>
+    <row r="2904">
+      <c r="E2904" s="2" t="n"/>
+    </row>
+    <row r="2905">
+      <c r="E2905" s="2" t="n"/>
+    </row>
+    <row r="2906">
+      <c r="E2906" s="2" t="n"/>
+    </row>
+    <row r="2907">
+      <c r="E2907" s="2" t="n"/>
+    </row>
+    <row r="2908">
+      <c r="E2908" s="2" t="n"/>
+    </row>
+    <row r="2909">
+      <c r="E2909" s="2" t="n"/>
+    </row>
+    <row r="2910">
+      <c r="E2910" s="2" t="n"/>
+    </row>
+    <row r="2911">
+      <c r="E2911" s="2" t="n"/>
+    </row>
+    <row r="2912">
+      <c r="E2912" s="2" t="n"/>
+    </row>
+    <row r="2913">
+      <c r="E2913" s="2" t="n"/>
+    </row>
+    <row r="2914">
+      <c r="E2914" s="2" t="n"/>
+    </row>
+    <row r="2915">
+      <c r="E2915" s="2" t="n"/>
+    </row>
+    <row r="2916">
+      <c r="E2916" s="2" t="n"/>
+    </row>
+    <row r="2917">
+      <c r="E2917" s="2" t="n"/>
+    </row>
+    <row r="2918">
+      <c r="E2918" s="2" t="n"/>
+    </row>
+    <row r="2919">
+      <c r="E2919" s="2" t="n"/>
+    </row>
+    <row r="2920">
+      <c r="E2920" s="2" t="n"/>
+    </row>
+    <row r="2921">
+      <c r="E2921" s="2" t="n"/>
+    </row>
+    <row r="2922">
+      <c r="E2922" s="2" t="n"/>
+    </row>
+    <row r="2923">
+      <c r="E2923" s="2" t="n"/>
+    </row>
+    <row r="2924">
+      <c r="E2924" s="2" t="n"/>
+    </row>
+    <row r="2925">
+      <c r="E2925" s="2" t="n"/>
+    </row>
+    <row r="2926">
+      <c r="E2926" s="2" t="n"/>
+    </row>
+    <row r="2927">
+      <c r="E2927" s="2" t="n"/>
+    </row>
+    <row r="2928">
+      <c r="E2928" s="2" t="n"/>
+    </row>
+    <row r="2929">
+      <c r="E2929" s="2" t="n"/>
+    </row>
+    <row r="2930">
+      <c r="E2930" s="2" t="n"/>
+    </row>
+    <row r="2931">
+      <c r="E2931" s="2" t="n"/>
+    </row>
+    <row r="2932">
+      <c r="E2932" s="2" t="n"/>
+    </row>
+    <row r="2933">
+      <c r="E2933" s="2" t="n"/>
+    </row>
+    <row r="2934">
+      <c r="E2934" s="2" t="n"/>
+    </row>
+    <row r="2935">
+      <c r="E2935" s="2" t="n"/>
+    </row>
+    <row r="2936">
+      <c r="E2936" s="2" t="n"/>
+    </row>
+    <row r="2937">
+      <c r="E2937" s="2" t="n"/>
+    </row>
+    <row r="2938">
+      <c r="E2938" s="2" t="n"/>
+    </row>
+    <row r="2939">
+      <c r="E2939" s="2" t="n"/>
+    </row>
+    <row r="2940">
+      <c r="E2940" s="2" t="n"/>
+    </row>
+    <row r="2941">
+      <c r="E2941" s="2" t="n"/>
+    </row>
+    <row r="2942">
+      <c r="E2942" s="2" t="n"/>
+    </row>
+    <row r="2943">
+      <c r="E2943" s="2" t="n"/>
+    </row>
+    <row r="2944">
+      <c r="E2944" s="2" t="n"/>
+    </row>
+    <row r="2945">
+      <c r="E2945" s="2" t="n"/>
+    </row>
+    <row r="2946">
+      <c r="E2946" s="2" t="n"/>
+    </row>
+    <row r="2947">
+      <c r="E2947" s="2" t="n"/>
+    </row>
+    <row r="2948">
+      <c r="E2948" s="2" t="n"/>
+    </row>
+    <row r="2949">
+      <c r="E2949" s="2" t="n"/>
+    </row>
+    <row r="2950">
+      <c r="E2950" s="2" t="n"/>
+    </row>
+    <row r="2951">
+      <c r="E2951" s="2" t="n"/>
+    </row>
+    <row r="2952">
+      <c r="E2952" s="2" t="n"/>
+    </row>
+    <row r="2953">
+      <c r="E2953" s="2" t="n"/>
+    </row>
+    <row r="2954">
+      <c r="E2954" s="2" t="n"/>
+    </row>
+    <row r="2955">
+      <c r="E2955" s="2" t="n"/>
+    </row>
+    <row r="2956">
+      <c r="E2956" s="2" t="n"/>
+    </row>
+    <row r="2957">
+      <c r="E2957" s="2" t="n"/>
+    </row>
+    <row r="2958">
+      <c r="E2958" s="2" t="n"/>
+    </row>
+    <row r="2959">
+      <c r="E2959" s="2" t="n"/>
+    </row>
+    <row r="2960">
+      <c r="E2960" s="2" t="n"/>
+    </row>
+    <row r="2961">
+      <c r="E2961" s="2" t="n"/>
+    </row>
+    <row r="2962">
+      <c r="E2962" s="2" t="n"/>
+    </row>
+    <row r="2963">
+      <c r="E2963" s="2" t="n"/>
+    </row>
+    <row r="2964">
+      <c r="E2964" s="2" t="n"/>
+    </row>
+    <row r="2965">
+      <c r="E2965" s="2" t="n"/>
+    </row>
+    <row r="2966">
+      <c r="E2966" s="2" t="n"/>
+    </row>
+    <row r="2967">
+      <c r="E2967" s="2" t="n"/>
+    </row>
+    <row r="2968">
+      <c r="E2968" s="2" t="n"/>
+    </row>
+    <row r="2969">
+      <c r="E2969" s="2" t="n"/>
+    </row>
+    <row r="2970">
+      <c r="E2970" s="2" t="n"/>
+    </row>
+    <row r="2971">
+      <c r="E2971" s="2" t="n"/>
+    </row>
+    <row r="2972">
+      <c r="E2972" s="2" t="n"/>
+    </row>
+    <row r="2973">
+      <c r="E2973" s="2" t="n"/>
+    </row>
+    <row r="2974">
+      <c r="E2974" s="2" t="n"/>
+    </row>
+    <row r="2975">
+      <c r="E2975" s="2" t="n"/>
+    </row>
+    <row r="2976">
+      <c r="E2976" s="2" t="n"/>
+    </row>
+    <row r="2977">
+      <c r="E2977" s="2" t="n"/>
+    </row>
+    <row r="2978">
+      <c r="E2978" s="2" t="n"/>
+    </row>
+    <row r="2979">
+      <c r="E2979" s="2" t="n"/>
+    </row>
+    <row r="2980">
+      <c r="E2980" s="2" t="n"/>
+    </row>
+    <row r="2981">
+      <c r="E2981" s="2" t="n"/>
+    </row>
+    <row r="2982">
+      <c r="E2982" s="2" t="n"/>
+    </row>
+    <row r="2983">
+      <c r="E2983" s="2" t="n"/>
+    </row>
+    <row r="2984">
+      <c r="E2984" s="2" t="n"/>
+    </row>
+    <row r="2985">
+      <c r="E2985" s="2" t="n"/>
+    </row>
+    <row r="2986">
+      <c r="E2986" s="2" t="n"/>
+    </row>
+    <row r="2987">
+      <c r="E2987" s="2" t="n"/>
+    </row>
+    <row r="2988">
+      <c r="E2988" s="2" t="n"/>
+    </row>
+    <row r="2989">
+      <c r="E2989" s="2" t="n"/>
+    </row>
+    <row r="2990">
+      <c r="E2990" s="2" t="n"/>
+    </row>
+    <row r="2991">
+      <c r="E2991" s="2" t="n"/>
+    </row>
+    <row r="2992">
+      <c r="E2992" s="2" t="n"/>
+    </row>
+    <row r="2993">
+      <c r="E2993" s="2" t="n"/>
+    </row>
+    <row r="2994">
+      <c r="E2994" s="2" t="n"/>
+    </row>
+    <row r="2995">
+      <c r="E2995" s="2" t="n"/>
+    </row>
+    <row r="2996">
+      <c r="E2996" s="2" t="n"/>
+    </row>
+    <row r="2997">
+      <c r="E2997" s="2" t="n"/>
+    </row>
+    <row r="2998">
+      <c r="E2998" s="2" t="n"/>
+    </row>
+    <row r="2999">
+      <c r="E2999" s="2" t="n"/>
+    </row>
+    <row r="3000">
+      <c r="E3000" s="2" t="n"/>
+    </row>
+    <row r="3001">
+      <c r="E3001" s="2" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H3001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -12501,54 +21597,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Empresa</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Nome do gestor</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Cargo</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>E-mail do gestor</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Gestor de contrato,Gerente,Supervisor,Coordenador"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12557,7 +21606,7 @@
   <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="115" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12570,73 +21619,73 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>Aba "Pessoas": uma linha por colaborador. Matrícula igual à da TFleet (é ela que liga a pessoa ao embarque). Sem matrícula, usa o nome.</t>
+          <t>Preencha só as abas que precisar e suba no painel: Ocupação dos ônibus &gt; Cadastro e gestores &gt; senha &gt; "Subir planilha" &gt; conferir &gt; Salvar.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>E-mail do gestor na linha da pessoa: só se essa pessoa tiver um gestor diferente do resto da empresa. Pode deixar em branco.</t>
+          <t>Aba "Gestor por empresa": uma linha por empresa. O gestor (gerente, gestor de contrato…) recebe o e-mail de TODAS as pessoas daquela empresa. Escreva a empresa como aparece na TFleet.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Aba "Gestor por empresa": o gestor (ou gestor de contrato) de cada empresa. Todo mundo daquela empresa cai para ele.</t>
+          <t>Aba "Base de gestores": gestor por gerência de área (GA), gerência geral (GG) e centro de custo. Preencha só o que souber: só GA já vale para toda a GA; com centro de custo vale só para aquele centro.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Para quem vai o e-mail de passageiro fora de rota: 1) e-mail do gestor na linha da pessoa; 2) gestor da empresa; 3) gestor da gerência (GA) cadastrado no painel; 4) sem nenhum, vai para você.</t>
+          <t>Aba "Pessoas": SÓ para exceções, quem tem um gestor diferente do resto da empresa. Matrícula igual à da TFleet.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Cada linha precisa de pelo menos um destes: e-mail do gestor, empresa ou gerência de área.</t>
+          <t>Para quem vai o e-mail: 1) pessoa com gestor próprio; 2) gestor da empresa; 3) base por centro de custo; 4) base por GA; 5) base por GG; 6) sem nenhum, vai para você.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Subir: painel Ocupação dos ônibus &gt; Gestores &gt; senha &gt; "Subir planilha". Ou copiar as linhas e colar na caixa.</t>
+          <t>Mandar de novo a mesma empresa, a mesma GA/GG/centro de custo ou a mesma matrícula atualiza o cadastro. Não precisa apagar antes.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Mandar a mesma pessoa de novo atualiza o cadastro dela.</t>
+          <t>Exemplos (não preencher aqui):</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr"/>
-    </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Exemplo (não preencher aqui):</t>
+          <t>Gestor por empresa:  EMPRESA X LTDA | Maria Souza | Gestor de contrato | maria.souza@empresax.com.br</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Pessoas:  1234567 | 0012345678 | JOÃO DA SILVA | EMPRESA X | MANUTENÇÃO MINA | OPERAÇÕES MINA | (vazio) | (vazio)</t>
+          <t>Base de gestores:  João Lima | joao.lima@hydro.com | MANUTENÇÃO MINA | OPERAÇÕES MINA | 000035</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Gestor por empresa:  EMPRESA X | Maria Souza | Gestor de contrato | maria.souza@empresax.com.br</t>
+          <t>Pessoas:  1234567 | 0012345678 | JOSÉ DA SILVA | EMPRESA X LTDA | MANUTENÇÃO MINA | OPERAÇÕES MINA | ana@empresax.com.br | Ana</t>
         </is>
       </c>
     </row>
